--- a/Lab/outils/work/enriched.xlsx
+++ b/Lab/outils/work/enriched.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Les échos du passé</t>
+          <t>Urchin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -564,29 +564,29 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mascha Schilinski</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Prix du jury Cannes 2025</t>
-        </is>
-      </c>
+          <t>Harris Dickinson</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/16/07/1607b1aa4e7516d75f83006f89c4cb20.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/e7/82/e782432beca8a04cea3b2dc66459c4a5.jpg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Quatre jeunes filles à quatre époques différentes. Alma, Erika, Angelika et Lenka passent leur adolescence dans la même ferme, au nord de l’Allemagne. Alors que la maison se transforme au fil du siècle, les échos du passé résonnent entre ses murs. Malgré les années qui les séparent, leurs vies semblent se répondre.</t>
+          <t>À Londres, Mike vit dans la rue, il va de petits boulots en larcins, jusqu'au jour où il se fait incarcérer. À sa sortie de prison, aidé par les services sociaux, il tente de reprendre sa vie en main en combattant ses vieux démons.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -596,352 +596,344 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United Kingdom, United States of America</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Luise Heyer, Lena Urzendowsky, Claudia Geisler-Bading, Lea Drinda, Hanna Heckt, Laeni Geiseler, Florian Geißelmann, Andreas Anke</t>
+          <t>Frank Dillane, Megan Northam, Карина Химчук, Shonagh Marie, Amr Waked, Claudia Jones, Shahzad Ali, Michael Quartey</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Prix du jury Cannes 2025, Festival de Cannes 2025: Prix du Jury</t>
+          <t>Festival de Cannes 2025: Un Certain Regard - Prix du meilleur acteur</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=O-jgGbvLgVo</t>
+          <t>https://www.youtube.com/watch?v=4cJL6vmYOeo</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325123.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019912.html</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/86/d3/86d38c6dd4000621947c32b2014372f3.jpg", "https://fr.web.img2.acsta.net/img/be/c5/bec52dc5aeea9924834d5f46cd9b8cc9.jpg", "https://fr.web.img6.acsta.net/img/6d/07/6d078fd7f3d7326d1c3ee3953f9bc9d1.jpg", "https://fr.web.img2.acsta.net/img/5c/db/5cdb07e0ee44ccc8941753c17d1e36a8.jpg", "https://fr.web.img5.acsta.net/img/40/d2/40d290c211e1bb18d48d917d0ca50f9b.jpg", "https://fr.web.img5.acsta.net/img/07/73/07735cd34fa049081e34c640d97fe19d.jpg", "https://fr.web.img2.acsta.net/img/f2/b4/f2b4b9064e0c0860d0a897904fbd0bf4.jpg", "https://fr.web.img4.acsta.net/img/6c/42/6c424327f43349499b27fd96f15be722.jpg", "https://fr.web.img6.acsta.net/img/85/92/8592629bc839a2ed6132c6a2898bd64e.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/bb/78/bb784f39d4843f599afba87529b2c028.jpg", "https://fr.web.img2.acsta.net/img/df/3d/df3dc86c2a96673a0d49796581ea5929.jpg", "https://fr.web.img4.acsta.net/img/1e/44/1e4451e35e6059ee33003bb1ddbe8b9c.jpg", "https://fr.web.img2.acsta.net/img/2d/a2/2da21da8e6c084f763290e30f0e31548.jpg", "https://fr.web.img6.acsta.net/img/da/30/da301edeec034ee0839592ee70672741.jpg", "https://fr.web.img4.acsta.net/img/fc/1e/fc1e3b1ba4bbd2e5fb722ed5f0b294e3.jpg"]</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Christy and his brother</t>
+          <t>Le sommet des dieux</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CM1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Brendan Canty</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coip de cœur</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Patrick Imbert</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SCOL CauC</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/88/62/8862127888090061db98a62f1680fd52.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/pictures/21/07/29/17/38/3976490.jpg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Expulsé de sa famille d’accueil, Christy, 17 ans, débarque chez son demi-frère, jeune papa, qu’il connait peu. Ce dernier vit mal cet arrangement qu’il espère temporaire, mais Christy se sent vite chez lui, dans ce quartier populaire de Cork, se faisant des amis et renouant avec la famille de sa mère. Les deux frères vont devoir se confronter à leur passé tumultueux pour envisager un avenir commun.</t>
+          <t>A Katmandou, le reporter japonais Fukamachi croit reconnaître Habu Jôji, cet alpiniste que l'on pensait disparu depuis des années. Il semble tenir entre ses mains un appareil photo qui pourrait changer l’histoire de l’alpinisme. Et si George Mallory et Andrew Irvine étaient les premiers hommes à avoir atteint le sommet de l’Everest, le 8 juin 1924 ? Seul le petit Kodak Vest Pocket avec lequel ils devaient se photographier sur le toit du monde pourrait livrer la vérité. 70 ans plus tard, pour tenter de résoudre ce mystère, Fukamachi se lance sur les traces de Habu. Il découvre un monde de passionnés assoiffés de conquêtes impossibles et décide de l’accompagner jusqu’au voyage ultime vers le sommet des dieux.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Aventure, Animation, Drame</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Ireland, United Kingdom</t>
+          <t>France, Luxembourg</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Danny Power, Diarmuid Noyes, Emma Willis, Alison Oliver, Helen Behan, Chris Walley, Kane O'Connell Flynn, Ciaran Bermingham</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>Éric Herson-Macarel, Damien Boisseau, Elisabeth Ventura, Lazare Herson-Macarel, Kylian Rehlinger, François Dunoyer, Philippe Vincent, Luc Bernard</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2.8, César 2022: César du Meilleur film d'animation, Lumières de la presse étrangère 2022: Meilleur film d'animation, Fondation Gan pour le cinéma 2018: Prix Fondation Gan, Festival du Cinéma et Musique de Film de la Baule 2022: Ibis d'or de la meilleure musique de film de l'année</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yz9t81MXyt0</t>
+          <t>https://www.youtube.com/watch?v=sM_KmxpEaJU</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019314.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=269946.html</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/81/8e/818eeea254d15ea4716b00236a0918bd.jpg", "https://fr.web.img4.acsta.net/img/b5/5f/b55faaf266f267a80ed33293c62c4433.jpg", "https://fr.web.img6.acsta.net/img/e1/77/e17706fcba04a53a1edd40b0a02b1602.jpg", "https://fr.web.img2.acsta.net/img/44/ca/44ca7eca8532911c18bb517e8d44a57a.jpg", "https://fr.web.img5.acsta.net/img/37/21/372151cf69d85927e75aa87f32909301.jpg", "https://fr.web.img6.acsta.net/img/8b/38/8b38eb824aa3cd56fa2c21b9e97aa8a3.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/pictures/21/07/09/13/07/5600107.jpg", "https://fr.web.img4.acsta.net/pictures/21/07/09/13/07/5586066.jpg", "https://fr.web.img6.acsta.net/pictures/21/07/09/13/07/5572026.jpg", "https://fr.web.img6.acsta.net/pictures/21/07/09/13/07/5557985.jpg", "https://fr.web.img3.acsta.net/pictures/21/07/09/13/07/5543945.jpg"]</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2021-09-22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ma frère</t>
+          <t>Rue Malaga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lise Akoka, Romane Gueret</t>
+          <t>Maryam Touzani</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI - Famille</t>
+          <t>Prix du public Venise</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Tarif Unique 5 €</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/35/23/35233aa3767ab31d242ec1c3ff34497c.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/4f/46/4f46a55374da1919875e846787fd1289.jpg</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Shaï et Djeneba ont 20 ans et sont amies depuis l’enfance. Cet été-là, elles sont animatrices dans une colonie de vacances. Elles accompagnent dans la Drôme une bande d’enfants qui, comme elles, ont grandi entre les tours de la Place des Fêtes à Paris. À l’aube de l’âge adulte, elles devront faire des choix pour dessiner leur avenir et réinventer leur amitié.</t>
+          <t>Maria Angeles, une Espagnole de 79 ans, vit seule à Tanger, dans le nord du Maroc, où elle profite de sa ville et de son quotidien. Sa vie bascule lorsque sa fille Clara arrive de Madrid pour vendre l’appartement dans lequel elle a toujours vécu. Déterminée à rester dans cette ville qui l'a vue grandir, elle met tout en œuvre pour garder sa maison et récupérer les objets d'une vie. Contre toute attente, elle redécouvre en chemin l’amour et le désir.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>117</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Morocco, France, Spain, Germany, Belgium</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fanta Kebe, Shirel Nataf, Zakaria-Tayeb Lazab, Mouctar Diawara, Idir Azougli, Yuming Hey, Suzanne De Baecque, Amel Bent</t>
+          <t>Carmen Maura, Marta Etura, Ahmed Boulane, Miguel Garcés, María Alfonsa Rosso, La Imèn, Tarik Rmili, Mohamed Naimane</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=53BgM9euEOQ</t>
+          <t>https://www.youtube.com/watch?v=FwtLBQpAnk0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007387.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020088.html</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/98/b8/98b83a6cafcd5ae0c8a89c20f9ae7437.jpg", "https://fr.web.img2.acsta.net/img/37/9d/379dbf504a6aee9a25b25e1c699b25c3.jpg", "https://fr.web.img4.acsta.net/img/5e/08/5e08b0482694b6ce002742071afe0b45.jpg", "https://fr.web.img6.acsta.net/img/2d/c0/2dc0c49d0be726b94b67121cac743537.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/84/df/84dfc5e9a03da904c491ef5bcab2ec53.jpg", "https://fr.web.img5.acsta.net/img/0e/d4/0ed4d030496886c31283dad276baec29.jpg", "https://fr.web.img5.acsta.net/img/4a/cb/4acb7d81653a7b5ca65bdc5257fefef6.jpg", "https://fr.web.img6.acsta.net/img/55/0b/550b3a5a46eefd999b31e246819e1b4d.jpg", "https://fr.web.img6.acsta.net/img/17/22/1722bdb5f07a5101d5df9ec34a463491.jpg"]</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hamnet</t>
+          <t>Microcosmos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chloé Zhao</t>
+          <t>Claude Nuridsany, Marie Pérennou</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SCOL EauC</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/9a/f5/9af5f87b39938fec50f86c32c3d31b69.jpg</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Angleterre, 1580. Un professeur de latin fauché, fait la connaissance d’Agnes, jeune femme à l’esprit libre. Fascinés l’un par l’autre, ils entament une liaison fougueuse avant de se marier et d’avoir trois enfants. Tandis que Will tente sa chance comme dramaturge à Londres, Agnes assume seule les tâches domestiques. Lorsqu’un drame se produit, le couple, autrefois profondément uni, vacille. Mais c’est de leur épreuve commune que naîtra l’inspiration d’un chef d’œuvre universel.</t>
+          <t>Voyage sur terre à l’échelle du centimètre. Ses habitants: insectes et autres animaux de l'herbe et de l'eau. Grand prix de la commission supérieure technique, Festival de Cannes 1996.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>United Kingdom, United States of America</t>
+          <t>France, Switzerland, Italy</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jessie Buckley, Paul Mescal, Emily Watson, Joe Alwyn, Jacobi Jupe, Noah Jupe, Bodhi Rae Breathnach, Olivia Lynes</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026, Golden Globes 2026: Meilleur film dramatique, Meilleure actrice dans un drame</t>
-        </is>
-      </c>
+          <t>Jacques Perrin</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>1996-05-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYcgQMxQwmk</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=315003.html</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img6.acsta.net/img/db/27/db27c1195bfb8835aef4671ac165e436.jpg", "https://fr.web.img3.acsta.net/img/ea/c4/eac4203c2df8347475f77ec8ce61d7ca.jpg", "https://fr.web.img6.acsta.net/img/7e/b8/7eb8bf6fa577347479dfd6347f103afb.jpg", "https://fr.web.img4.acsta.net/img/b0/3d/b03d7554c97c3f7ba8c880de57c35b31.jpg", "https://fr.web.img2.acsta.net/img/e0/f2/e0f2b4497faaf505ab30ecd733f2a531.jpg", "https://fr.web.img6.acsta.net/img/9a/fd/9afde980a6402b830c5007cc66e72aff.jpg", "https://fr.web.img5.acsta.net/img/ce/fe/cefe5da862eb8228d3bf79a068a9844a.jpg", "https://fr.web.img4.acsta.net/img/c0/41/c041a05c78908f57f777fb269f515979.jpg", "https://fr.web.img3.acsta.net/img/fd/f9/fdf917bfcee844d0fbd3ac41bba90997.jpg", "https://fr.web.img5.acsta.net/img/dc/88/dc886647f0301e242fd931547cd4d10e.jpg", "https://fr.web.img2.acsta.net/img/fc/d8/fcd8803be480fc3fd79f80b56597c9ba.jpg", "https://fr.web.img2.acsta.net/img/f1/de/f1deaf59daf5e4773c85bcf1702633d7.jpg", "https://fr.web.img2.acsta.net/img/5f/dc/5fdc64d7259e00568cfd5ab9344356b1.jpg", "https://fr.web.img3.acsta.net/img/19/5f/195f3ffc57720410317e2fb3d51ae61f.jpg", "https://fr.web.img2.acsta.net/img/b8/76/b876bf840dab929460f48ff0dac4d321.jpg"]</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=5fA3h9dy1NQ</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>1996-05-20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Alter ego</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -952,188 +944,192 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Irene Iborra</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
+          <t>Nicolas Charlet, Bruno Lavaine</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TU 5 €</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Séance EPHAD HANDI</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/35/40/354092484a9bc5dfedb67167f9da43da.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/a3/21/a3212f7a3bc901b69704c09de6e30093.jpg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>À 12 ans, Olivia voit son quotidien bouleversé du jour au lendemain. Elle va devoir s’habituer à une nouvelle vie plus modeste et veiller seule sur son petit frère Tim. Mais, heureusement, leur rencontre avec des voisins chaleureux et hauts en couleur va transformer leur monde en un vrai film d’aventure ! Ensemble, ils vont faire de chaque défi un jeu et de chaque journée un moment inoubliable.D’après le roman Olivia de Maite Carranza.</t>
+          <t>Alex a un problème : son nouveau voisin est son sosie parfait. Avec des cheveux. Un double en mieux, qui va totalement bouleverser son existence.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Animation</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Olivia Leon</t>
+          <t>Laurent Lafitte, Olga Kurylenko, Blanche Gardin, Valérie Donzelli, Monsieur Fraize, Zabou Breitman, Bertrand Goncalves</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Festival du Film d'Animation d'Annecy 2025: Prix Fondation Gan à la Diffusion</t>
+          <t>TU 5 €</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ObYzfs8ITaE</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=302424.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=288260.html</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/68/7d/687dcf80fd39e1a57716b2d8386570a8.jpg", "https://fr.web.img3.acsta.net/img/d5/64/d5641afeb1a1642616fed8ebddb88f7f.jpg", "https://fr.web.img5.acsta.net/img/e0/9f/e09f107f2cfe985b36a15aae0a2ffcb3.jpg", "https://fr.web.img6.acsta.net/img/5c/20/5c2057cf0bbdb2994fbb4f581cac70eb.jpg", "https://fr.web.img6.acsta.net/img/5a/95/5a956d1bc8d439383efb75c8f58020a3.jpg", "https://fr.web.img6.acsta.net/img/e0/58/e05866f0898362e1ddb408a724b4bccb.jpg", "https://fr.web.img2.acsta.net/img/d1/79/d179899a0e3dcdaa15a123c96785b7e6.jpg", "https://fr.web.img6.acsta.net/img/8c/e4/8ce4f7d363e6b866184f85fbb6ba51dc.jpg", "https://fr.web.img4.acsta.net/img/18/5e/185eb0f57dc20597fcf0762ed42135b7.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/80/5b/805b22393a7bfefa87e3451df4cf7dec.jpg", "https://fr.web.img5.acsta.net/img/07/ab/07abed9ca6cb0edbc30f2b81cbb9b834.jpg", "https://fr.web.img6.acsta.net/img/4b/3f/4b3fbfd620d39125a6f27fb7892d55bb.jpg", "https://fr.web.img3.acsta.net/img/23/af/23af1eaeb399756c22b6bf621a1d2975.jpg", "https://fr.web.img6.acsta.net/img/33/47/334744d4e4ada016646ca09124efe5f1.jpg", "https://fr.web.img2.acsta.net/img/9a/5f/9a5fb0790ce6ddcc6a39202ec8828fe5.jpg", "https://fr.web.img6.acsta.net/img/6b/da/6bdaeb4a15e035b7aa58b4e87bd47ac7.jpg", "https://fr.web.img2.acsta.net/img/b9/62/b962e3314824b9b32d8cf4320496290c.jpg"]</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bardot</t>
+          <t>La couleuvre noire</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Alain Berliner, Elora Thevenet</t>
+          <t>Aurélien Vernhes-Lermusiaux</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
+          <t>Prix Fondation Gan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
+          <t>Cinélatino Avant-première</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/18/89/188956009aaf66c5f715713a92dd670a.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/41/e6/41e68878abbf465c362d6dcf53bdf30d.jpg</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Jamais vraiment dans une case, muse de cinéastes finissant par sacrifier tout à la cause animale, Brigitte Bardot est une femme libre mais sans doute incomprise. BARDOT revient sur les aspects si contradictoires de sa vie, de sa carrière artistique légendaire à sa célèbre fondation. Elle qui bouscula l’image des femmes et fut en avance sur la conscience écologique et le bien-être animal qui semblent, enfin, pour tous une évidence. Une réflexion croisée sur ce que signifie être une femme artiste, une femme libre et parfois en avance sur son temps.</t>
+          <t>Après des années d’absence, Ciro revient chez lui, au chevet de sa mère. Dans ce désert colombien de la Tatacoa, il retrouve ceux qu’il avait fuis et affronte les derniers gardiens d’un territoire aussi fragile qu’envoûtant.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>85</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>France, United Kingdom</t>
+          <t>Colombia, Brazil, France</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brigitte Bardot, Claude Lelouch, Naomi Campbell, Paul Watson, Stella McCartney, Hugo Clément, Allain Bougrain-Dubourg</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>Alexis Tafur, Miguel Ángel Viera, Ángela Rodríguez, Laura Valentina Quintero, Virgelina Gil Saénz, Santiago Porras, Laura Rodríguez, Jonathan Mortenson</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Fondation Gan pour le cinéma 2023: Fondation Gan - Prix à la création</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2M1zr-f7Wtk</t>
-        </is>
-      </c>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=304625.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325278.html</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/84/47/84478d2cb4fd84519c8311ae8c84329f.jpg", "https://fr.web.img2.acsta.net/img/01/8c/018c905f1b37dea1b18c796e4bf00817.jpg", "https://fr.web.img3.acsta.net/img/b2/6a/b26a24bf510fc9eeb1f05fa534fc4877.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/bb/97/bb97bee3e88688957ba27a8753fbeb36.jpg", "https://fr.web.img6.acsta.net/img/e2/67/e267201f2a234b9227f0caf0c2fbe8f5.jpg", "https://fr.web.img6.acsta.net/img/e4/3f/e43f8f9bb6b21486ed7aaaf11ef813b4.jpg", "https://fr.web.img2.acsta.net/img/9c/23/9c236b8bfd0d130eb548acf4198ebacf.jpg", "https://fr.web.img4.acsta.net/img/d3/6b/d36b2b2c604b0fb61f8dc457d579f722.jpg", "https://fr.web.img3.acsta.net/img/df/f4/dff426c01fc11d33ec6f763b4a0ac0b4.jpg", "https://fr.web.img6.acsta.net/img/49/70/49705864b270d9141fd2f87877bfbb9b.jpg", "https://fr.web.img6.acsta.net/img/f6/fb/f6fbab37a4045cb645f3b2c585eeb018.jpg", "https://fr.web.img4.acsta.net/img/17/98/17984d2d9dc437fb8ab12cfbf25ae155.jpg"]</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grand ciel</t>
+          <t>L'ourse et l'oiseau</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1144,84 +1140,76 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Akihiro Hata</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+          <t>Marie Caudry, Aurore Peuffier, Nina Bisyarina</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TU 3 €</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/46/06/460600d5f82b83f150654089c463af9b.jpg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Vincent travaille au sein d’une équipe de nuit sur le chantier de Grand Ciel, un nouveau quartier futuriste. Lorsqu’un ouvrier disparaît, Vincent et ses collègues suspectent leur hiérarchie d’avoir dissimulé son accident. Mais bientôt un autre ouvrier disparait.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Thriller, Drame</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/af/46/af46510d2d819c30b064e68efa6e5233.jpg</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>France, Luxembourg</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Damien Bonnard, Samir Guesmi, Mouna Soualem, Tudor Aaron Istodor, Ahmed Abdel Laoui, Issaka Sawadogo, Sophie Mousel, Denis Eyriey</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>TU 3 €</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=DkPQbmM-uZM</t>
-        </is>
-      </c>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=300430.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000031821.html</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/0f/e0/0fe0a74367803075fd0f0381d06bd4f3.jpg", "https://fr.web.img6.acsta.net/img/49/75/4975868cbec7f4b9228533568e65a83a.jpg", "https://fr.web.img4.acsta.net/img/ed/d1/edd1eaa8be28495ddb4a4ffaef01abb0.jpg", "https://fr.web.img4.acsta.net/img/09/5f/095fef1364af93787d4e13e110fb9dae.jpg", "https://fr.web.img5.acsta.net/img/f4/c2/f4c25e50a561c0566c338c5485e0d70d.jpg", "https://fr.web.img5.acsta.net/img/02/cf/02cf505e6f0ec20bfd9e08bfe041dc31.jpg", "https://fr.web.img6.acsta.net/img/c1/37/c137795561f8165a58e53498c0fe86ce.jpg", "https://fr.web.img4.acsta.net/img/ba/7e/ba7e00cac438cb9a64541afba9f3de54.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/84/71/8471bb1a8bd4e80543025ce50f15748f.jpg", "https://fr.web.img4.acsta.net/img/92/65/9265c8b5dc48406633f3fb1fbd6ddfca.jpg", "https://fr.web.img6.acsta.net/img/a4/17/a4178fea144bc542aeb1d67517b484e3.jpg", "https://fr.web.img6.acsta.net/img/21/b7/21b7fff1eb2b6d33c60f28bc8262df70.jpg", "https://fr.web.img6.acsta.net/img/36/d5/36d51017ba6721475005c65af158b8c3.jpg", "https://fr.web.img5.acsta.net/img/58/25/582576c31308e4460671911d2de3f3ee.jpg", "https://fr.web.img4.acsta.net/img/b9/71/b9712420bfd364b02b83bf3b22470764.jpg", "https://fr.web.img3.acsta.net/img/31/40/31403126892acb5287317c41fdd2b6ec.jpg", "https://fr.web.img2.acsta.net/img/fe/f2/fef22b1db43302c25cb11b8e256c850c.jpg", "https://fr.web.img4.acsta.net/img/bd/64/bd64033f6fc3148e1e917b1544f529b8.jpg", "https://fr.web.img5.acsta.net/img/21/9c/219c65998d57faaf9fe7e4c5bfba0480.jpg", "https://fr.web.img4.acsta.net/img/8f/e9/8fe98fbd0f4fcbc60df34c487b5dde28.jpg", "https://fr.web.img6.acsta.net/img/7f/89/7f89bdc9dbd33efc5169b6876d68a8bb.jpg", "https://fr.web.img3.acsta.net/img/79/d7/79d75776630a8743a034982631efb86e.jpg", "https://fr.web.img5.acsta.net/img/a2/c3/a2c34b595a816cf34d64067cabdbc71c.jpg", "https://fr.web.img4.acsta.net/img/17/4b/174bacf6107acbae117ee7f9ec5a4394.jpg", "https://fr.web.img6.acsta.net/img/b9/63/b963d7a5754630388677ab0567d52e58.jpg", "https://fr.web.img2.acsta.net/img/43/c4/43c4950db5cba3e0b60ed65b2a0a7c71.jpg", "https://fr.web.img4.acsta.net/img/51/a8/51a8e13eb81ae507eab521b88c67cff7.jpg", "https://fr.web.img2.acsta.net/img/15/37/1537d27e10786df4b6d3e23bfef289e7.jpg", "https://fr.web.img6.acsta.net/img/f8/f3/f8f30699660b4646ebdc89302c53fb43.jpg"]</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Biscuit le chien fantastique</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1232,176 +1220,200 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shea Wageman</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Edouard Bergeon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ADH 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>invité Jérôme Bayle attente de réponse</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/7b/09/7b095f309baf4441fc5966b2f217900e.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/76/32/76325273dba162d20a31fbc235173f69.jpg</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Danny et son petit chien Biscuit sont les meilleurs amis du monde. Un jour, une magie mystérieuse donne à Biscuit des pouvoirs incroyables : il peut désormais parler et voler. Dès que quelqu’un a besoin de lui, il met son masque, enfile sa cape et s’élance dans le ciel pour aider : il est devenu un chien fantastique ! Biscuit a désormais deux passions : manger des tacos et sauver le monde. Mais Pudding, le chat du voisin, lui aussi doté de super-pouvoirs, rêve de faire régner les chats sur l’univers. Danny et Biscuit devront prouver qu’ensemble, rien ne peut les arrêter !</t>
+          <t>Edouard Bergeon (« Au Nom de la Terre ») nous plonge dans la vie de Jérôme Bayle, éleveur charismatique du Sud-Ouest et figure nationale de la ruralité. Avec humour et tendresse, il dresse un portrait sensible de l’agriculture familiale française d’aujourd’hui et de ceux qui se battent pour la faire perdurer.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Animation, Comédie, Famille</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Owen Wilson, Dawson Littman, Tabitha St. Germain, Sebastian Billingsley-Rodriguez, Rhona Rees, Anthony Bolognese, Caitlynne Medrek, Emily Delahunty</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>Jérôme Bayle</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ADH 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VmxXMWGaDzQ</t>
+          <t>https://www.youtube.com/watch?v=RdkB6UGDQmM</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017117.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000032102.html</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/cc/bb/ccbb0018fbe560c8535c07949d408025.jpg", "https://fr.web.img3.acsta.net/img/e7/ac/e7acc11655324629f86345607eafcf23.jpg", "https://fr.web.img2.acsta.net/img/f9/7b/f97bfe76e783f57e01a872b7c763cf47.jpg", "https://fr.web.img5.acsta.net/img/7f/c6/7fc688f605e3c9f8bb6fe9058bc80942.jpg", "https://fr.web.img5.acsta.net/img/67/0e/670e08bbd5558a2b53def24b58a59715.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/a3/a0/a3a0456f8fa4f8c2dc2ffc3215e53740.jpg", "https://fr.web.img6.acsta.net/img/a6/7e/a67e4d10463b7272be66cb1bb3b44535.jpg", "https://fr.web.img4.acsta.net/img/1f/f7/1ff7c0cae0beb97de65034488de20640.jpg", "https://fr.web.img6.acsta.net/img/92/4e/924e7c5bcbe978bf140e4dca1c1a29e5.jpg", "https://fr.web.img4.acsta.net/img/d4/10/d41017db78436edfcd562b4192b02e56.jpg", "https://fr.web.img4.acsta.net/img/0c/41/0c410c9f2d25735e7cc3f72a79c16686.jpg", "https://fr.web.img4.acsta.net/img/19/d8/19d86ca951be7193dfbfc73330e0e761.jpg", "https://fr.web.img2.acsta.net/img/d2/e5/d2e56406a296cf0e5a5921fa34ed7415.jpg"]</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L'affaire Bojarski</t>
+          <t>Marty Supreme</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jean-Paul Salomé</t>
+          <t>Josh Safdie</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Golden Globe meilleur acteur</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Coup de cœur</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/18/05/18059e8dd9bca2e516d41023cc08d9d1.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/7d/cb/7dcb8416ab4e8fd4ff6eeaed758c6004.jpg</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Jan Bojarski, jeune ingénieur polonais, se réfugie en France pendant la guerre. Il y utilise ses dons pour fabriquer des faux papiers pendant l’occupation allemande. Après la guerre, son absence d’état civil l’empêche de déposer les brevets de ses nombreuses inventions et il est limité à des petits boulots mal rémunérés… jusqu’au jour où un gangster lui propose d’utiliser ses talents exceptionnels pour fabriquer des faux billets. Démarre alors pour lui une double vie à l’insu de sa famille. Très vite, il se retrouve dans le viseur de l’inspecteur Mattei, meilleur flic de France.</t>
+          <t>Marty Mauser, un jeune homme à l’ambition démesurée, est prêt à tout pour réaliser son rêve et prouver au monde entier que rien ne lui est impossible.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Drame, Biopic</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Reda Kateb, Sara Giraudeau, Bastien Bouillon, Quentin Dolmaire, Pierre Lottin, Camille Japy, Lolita Chammah, Olivier Loustau</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A'zion, Kevin O'Leary, Tyler, The Creator, Fran Drescher, Abel Ferrara, Emory Cohen</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lz4trma4mCU</t>
+          <t>https://www.youtube.com/watch?v=s9gSuKaKcqM</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000014092.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007317.html</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/15/d8/15d8fafca4998c253b2513d29f223350.jpg", "https://fr.web.img5.acsta.net/img/81/b3/81b30ddb0cecd137cedc5220f971c839.jpg", "https://fr.web.img6.acsta.net/img/b1/cf/b1cfe81aa1138030e212e9c701898bf6.jpg", "https://fr.web.img5.acsta.net/img/5a/cc/5acce5895b2080afc842c8d57340122c.jpg", "https://fr.web.img6.acsta.net/img/5d/1e/5d1e210d87c5045ba1d443e552d407f3.jpg", "https://fr.web.img6.acsta.net/img/b1/0f/b10f18819f1ccea971de115bc964d1d6.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/c3/09/c309b5855c7b236945b1013c62676a5c.jpg", "https://fr.web.img5.acsta.net/img/29/b5/29b53a920df12d99a5314b789f1faf9c.jpg", "https://fr.web.img4.acsta.net/img/0d/7d/0d7dfee552b2aa4423aaf0e26885eb9d.jpg", "https://fr.web.img4.acsta.net/img/91/b0/91b02b31e4cf6df8f526d920ed5d1bbb.jpg", "https://fr.web.img5.acsta.net/img/09/80/09801189159bd682629326396f00f1b1.jpg", "https://fr.web.img6.acsta.net/img/cd/df/cddf292cfd1032909df0ccf6057bb151.jpg", "https://fr.web.img6.acsta.net/img/04/e1/04e1efb1f485ab6aa99c0c9ddf05ae28.jpg", "https://fr.web.img6.acsta.net/img/f2/86/f28623015549bbd278d0c162203d0e9d.jpg", "https://fr.web.img5.acsta.net/img/fa/ff/faffe9d8707cbb03040bae34d8bed952.jpg", "https://fr.web.img3.acsta.net/img/a3/04/a30488d5862e30c8597eddcee3f3c426.jpg", "https://fr.web.img6.acsta.net/img/b2/ae/b2ae37eae4f102a5427889137ea062be.jpg", "https://fr.web.img6.acsta.net/img/a1/88/a188dbf927027d760a1034d3cafb2dde.jpg", "https://fr.web.img4.acsta.net/img/f8/05/f8059864a9d229cab3d664173280ca83.jpg", "https://fr.web.img3.acsta.net/img/29/80/298098488caa5271b37f7b8207cc6f83.jpg", "https://fr.web.img6.acsta.net/img/63/88/63888a193780eeb0574c836513e5c75c.jpg"]</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tafiti</t>
+          <t>Marsupilami</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1412,7 +1424,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nina Wels</t>
+          <t>Philippe Lacheau</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1421,263 +1433,271 @@
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/e7/ff/e7ffdee0f33865e434c017c192af11ac.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/b2/cb/b2cb998b62863d43cdd9a5f49c5ea4e6.jpg</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Lorsque Tafiti, un jeune suricate, rencontre Mèchefol, un potamochère aussi sympathique qu’exubérant, il sait qu’ils ne pourront jamais devenir amis. En effet, la vie dans le désert est pleine de dangers et Tafiti a toujours respecté la règle essentielle de survie chez les suricates : il ne faut jamais se lier aux étrangers. Mais lorsque son grand-père est mordu par un serpent venimeux, Tafiti n’a pas le choix. Il doit partir à la recherche d’une fleur légendaire qui guérit de tous les maux, mais qui pousse au-delà des vastes étendues brûlantes du désert. Une quête périlleuse que Tafiti décide d’affronter seul. Mais c’est sans compter sur Mèchefol, bien décidé à accompagner son nouveau meilleur ami dans cette aventure, qu’il le veuille ou non…</t>
+          <t>Pour sauver son emploi, David accepte un plan foireux : ramener un mystérieux colis d’Amérique du Sud. Il se retrouve à bord d’une croisière avec son ex Tess, son fils Léo, et son collègue Stéphane, aussi benêt que maladroit, dont David se sert pour transporter le colis à sa place. Tout dérape lorsque ce dernier l’ouvre accidentellement : un adorable bébé Marsupilami apparait et le voyage vire au chaos ! La bande à Fifi est de retour et elle s’est fait un nouveau copain…</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Animation, Famille, Aventure</t>
+          <t>Comédie, Aventure, Famille</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France, Belgium</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Cosima Henman, Steve Hudson, Bürger Lars Dietrich, Thomas Schmuckert, Dela Dabulamanzi, Simon Werner, Dustin Semmelrogge, Simone Cohn-Vossen</t>
+          <t>Philippe Lacheau, Jamel Debbouze, Tarek Boudali, Élodie Fontan, Julien Arruti, Jean Reno, Corentin Guillot, Gérard Jugnot</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0AG59XQEhbA</t>
+          <t>https://www.youtube.com/watch?v=jd1p07MSUHA</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327254.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317669.html</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/19/77/1977bdc7a0058cac90b8d00732caf0ca.jpg", "https://fr.web.img4.acsta.net/img/52/e6/52e62dd9215f23f1e25d326ba6b7a5fa.jpg", "https://fr.web.img2.acsta.net/img/e5/7e/e57edcf31ace74fb0a0f6f4de3be14cd.jpg", "https://fr.web.img6.acsta.net/img/aa/9f/aa9ff537ce0c29024615907c2622e4eb.jpg", "https://fr.web.img2.acsta.net/img/e5/8e/e58e207ab8bc2ac27ba7fec7da0c3696.jpg", "https://fr.web.img6.acsta.net/img/0a/ff/0aff7a5c96e70c97623d4098cfe9e51b.jpg", "https://fr.web.img4.acsta.net/img/83/73/837380da5f0906bbc4ddd94b380822c0.jpg", "https://fr.web.img3.acsta.net/img/65/3e/653e66af639a0e783b18aecde51ff7f3.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/3f/ed/3feda78092e00ae808ac3b1459d7ce6d.jpg", "https://fr.web.img6.acsta.net/img/73/6c/736ca7cbb7149dc50fab40d89a4ede0b.jpg", "https://fr.web.img3.acsta.net/img/ba/b3/bab3e1215a3162567806058a4eca3366.jpg", "https://fr.web.img4.acsta.net/img/5c/f2/5cf297231feedcba95dbd750f3ff4a1b.jpg", "https://fr.web.img2.acsta.net/img/03/93/039383dd4d79a0cf1b6421d72fc5dcac.jpg", "https://fr.web.img6.acsta.net/img/6e/26/6e26cc82c87547ef1fe525c274e8207e.jpg", "https://fr.web.img5.acsta.net/img/dd/f6/ddf6b584fe3892e8614a3269a11fc5fd.jpg", "https://fr.web.img2.acsta.net/img/15/58/155880bca2d2f451afe6ebd37a5d0d5c.jpg", "https://fr.web.img3.acsta.net/img/12/7b/127bb7b1851154fe0647d7938a458454.jpg", "https://fr.web.img4.acsta.net/img/99/5f/995f1c3e1f3def1dbcedf39fc1b8ed1a.jpg", "https://fr.web.img4.acsta.net/img/fe/24/fe24cc8065bca7c905b4f6cd3df92823.jpg", "https://fr.web.img6.acsta.net/img/52/9c/529c6800b388fd6a3ee7921fa5c21abd.jpg", "https://fr.web.img4.acsta.net/img/88/a2/88a2c61b5b5e54483f284b6afeb02ccd.jpg", "https://fr.web.img6.acsta.net/img/66/c7/66c7424d9f2d1f307daf13f3a70de290.jpg"]</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Le mage du Kremlin</t>
+          <t>Maigret et le mort amoureux</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivier Assayas</t>
+          <t>Pascal Bonitzer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/27/26/27264fbe0076f4db99b28acfa0e21ac5.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/59/d8/59d850a90c94bb8ebbbb22fbff9d4970.jpg</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Russie, dans les années 1990. L’URSS s’effondre. Dans le tumulte d’un pays en reconstruction, un jeune homme à l’intelligence redoutable, Vadim Baranov, trace sa voie. D’abord artiste puis producteur de télé-réalité, il devient le conseiller officieux d’un ancien agent du KGB promis à un pouvoir absolu, le futur « Tsar » Vladimir Poutine. Plongé au cœur du système, Baranov devient un rouage central de la nouvelle Russie, façonnant les discours, les images, les perceptions. Mais une présence échappe à son contrôle : Ksenia, femme libre et insaisissable, incarne une échappée possible, loin des logiques d’influence et de domination. Quinze ans plus tard, après s’être retiré dans le silence, Baranov accepte de parler. Ce qu’il révèle alors brouille les frontières entre réalité et fiction, conviction et stratégie. Le Mage du Kremlin est une plongée dans les arcanes du pouvoir, un récit où chaque mot dissimule une faille.</t>
+          <t>Le commissaire Maigret est appelé en urgence au Quai d’Orsay. Monsieur Berthier-Lagès, ancien ambassadeur renommé, a été assassiné. Maigret découvre qu’il entretenait depuis cinquante ans une correspondance amoureuse avec la princesse de Vuynes, dont le mari, étrange coïncidence, vient de décéder. En se confrontant aux membres des deux familles et au mutisme suspect de la domestique du diplomate, Maigret va aller de surprise en surprise...</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Thriller</t>
+          <t>Policier</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>France, United States of America, United Kingdom</t>
+          <t>France, Belgium</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Paul Dano, Jude Law, Alicia Vikander, Tom Sturridge, Will Keen, Jeffrey Wright, Andris Keišs, Magne-Håvard Brekke</t>
+          <t>Denis Podalydès, Olivier Rabourdin, Micha Lescot, Laurent Poitrenaux, Irène Jacob, Manuel Guillot, Anne Alvaro, Julia Faure</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M14DI1qeXM8</t>
+          <t>https://www.youtube.com/watch?v=G-_jyFNqjiY</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000005026.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325655.html</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/29/4c/294c8fa12ac7e3930bca5c716a63a0f5.jpg", "https://fr.web.img5.acsta.net/img/e1/92/e1920a60aa6ee9290fc41bc6f15bb79d.jpg", "https://fr.web.img6.acsta.net/img/46/ae/46aea80f14f96ea297a83b899f570449.jpg", "https://fr.web.img3.acsta.net/img/92/8e/928e332e5da006270382516c3782a9d2.jpg", "https://fr.web.img6.acsta.net/img/a9/61/a9617f337638540cbd0e9dd3a7f89fab.JPG", "https://fr.web.img6.acsta.net/img/2e/f7/2ef712f51779e0ff419c6a0db501e5c4.jpg", "https://fr.web.img4.acsta.net/img/4b/de/4bde2f077a644e4d421af6db418cb9e1.jpg", "https://fr.web.img3.acsta.net/img/c7/5f/c75fb2423730c53d9d2b5dfdcc972802.jpg", "https://fr.web.img3.acsta.net/img/26/de/26de415570776b334e7f6955ae682f6c.jpg", "https://fr.web.img6.acsta.net/img/09/61/0961c8b58b6254e6b50ee5835cdd2e78.jpg", "https://fr.web.img2.acsta.net/img/e8/8a/e88a07db6b466338894b271fc9685194.jpg", "https://fr.web.img4.acsta.net/img/62/06/6206da95f59ae93b7530c5384090c899.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/4c/4d/4c4dc3d77c2856f1326750e92055846b.jpg", "https://fr.web.img6.acsta.net/img/60/8a/608a37aacde1ea9c31e956ac83572fe0.jpg", "https://fr.web.img4.acsta.net/img/3e/0a/3e0aae1da4936eac025c4c097c0b2422.jpg", "https://fr.web.img6.acsta.net/img/e1/6e/e16e92bc9774d5ec304ae243afece809.jpg", "https://fr.web.img6.acsta.net/img/de/68/de688f3fa92fda9440f9423a8688cbe3.jpg", "https://fr.web.img2.acsta.net/img/33/5b/335b2eef6f1ae0101537081120fedf33.jpg", "https://fr.web.img2.acsta.net/img/68/56/6856f89d96ed0a1a1f56a8fc639032c1.jpg"]</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The mastermind</t>
+          <t>Les Tourouges et les Toubleus</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kelly Reichardt</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Samantha Cutler, Daniel Snaddon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SCOL Liste</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/9b/e7/9be71377d6e8e664aa6225ee84a1daf5.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/pictures/23/06/27/16/09/1673570.jpg</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Massachussetts, 1970. Père de famille en quête d'un nouveau souffle, Mooney décide de se reconvertir dans le trafic d'œuvres d'art. Avec deux complices, il s'introduit dans un musée et dérobe des tableaux. Mais la réalité le rattrape : écouler les œuvres s’avère compliqué. Traqué, Mooney entame alors une cavale sans retour.</t>
+          <t>Un programme de quatre courts métrages haut en couleur pour triompher des différences !Les Tourouges et les Toubleus de Samantha Cutler et Daniel Snaddon • 2022 • 26mn • Grande Bretagne • Animation 3DSur une lointaine planète vivaient Édouard et Jeannette, un Toubleu et une Tourouge. Par un beau matin, ces deux-là tombèrent amoureux. Malheureusement pour eux, les Tourouges et les Toubleus ne se mélangent pas, et bien plus encore : ils se détestent depuis des générations...Sous les nuages de Vasilisa Tikunova • 2021 • 4 min • Russie Walter l’agneau souhaite plus que tout ressembler à un nuage. Mais le chemin qui mène à son rêve l’éloigne de son troupeau.Somni de Sonja Rohleder • 2023 • 3mn • Allemagne Le soleil se couche et les paupières se ferment. Se balançant d’une feuille à l’autre, le petit singe s’endort, basculant dans le monde des rêves, des plantes sauvages et des créatures mystérieuses et colorées.La Fiesta de Alfredo Soderguit et Alejo Schettini • 2021 • 3mn • Argentine, Colombie, Uruguay Deux petits oiseaux, l’un blanc, l’autre noir, vivent en harmonie dans le même arbre. Un jour, un groupe d’oiseaux rouges élit domicile au sommet de leur arbre... Les deux oiseaux vont tenter de se faire accepter.Par les créateurs du Gruffalo et de Superasticot, d’après le livre illustré de Julia Donaldson et Axel Scheffler.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Drame, Policier</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>38</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>United Kingdom, United States of America</t>
+          <t>Germany, United Kingdom</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Josh O'Connor, Alana Haim, Hope Davis, John Magaro, Gaby Hoffmann, Jasper Thompson, Sterling Thompson, Bill Camp</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Sally Hawkins, Bill Bailey, Ashna Rabheru, Adjoa Andoh, Daniel Ezra, Meera Syal, Rob Brydon, Raphaella Crow</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4, International Emmy Awards 2023: Prix du Meilleur programme d'animation</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ASH5vXpi3xA</t>
+          <t>https://www.youtube.com/watch?v=BT6b4zO-VSM</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012006.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317561.html</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/01/46/01461c4b5cc6ef2ee6f283f387b27230.jpg", "https://fr.web.img6.acsta.net/img/d5/6a/d56a3d76132fe08b842ec450a47996ce.jpg", "https://fr.web.img6.acsta.net/img/57/ae/57ae704079ab723424601cb09d967ca2.jpg", "https://fr.web.img5.acsta.net/img/f1/af/f1afb00d14115a94ced5b55bd7696aa3.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/pictures/23/06/27/16/10/3295534.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/10/3281495.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/10/3265895.jpg", "https://fr.web.img2.acsta.net/pictures/23/06/27/16/10/3251856.jpg", "https://fr.web.img5.acsta.net/pictures/23/06/27/16/10/3236256.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/09/5479872.jpg"]</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2023-10-18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avatar De cendres et de feu</t>
+          <t>Coutures</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1688,66 +1708,74 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>James Cameron</t>
+          <t>Alice Winocour</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Famille - 2D</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/66/c3/66c3fe35122f2e0e86e01859a80153b7.jpg</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Après la mort de Neteyam, Jake et Neytiri affrontent leur chagrin tout en faisant face au Peuple des Cendres, une tribu Na’vi redoutable menée par le fougueux Varang, alors que le conflit sur Pandora s’intensifie et qu’une nouvelle quê morale s’amorce.</t>
+          <t>A Paris, dans le tumulte de la Fashion Week, Maxine, une réalisatrice américaine apprend une nouvelle qui va bouleverser sa vie. Elle croise alors le chemin d’Ada, une jeune mannequin sud‐soudanaise ayant quitté son pays, et Angèle, une maquilleuse française aspirant à une autre vie. Entre ces trois femmes aux horizons pourtant si différents se tisse une solidarité insoupçonnée. Sous le vernis glamour se révèle une forme de révolte silencieuse : celle de femmes qui recousent, chacune à leur manière, les fils de leur propre histoire.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Science-Fiction, Aventure, Fantastique</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>107</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>France, United States of America</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sam Worthington, Zoe Saldaña, Sigourney Weaver, Stephen Lang, Oona Chaplin, Jack Champion, Kate Winslet, Cliff Curtis</t>
+          <t>Angelina Jolie, Ella Rumpf, Anyier Anei, Louis Garrel, Garance Marillier, Vincent Lindon, Finnegan Oldfield, Sean Gullette</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Zegl3vxOPjM</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=UsUDEFfZiys</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000015619.html</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img6.acsta.net/img/38/0c/380ce7989a2c199ce7cee4765a58e93f.jpg", "https://fr.web.img4.acsta.net/img/6d/c7/6dc704d0821db6a38029b12f5cbf3801.jpg", "https://fr.web.img4.acsta.net/img/e2/05/e205108590799a901dd70d85f084b3a0.jpg", "https://fr.web.img3.acsta.net/img/67/90/6790c53e743597cc1816ffd26ab7d2f5.jpg", "https://fr.web.img2.acsta.net/img/bb/cc/bbcc4f05a05fd27bc0077fe6ed46b545.jpg", "https://fr.web.img4.acsta.net/img/10/c0/10c0566d711c8cfc5718381bfc384e3e.jpg", "https://fr.web.img6.acsta.net/img/82/50/825020e892f8ffd453c1375dc83187fb.jpg", "https://fr.web.img2.acsta.net/img/46/d4/46d4fb614854a9ba8365ebaa1ecf5fcd.jpg", "https://fr.web.img6.acsta.net/img/6a/6a/6a6a0371af4c1430a61630bd86961ccc.jpg"]</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1757,97 +1785,81 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>En garde</t>
+          <t>Pédale rurale</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nelicia Low</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Grand Prix du Jury La Roche sur Yon - Meilleur réalisation Karlovy Vary</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Antine Vasquez</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>DOC Découverte</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/47/c1/47c1b14d006b27555c7ef261736328c2.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/82/5e/825eb2b7151adae83555d489e46dd35b.jpg</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Jie, un jeune talent prometteur de l’escrime, renoue avec son frère aîné Han, récemment libéré après sept ans de prison pour la mort accidentelle d’un adversaire lors d’une compétition. En secret, Han soutient Jie dans son entraînement, l’aidant à viser une qualification aux championnats nationaux. Mais une dispute éclate, et Jie commence à douter de l’innocence de son frère.</t>
+          <t>Benoît vit en Dordogne, à quelques kilomètres du village où il a grandi. Il a construit son paradis à l'abri des regards, s’est émancipé à sa manière, seul, dans la nature, avec ses couleurs. Il a trouvé ses manières de résister, de s’affranchir des stigmates du passé pour continuer à habiter le territoire de son enfance. Sur le chemin qu’il est parvenu à ouvrir, il reste des ronces qui continuent à le blesser. Alors ensemble on avance, on défriche parce que nos histoires résonnent, parce qu’on s’est trouvé. Et puis, avec les autres queers du coin on décide d’organiser une Pride, parce qu’il est temps de sortir du bois, de prendre l’espace qu’on n’a jamais eu, pour se célébrer, se réparer et enfin ouvrir une voie.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Singapore, Taiwan, Poland</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>劉修甫, 曹佑寧, 丁寧, Rosen Tsai, 林子恆, 曾向镇, 謝以樂, 楊文文</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Grand Prix du Jury La Roche sur Yon - Meilleur réalisation Karlovy Vary</t>
-        </is>
-      </c>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FQgcG7I2aho</t>
+          <t>https://vimeo.com/1012828750</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=307013.html</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img5.acsta.net/img/1d/5e/1d5ed38ccb2c6e3caf0b7bfed8c53f9d.jpg", "https://fr.web.img6.acsta.net/img/1e/e5/1ee5361e85068cd0e11e1b154f96a940.jpg"]</t>
-        </is>
-      </c>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023077.html</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1857,7 +1869,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Le gâteau du président</t>
+          <t>Little trouble girls</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1865,363 +1877,375 @@
           <t>VO</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CM2</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hasan Hadi</t>
+          <t>Urška Djukić</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/e6/19/e6195fdd0bbba065280ae124d28ea94b.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/96/f6/96f64541b789c2a43df6ede012b98c59.jpg</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Dans l’Irak de Saddam Hussein, Lamia, 9 ans, se voit confier la lourde tâche de confectionner un gâteau pour célébrer l’anniversaire du président. Sa quête d’ingrédients, accompagnée de son ami Saeed, bouleverse son quotidien.</t>
+          <t>Lucia, une jeune fille introvertie, rejoint la chorale de son école et se lie d’amitié avec Ana-Maria, populaire et séduisante. Confrontée à un environnement inconnu et à l’éveil de sa sexualité, Lucia commence à remettre en question ses croyances, perturbant l’harmonie du chœur.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Comédie dramatique</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>90</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Croatia, Slovenia, Serbia, Italy</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Banin Ahmad Nayef, Sajad Mohamad Qasem, Waheed Thabet Khreibat, Rahim AlHaj, Muthanna Malaghi, Ahmad Qasem Saywan, Thaer Salem, Fatima Abouharoon</t>
+          <t>Jara Sofija Ostan, Mina Švajger, Saša Tabaković, Nataša Burger, Staša Popovič, Mateja Strle, Saša Pavček, Matia Casson</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8i3idbVnC6I</t>
+          <t>https://www.youtube.com/watch?v=Rm9m7u-NsN4</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023006.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317577.html</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/e6/d0/e6d0d27f1ee4074bcb15c1798450bcf5.jpg", "https://fr.web.img2.acsta.net/img/01/07/010737a7656331d34031a3f11edcca0f.jpg", "https://fr.web.img5.acsta.net/img/b8/80/b880b190c52ee73455579a566f41027a.jpg", "https://fr.web.img2.acsta.net/img/b4/0f/b40f6bacb2fa739c18dd4ecdca6077e0.jpg", "https://fr.web.img5.acsta.net/img/11/69/1169a9082f16d9eff6019ffb541ca320.jpg", "https://fr.web.img3.acsta.net/img/06/c0/06c091be44fae3533e737cd30061e946.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/da/f4/daf4bd80fababe2574f48d7370ece43e.jpg", "https://fr.web.img3.acsta.net/img/91/89/91893ef8d9c7d9e2f7227d74c7216b43.jpg", "https://fr.web.img3.acsta.net/img/26/8b/268b7f9aed09a21bb960d0d7150ddeb2.jpg", "https://fr.web.img4.acsta.net/img/42/a6/42a689bc3a96edb020c7da2b3b2d97e2.jpg", "https://fr.web.img2.acsta.net/img/0f/4b/0f4b473b8012df29d0a2c22c5b6c48ec.jpg"]</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Les toutes petites créatures 2</t>
+          <t>Marty Supreme</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lucy Izzard</t>
+          <t>Josh Safdie</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Golden Globe meilleur acteur</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tarif Unique 3 €</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/70/e4/70e4bca25a2fa64e3574bcb887805ffe.jpg</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/7d/cb/7dcb8416ab4e8fd4ff6eeaed758c6004.jpg</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Marty Mauser, un jeune homme à l’ambition démesurée, est prêt à tout pour réaliser son rêve et prouver au monde entier que rien ne lui est impossible.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Drame, Biopic</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A'zion, Kevin O'Leary, Tyler, The Creator, Fran Drescher, Abel Ferrara, Emory Cohen</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s9gSuKaKcqM</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000037794.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007317.html</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/20/9f/209f6648709f5ac9ac1b24d0b7300e8b.jpg", "https://fr.web.img6.acsta.net/img/e9/8d/e98d3ea0f91318eae342f1679376a5f5.jpg", "https://fr.web.img4.acsta.net/img/25/42/2542406b179eaa94973416ee53983824.jpg", "https://fr.web.img2.acsta.net/img/b4/be/b4bee561b2baf9b5ce48442ab59426f0.jpg", "https://fr.web.img6.acsta.net/img/95/4f/954f8835a08c41b04a5c95b7651eb3ef.jpg", "https://fr.web.img4.acsta.net/img/51/08/5108a7f9bd7a372c10b97486344b08c4.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/c3/09/c309b5855c7b236945b1013c62676a5c.jpg", "https://fr.web.img5.acsta.net/img/29/b5/29b53a920df12d99a5314b789f1faf9c.jpg", "https://fr.web.img4.acsta.net/img/0d/7d/0d7dfee552b2aa4423aaf0e26885eb9d.jpg", "https://fr.web.img4.acsta.net/img/91/b0/91b02b31e4cf6df8f526d920ed5d1bbb.jpg", "https://fr.web.img5.acsta.net/img/09/80/09801189159bd682629326396f00f1b1.jpg", "https://fr.web.img6.acsta.net/img/cd/df/cddf292cfd1032909df0ccf6057bb151.jpg", "https://fr.web.img6.acsta.net/img/04/e1/04e1efb1f485ab6aa99c0c9ddf05ae28.jpg", "https://fr.web.img6.acsta.net/img/f2/86/f28623015549bbd278d0c162203d0e9d.jpg", "https://fr.web.img5.acsta.net/img/fa/ff/faffe9d8707cbb03040bae34d8bed952.jpg", "https://fr.web.img3.acsta.net/img/a3/04/a30488d5862e30c8597eddcee3f3c426.jpg", "https://fr.web.img6.acsta.net/img/b2/ae/b2ae37eae4f102a5427889137ea062be.jpg", "https://fr.web.img6.acsta.net/img/a1/88/a188dbf927027d760a1034d3cafb2dde.jpg", "https://fr.web.img4.acsta.net/img/f8/05/f8059864a9d229cab3d664173280ca83.jpg", "https://fr.web.img3.acsta.net/img/29/80/298098488caa5271b37f7b8207cc6f83.jpg", "https://fr.web.img6.acsta.net/img/63/88/63888a193780eeb0574c836513e5c75c.jpg"]</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nuages flottants</t>
+          <t>Esprit(s) rebelle(s)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mikio Naruse</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Natalia Chernysheva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>TU 3 €</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Ciné Patrimoine du samedi 18h</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
-        </is>
-      </c>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/1a/71/1a7161c2d9b100af2aaa05b060e14945.jpg</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Après la défaite japonaise, Yukiko, dactylographe sans le sou, retourne à Tokyo dans l’espoir de renouer avec Tomioka, un homme marié avec qui elle a vécu une intense histoire d’amour en Indochine durant la Seconde Guerre mondiale. Mais si leurs retrouvailles ravivent les braises de cette ancienne passion qui les hante, le sombre et indécis Tomioka ne semble pas partager les espoirs de Yukiko. Luttant pour survivre dans une société dévastée, la jeune femme emploiera toutes ses forces à le reconquérir...</t>
+          <t>Ex-membre des marines, Louanne Johnson accepte d'enseigner à la East Palo Alto Highschool, un établissement à la réputation sulfureuse. Réalisant que ses élèves possèdent de grandes capacités intellectuelles, elle décide de se battre pour les aider à apprendre.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Drame, Romance</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>高峰秀子, 森雅之, Mariko Okada, 山形勲, 中北千枝子, Daisuke Katō, 千石規子, 木匠マユリ</t>
+          <t>Michelle Pfeiffer, George Dzundza, Courtney B. Vance, Robin Bartlett, Beatrice Winde, John Neville, Lorraine Toussaint, Renoly Santiago</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1984-01-25</t>
+          <t>1996-02-07</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=26e44cJ1G5Y</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1930.html</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img5.acsta.net/img/30/4e/304ec21c6636d0f0368e3cf0b959f6bc.jpg", "https://fr.web.img6.acsta.net/img/cb/37/cb37f6c5895a53951c3c065005ce05f2.jpg", "https://fr.web.img6.acsta.net/img/27/20/2720359df0f6172141b00af19d329b71.jpg"]</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/watch?v=gA-5nLQCmW8</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1984-01-25</t>
+          <t>1996-02-07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palestine 36</t>
+          <t>Une balle dans la tête</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Annemarie Jacir</t>
+          <t>John Woo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Grand Prix Tokyo - Meilleur film Milan</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>ADH 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ciné Patrimoine du samedi 18h</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/37/0c/370c9b5f7f8502fb80051e5e9920fe9b.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/8b/f4/8bf4588571b3ca5edd40c475993bc21b.jpg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Palestine, 1936. La grande révolte arabe, destinée à faire émerger un État indépendant, se prépare alors que le territoire est sous mandat britannique.</t>
+          <t>Hong Kong 1967. Tandis que les manifestations pro-communistes secouent la colonie britannique, trois amis, Ben, Frank et Paul tentent de subsister malgré leur condition sociale précaire. Devenu assassin malgré-lui le jour même de son mariage, Ben se voit contraint de fuir au Vietnam, accompagné de ses deux camarades. Projetés dans la guerre qui fait rage, les 3 jeunes hommes vont subir les pires revers et humiliations, jusqu’à ce que leur amitié explose...</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Drame, Action, Thriller</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>136</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Palestinian Territory, United Kingdom, France, Denmark, Qatar</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>كريم داود عناية, Yasmine Al Massri, Billy Howle, Dhafer L'Abidine, Ward Helou, Robert Aramayo, Yafa Bakri, Wardi Eilabouni</t>
+          <t>Tony Leung Chiu-Wai, 張學友, Waise Lee Chi-Hung, Simon Yam, 袁潔瑩, 甄楚倩, 林聰, 鮑起靜</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Grand Prix Tokyo - Meilleur film Milan</t>
+          <t>ADH 4 € - Autres 5 €</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>1993-08-04</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7azScdJHB_A</t>
+          <t>https://www.youtube.com/watch?v=NIACrhExQgM</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000022541.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=8190.html</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/32/c9/32c950d9134bd15520ba8979e8dd1e83.jpg", "https://fr.web.img5.acsta.net/img/9e/9b/9e9ba1c64e61b67287fedecbb0fc951d.jpg", "https://fr.web.img6.acsta.net/img/87/86/8786dbb2eb68ac00ab806e70114a63c1.jpg", "https://fr.web.img5.acsta.net/img/51/76/5176ce9562ceda7efd0ed448ea705d08.jpg", "https://fr.web.img6.acsta.net/img/72/33/72333e39f472f5d3aa5f1bfef49f8d59.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/medias/nmedia/18/35/56/43/18407018.jpg"]</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>1993-08-04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Le chant des forêts</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2232,92 +2256,84 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vincent Munier</t>
+          <t>Anthony Marciano</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Documentaire Famille</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Tarif Unique 4,50 €</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/f5/52/f5523e15c97af96169bdc93479553602.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Après La Panthère des neiges, Vincent Munier nous invite au coeur des forêts des Vosges. C’est ici qu’il a tout appris grâce à son père Michel, naturaliste, ayant passé sa vie à l’affut dans les bois. Il est l’heure pour eux de transmettre ce savoir à Simon, le fils de Vincent. Trois regards, trois générations, une même fascination pour la vie sauvage. Nous découvrirons avec eux cerfs, oiseaux rares, renards et lynx… et parfois, le battement d’ailes d’un animal légendaire : le Grand Tétras.</t>
+          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>121</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>France, Canada</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vincent Munier, Michel Munier, Simon Munier</t>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Gregory Defleur, David Clark, Josh Casaubon, Etienne Guillou-Kervern, Gabriel Caballero, Momar Sakanoko</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=heoMyS_hjm8</t>
+          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=321789.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/48/79/4879231bf7df434ccefa260bf84fb18e.jpg", "https://fr.web.img2.acsta.net/img/06/47/0647937046e9709ff0b5a12f5af66696.jpg", "https://fr.web.img3.acsta.net/img/65/07/6507a80e00b779bd573a117ffb50cb59.jpg", "https://fr.web.img5.acsta.net/img/6d/64/6d641e15f7e1462ca5892078bb90c316.jpg", "https://fr.web.img5.acsta.net/img/69/b5/69b5410351d939cf5c005d68177db47c.jpg", "https://fr.web.img6.acsta.net/img/59/c4/59c4faa4bcbdbf003d6d30ecf546b632.jpg", "https://fr.web.img2.acsta.net/img/3f/d9/3fd9448d45fd39f1e5528ce6fef5de9d.jpg", "https://fr.web.img6.acsta.net/img/3d/a8/3da8c497a50cc952bb2b6da89f2095bd.jpg", "https://fr.web.img6.acsta.net/img/a5/ec/a5ecb292afd35323c0ba493853527eb1.jpg", "https://fr.web.img6.acsta.net/img/80/32/803246533fc9555b203272de850bede6.jpg", "https://fr.web.img4.acsta.net/img/5d/66/5d664316ddf74a92e69ea1f8bfb8051e.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gourou</t>
+          <t>Le chant des forêts</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2328,31 +2344,35 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yann Gozlan</t>
+          <t>Vincent Munier</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>DOC Coup de coeur</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/70/e9/70e9dfd918886ca3ea4e1088f06f659c.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/f5/52/f5523e15c97af96169bdc93479553602.jpg</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Matt est le coach en développement personnel le plus suivi de France. Dans une société en quête de sens où la réussite individuelle est devenue sacrée, il propose à ses adeptes une catharsis qui électrise les foules autant qu'elle inquiète les autorités. Sous le feu des critiques, Matt va s'engager dans une fuite en avant qui le mènera aux frontières de la folie et peut-être de la gloire...</t>
+          <t>Après La Panthère des neiges, Vincent Munier nous invite au coeur des forêts des Vosges. C’est ici qu’il a tout appris grâce à son père Michel, naturaliste, ayant passé sa vie à l’affut dans les bois. Il est l’heure pour eux de transmettre ce savoir à Simon, le fils de Vincent. Trois regards, trois générations, une même fascination pour la vie sauvage. Nous découvrirons avec eux cerfs, oiseaux rares, renards et lynx… et parfois, le battement d’ailes d’un animal légendaire : le Grand Tétras.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Thriller, Drame</t>
+          <t>Documentaire</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>93</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2362,40 +2382,44 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pierre Niney, Marion Barbeau, Anthony Bajon, Christophe Montenez, Jonathan Turnbull, Raphaëlle Simon, Tracy Gotoas, Holt McCallany</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+          <t>Vincent Munier, Michel Munier, Simon Munier</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>César 2026: César du Meilleur documentaire, César du Meilleur son</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fJPl2vIVyQo</t>
+          <t>https://www.youtube.com/watch?v=heoMyS_hjm8</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328179.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=321789.html</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/9f/1d/9f1dbd266488613c10a426a974261b8c.jpg", "https://fr.web.img4.acsta.net/img/17/c6/17c6e2af9d1f11967aaaa2f1306b540b.jpg", "https://fr.web.img6.acsta.net/img/9a/7a/9a7a22f18891b552a20f418c87e1e687.jpg", "https://fr.web.img4.acsta.net/img/8c/19/8c1949acd4d427f4b9d91909697caca2.jpg", "https://fr.web.img6.acsta.net/img/f1/57/f157ec82c7710e95087f7e892512471f.jpg", "https://fr.web.img2.acsta.net/img/3b/8c/3b8cc41306419098a3af1f0ac5e363f7.jpg", "https://fr.web.img4.acsta.net/img/cd/49/cd49a9acf07e9a8c2402d874604c8ff7.jpeg", "https://fr.web.img6.acsta.net/img/ac/6a/ac6a7407004bee6c41d905d61ec8a19c.jpg", "https://fr.web.img2.acsta.net/img/93/00/9300f8b3ff1dba6e2e53a0708e08ce5f.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/48/79/4879231bf7df434ccefa260bf84fb18e.jpg", "https://fr.web.img2.acsta.net/img/06/47/0647937046e9709ff0b5a12f5af66696.jpg", "https://fr.web.img3.acsta.net/img/65/07/6507a80e00b779bd573a117ffb50cb59.jpg", "https://fr.web.img5.acsta.net/img/6d/64/6d641e15f7e1462ca5892078bb90c316.jpg", "https://fr.web.img5.acsta.net/img/69/b5/69b5410351d939cf5c005d68177db47c.jpg", "https://fr.web.img6.acsta.net/img/59/c4/59c4faa4bcbdbf003d6d30ecf546b632.jpg", "https://fr.web.img2.acsta.net/img/3f/d9/3fd9448d45fd39f1e5528ce6fef5de9d.jpg", "https://fr.web.img6.acsta.net/img/3d/a8/3da8c497a50cc952bb2b6da89f2095bd.jpg", "https://fr.web.img6.acsta.net/img/a5/ec/a5ecb292afd35323c0ba493853527eb1.jpg", "https://fr.web.img6.acsta.net/img/80/32/803246533fc9555b203272de850bede6.jpg", "https://fr.web.img4.acsta.net/img/5d/66/5d664316ddf74a92e69ea1f8bfb8051e.jpg"]</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2405,7 +2429,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Les légendaires</t>
+          <t>Les enfants de la Résistance</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2416,7 +2440,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guillaume Ivernel</t>
+          <t>Christophe Barratier</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2425,79 +2449,83 @@
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/2f/d5/2fd599857351d16d6bfdc4f2fefeb6c3.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Les Légendaires, intrépides aventuriers, étaient les plus grands héros de leur temps. Mais suite à une terrible malédiction, les voilà redevenus... des enfants de 10 ans ! Danaël, Jadina, Gryf, Shimy et Razzia vont unir leurs pouvoirs pour vaincre le sorcier Darkhell et libérer leur planète de l’enfance éternelle…</t>
+          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Fantastique</t>
+          <t>Drame, Historique, Aventure, Famille</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Belgium, France</t>
+          <t>France, Belgium</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Roman Doduik, Esthèle Dumand, Elise Tilloloy, Thomas Sagols, Antoine Schoumsky, Damien Witecka, Arthur Raynal, Lila Lacombe</t>
+          <t>Artus, Gérard Jugnot, Pierre Deladonchamps, Julien Arruti, Oscar Boissière, Leslie Medina, Julien Pestel, Vanessa Guide</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pV1SWn1Ywh8</t>
+          <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=281028.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/10/ff/10fffdefacafe24db47b052863ddda62.jpg", "https://fr.web.img2.acsta.net/img/6f/07/6f0749c6a78b06af7232687f6896c672.jpg", "https://fr.web.img3.acsta.net/img/fe/59/fe59795cff026603ec6509286e65cae2.jpg", "https://fr.web.img6.acsta.net/img/f0/16/f016b8c3dc3203dc1f6b36353293eee8.jpg", "https://fr.web.img5.acsta.net/img/63/32/63320b85a89d275f1a5d0d9c780b500f.jpg", "https://fr.web.img5.acsta.net/img/1a/99/1a997d97ddaa1d8dab61bdccc071b3c5.jpg", "https://fr.web.img5.acsta.net/img/98/fa/98faf076534288ceb543108e73e3207d.jpg", "https://fr.web.img3.acsta.net/img/95/d0/95d0df4ac2e7cb287b1d136b1889e820.jpg", "https://fr.web.img6.acsta.net/img/83/8b/838bbdf0b368f01174af41af63eaffe4.jpg", "https://fr.web.img5.acsta.net/img/09/62/0962ef494b4d4977bafb691688c32bae.jpg", "https://fr.web.img2.acsta.net/img/ce/35/ce351996d5af1ff6e50d2998a7c7bd5d.jpg", "https://fr.web.img6.acsta.net/img/ed/7f/ed7ff9fd0290f42f9a31398fd5ab6aa7.jpg", "https://fr.web.img6.acsta.net/img/83/4a/834ac89d75abf72496de462950e27138.jpg", "https://fr.web.img5.acsta.net/img/3b/03/3b03d942d59f7242d36becaf8ef6eccf.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Soulèvements</t>
+          <t>Chers parents</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2508,136 +2536,144 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomas Lacoste</t>
+          <t>Emmanuel Patron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Documentaire</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/c3/7a/c37aa39be9f24b3762c95b0d28a7f074.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/29/3f/293f877dfb7dcb5672591cba06329a20.jpg</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Un portrait choral à 16 voix, 16 trajectoires singulières, réflexif et intime d’un mouvement de résistance intergénérationnel porté par une jeunesse qui vit et qui lutte contre l’accaparement des terres et de l’eau, les ravages industriels, la montée des totalitarismes et fait face à la répression politique. Une plongée au cœur des Soulèvements de la Terre révélant la composition inédite des forces multiples déployées un peu partout dans le pays qui expérimentent d’autres modes de vie, tissent de nouveaux liens avec le vivant, bouleversant ainsi les découpages établis du politique et du sensible en nous ouvrant au champ de tous les possibles.</t>
+          <t>Quand Alice et Vincent Gauthier convoquent en urgence leurs trois enfants, la fratrie débarque affolée craignant le pire … mais, bonne nouvelle, leurs parents ont en fait touché le Jackpot ! Le problème : ils ne comptent pas leur donner un centime.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Documentaire</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>86</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>Belgium, France</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>André Dussollier, Miou-Miou, Arnaud Ducret, Thomas Solivérès, Pauline Clément, Frédérique Tirmont, Bernard Alane</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CC5sKvkiEVw</t>
+          <t>https://www.youtube.com/watch?v=hHBRGiURnQM</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000027296.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012022.html</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/1b/9b/1b9b3ff33962144829022b709cd9ee29.jpg", "https://fr.web.img3.acsta.net/img/a8/d6/a8d605a0b6bf958ef499b1fe347caa9e.jpg", "https://fr.web.img6.acsta.net/img/b3/85/b385a9bc79a9b50b2e37726afabba547.jpg", "https://fr.web.img3.acsta.net/img/18/e8/18e87a4c19b442a9a594de55b3e42e6f.jpg", "https://fr.web.img4.acsta.net/img/9e/85/9e857d294d3501d642fbfebde5623275.jpg", "https://fr.web.img6.acsta.net/img/50/b1/50b18c73c1ab806956884548189929fa.jpg", "https://fr.web.img4.acsta.net/img/01/0b/010b514e411d69aac38a26e35f13befb.jpg", "https://fr.web.img2.acsta.net/img/5e/e0/5ee0a38037f945a584330baf7736faf4.jpg", "https://fr.web.img4.acsta.net/img/5e/92/5e924deac43ee2c8f58dc9042e799dc8.jpg", "https://fr.web.img6.acsta.net/img/d3/af/d3af16e8a3583e87ef91ddba434be514.jpg", "https://fr.web.img5.acsta.net/img/a3/22/a322fe516953faf65bbac4e0b40f7fae.jpg", "https://fr.web.img2.acsta.net/img/14/fe/14fe970670f30afc2c9aedb8c844f280.jpg", "https://fr.web.img6.acsta.net/img/83/25/8325aaf8312916c0f28c51308598b3b5.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/ca/f1/caf1ebc7acc4d5c28fec740b199c3ac5.jpg", "https://fr.web.img6.acsta.net/img/7d/4f/7d4f4464f105a1b8cddd1149eac963e1.jpg", "https://fr.web.img4.acsta.net/img/4d/88/4d88b430ffeeadd55f368e40fcb13ab9.jpg", "https://fr.web.img4.acsta.net/img/b9/31/b931cab8dbe5ad24c3d0628e07f9f6f3.jpg", "https://fr.web.img5.acsta.net/img/04/2d/042d382e1411fe7f363b4a11103eabb6.jpg", "https://fr.web.img2.acsta.net/img/6d/4e/6d4ef8abf0fc4f96c924143e2c838e7e.jpg", "https://fr.web.img3.acsta.net/img/6c/40/6c40df5dcbab1a70702d9f196a1a9cd1.jpg", "https://fr.web.img6.acsta.net/img/f9/67/f967f2b5b10d36297d2a6eb307032374.jpg", "https://fr.web.img5.acsta.net/img/ee/33/ee33247bf7021e9758af1add30d0903a.jpg"]</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Les dimanches</t>
+          <t>Les enfants de la Résistance</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alauda Ruíz de Azúa</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Christophe Barratier</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SCOL Actu</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/18/71/18717c10a7a89df2cbf10f6584181ebd.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ainara, 17 ans, élève dans un lycée catholique, s'apprête à passer son bac et à choisir son futur parcours universitaire. A la surprise générale, cette brillante jeune fille annonce à sa famille qu'elle souhaite participer à une période d’intégration dans un couvent afin d'embrasser la vie de religieuse. La nouvelle prend tout le monde au dépourvu. Si le père semble se laisser convaincre par les aspirations de sa fille, pour Maite, la tante d’Ainara, cette vocation inattendue est la manifestation d'un mal plus profond …</t>
+          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Drame, Historique, Aventure, Famille</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Spain, France</t>
+          <t>France, Belgium</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blanca Soroa, Patricia López Arnaiz, Miguel Garcés, Juan Minujín, Mabel Rivera, Nagore Aranburu, Lier Alava, Noe Chiroque</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+          <t>Artus, Gérard Jugnot, Pierre Deladonchamps, Julien Arruti, Oscar Boissière, Leslie Medina, Julien Pestel, Vanessa Guide</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>2026-02-11</t>
@@ -2645,17 +2681,17 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JTU224MnTUM</t>
+          <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020167.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/3b/cb/3bcb5b416b32e7af3938ca6da2354161.jpg", "https://fr.web.img2.acsta.net/img/4a/2c/4a2ca4fa5c7c57f798c8a62840690b53.JPG", "https://fr.web.img5.acsta.net/img/37/e3/37e39954c8a41f30f2a7a4f57f208b7e.jpg", "https://fr.web.img6.acsta.net/img/a1/e2/a1e2fafa239c82277c9666a70113eabc.jpg", "https://fr.web.img5.acsta.net/img/7d/f3/7df35d0115cf51288fa6076afe776c8f.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2667,17 +2703,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Les toutes petites créatures 2</t>
+          <t>Victor comme tout le monde</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2688,58 +2724,74 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lucy Izzard</t>
+          <t>Pascal Bonitzer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Tarif Unique 3 €</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/70/e4/70e4bca25a2fa64e3574bcb887805ffe.jpg</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/7b/ec/7bec0c5e6b6d2cf4f985353223ae133a.jpg</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Habité par Victor Hugo, le comédien Robert Zucchini traîne une douce mélancolie lorsqu'il n'est pas sur scène. Chaque soir, il remplit les salles en transmettant son amour des mots. Jusqu’au jour où réapparaît sa fille, qu’il n’a pas vue grandir… Et si aimer, pour une fois, valait mieux qu’admirer ?</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Comédie dramatique</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fabrice Luchini, Chiara Mastroianni, Louise Orry-Diquéro, Suzanne De Baecque, Marie Narbonne, Lauretta Trefeu, Iris Bry, Naidra Ayadi</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t0RrVuOml0M</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000037794.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000021956.html</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/20/9f/209f6648709f5ac9ac1b24d0b7300e8b.jpg", "https://fr.web.img6.acsta.net/img/e9/8d/e98d3ea0f91318eae342f1679376a5f5.jpg", "https://fr.web.img4.acsta.net/img/25/42/2542406b179eaa94973416ee53983824.jpg", "https://fr.web.img2.acsta.net/img/b4/be/b4bee561b2baf9b5ce48442ab59426f0.jpg", "https://fr.web.img6.acsta.net/img/95/4f/954f8835a08c41b04a5c95b7651eb3ef.jpg", "https://fr.web.img4.acsta.net/img/51/08/5108a7f9bd7a372c10b97486344b08c4.jpg"]</t>
+          <t>["https://fr.web.img3.acsta.net/img/ae/9c/ae9c941a95ecbbce7cec4a9a6b007863.jpg", "https://fr.web.img6.acsta.net/img/d7/63/d76336aeef620ee4276e61ca19c16ae9.jpg", "https://fr.web.img5.acsta.net/img/b2/65/b26508a01fde5b941dbedd03c31f92d8.jpg", "https://fr.web.img6.acsta.net/img/a1/11/a1112c0a20486aba18ff5c874a31ce07.jpg", "https://fr.web.img5.acsta.net/img/a2/45/a24509dcf0996c251a6521648eb25183.jpg", "https://fr.web.img6.acsta.net/img/d3/eb/d3eb19a79b8f3f2ddc49f16017f1094a.jpg", "https://fr.web.img4.acsta.net/img/e9/87/e987439316c89fa9fecbc48c10843d0a.jpg"]</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2749,7 +2801,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nurenberg</t>
+          <t>La gifle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2760,497 +2812,576 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>James Vanderbilt</t>
+          <t>Frédéric Hambalek</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/8b/f3/8bf3d9725705d4ef36ebe09fcb93c92f.jpg</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>En 1948, le juge Haywood est envoyé à Nuremberg pour présider le procès de quatre magistrats allemands accusés de trop de complaisance à l'égard du régime Nazi. L'un d'eux, Janning, se renferme dans un silence méprisant et, en écartant les témoignages et les films sur les camps de concentration, dit qu'il n'a fait qu'appliquer la loi en vigueur...</t>
+          <t>Julia et Tobias semblent être le couple parfait. Mais derrière les apparences, un trouble gronde. L’équilibre fragile entre les deux est brisé lorsque leur fille Marielle développe soudainement des capacités télépathiques, lui accordant le pouvoir de voir et d’entendre tout ce que ses parents font, jour et nuit.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Drame, Histoire</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>86</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spencer Tracy, Richard Widmark, Maximilian Schell, Burt Lancaster, Marlene Dietrich, Judy Garland, Montgomery Clift, William Shatner</t>
+          <t>Laeni Geiseler, Julia Jentsch, Felix Kramer, Mehmet Ateşçi, Moritz von Treuenfels, Sissy Höfferer, Victoria Mayer, Nadja Sabersky</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1961-12-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=T3taV43-lGc</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=nbe3ITNfonQ</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017164.html</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/img/4d/e0/4de04abb0de6ae7a78ee6ea947452ab4.jpg", "https://fr.web.img5.acsta.net/img/5c/82/5c82daf8abe88d5ea23412e933b4ce33.jpg", "https://fr.web.img6.acsta.net/img/53/99/5399df917873462fcafb51c07268b43d.jpg"]</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1961-12-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marsupilami JP famille</t>
+          <t>Ce qu'il reste de nous</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Philippe Lacheau</t>
+          <t>Cherien Dabis</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Séance EPHAD HANDI - Famille</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tarif Unique 5 €</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/ab/be/abbedce650d9fd1b3fe6c2defe9c3518.jpg</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>De 1948 à nos jours, trois générations d’une famille palestinienne portent les espoirs et les blessures d’un peuple. Une fresque où Histoire et intime se rencontrent.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Drame</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Germany, Cyprus, United States of America, Qatar, Saudi Arabia, Egypt, United Arab Emirates, Jordan, Kuwait</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Saleh Bakri, Cherien Dabis, Adam Bakri, Maria Zreik, Mohammad Bakri, Muhammad Abed Elrahman, Sanad Alkabareti, Salah Al Din</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=od_EKv4n3p0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016229.html</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/img/82/b7/82b77dbba1ff19a6af5101f7fca7e897.jpg", "https://fr.web.img3.acsta.net/img/88/40/8840f9da13b5c59b532851fd21c5ae09.jpg", "https://fr.web.img4.acsta.net/img/36/2d/362d347ccb59c8956dba8ebccd40706e.jpg", "https://fr.web.img2.acsta.net/img/3f/0e/3f0ebf1110ef9ed746188c3b1d427fab.jpg", "https://fr.web.img3.acsta.net/img/a5/6c/a56c1f84811272bfc647ba1b6637f2d6.jpg", "https://fr.web.img2.acsta.net/img/60/2d/602db1d598e3d59161f9688de9b5439b.jpg", "https://fr.web.img2.acsta.net/img/df/be/dfbe86dfd73724f319005c36aae16701.jpg", "https://fr.web.img6.acsta.net/img/a5/bd/a5bdc5b23848b8c4c0141a3442356f79.jpg"]</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Aucun autre choix</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Park Chan-Wook</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Anthony Marciano</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>TU 5 €</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/a4/52/a4527664f53d4cdc51dbaf628184aff1.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cadre dans une usine de papier You Man-su est un homme heureux, il aime sa femme, ses enfants, ses chiens, sa maison. Lorsqu’il est licencié, sa vie bascule, il ne supporte pas l’idée de perdre son statut social et la vie qui va avec. Pour retrouver son bonheur perdu, il n’a aucun autre choix que d’éliminer tous ses concurrents…</t>
+          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Comédie, Thriller, Drame</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>121</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>South Korea, France</t>
+          <t>France, Canada</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lee Byung-hun, Son Ye-jin, Park Hee-soon, Lee Sung-min, 염혜란, Seung-Won Cha, 김우승, 최소율</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Gregory Defleur, David Clark, Josh Casaubon, Etienne Guillou-Kervern, Gabriel Caballero, Momar Sakanoko</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>TU 5 €</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HmIjLVScTCg</t>
+          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000001960.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/f3/d4/f3d468179b397ececd43f1711bbc1a76.jpg", "https://fr.web.img6.acsta.net/img/60/57/605725c49daa9020d47c4ce10f25758a.jpg", "https://fr.web.img5.acsta.net/img/11/76/1176ff6544e51bdc85b65a25ae9f4bee.jpg", "https://fr.web.img5.acsta.net/img/34/9d/349dcb149bbeb77fab3cbdf72112b5cf.jpg", "https://fr.web.img3.acsta.net/img/1f/3a/1f3a26c88428a73486318b40a627d770.jpg", "https://fr.web.img6.acsta.net/img/16/27/162791ba5975e5bd6aeae70c26a57888.jpg", "https://fr.web.img4.acsta.net/img/36/e6/36e6055fcf5065eb0e303d5e1fb79f16.jpg", "https://fr.web.img6.acsta.net/img/20/43/2043b580d48745f6c512da8f8826b3bd.jpg", "https://fr.web.img5.acsta.net/img/98/62/986235bea13d02d81b9c69dce82abe97.jpg", "https://fr.web.img2.acsta.net/img/98/9d/989d2ca66bd7c50ea92e0687f7108618.jpg", "https://fr.web.img6.acsta.net/img/de/9f/de9f0f312b1363464f0179f405c388bb.jpg", "https://fr.web.img4.acsta.net/img/4e/ec/4eecf5368ac8628bc6f99a0c0831488b.jpg", "https://fr.web.img3.acsta.net/img/00/d8/00d81ae0aec94b670bce45db163e32af.jpg", "https://fr.web.img4.acsta.net/img/b6/22/b622dcefa6e2bc72b5d4ebb710477c8b.jpg", "https://fr.web.img5.acsta.net/img/21/ca/21cafa7467d6acbeea12fa5d317af65b.jpg", "https://fr.web.img3.acsta.net/img/0a/f6/0af620a91b2dd78a9ca9f56b066bf307.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Biscuit le chien fantastique</t>
+          <t>Un monde fragile et merveilleux</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shea Wageman</t>
+          <t>Cyril Aris</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Ciné goûter, Jeune Public</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Coup de cœur</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/7b/09/7b095f309baf4441fc5966b2f217900e.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/9e/96/9e96bec2d1ac11dba0c4a6c65454a0ef.jpg</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Danny et son petit chien Biscuit sont les meilleurs amis du monde. Un jour, une magie mystérieuse donne à Biscuit des pouvoirs incroyables : il peut désormais parler et voler. Dès que quelqu’un a besoin de lui, il met son masque, enfile sa cape et s’élance dans le ciel pour aider : il est devenu un chien fantastique ! Biscuit a désormais deux passions : manger des tacos et sauver le monde. Mais Pudding, le chat du voisin, lui aussi doté de super-pouvoirs, rêve de faire régner les chats sur l’univers. Danny et Biscuit devront prouver qu’ensemble, rien ne peut les arrêter !</t>
+          <t>Nino et Yasmina tombent amoureux dans la cour de leur école à Beyrouth, et rêvent à leur vie d’adulte, à un monde merveilleux. 20 ans plus tard, ils se retrouvent par accident et c’est à nouveau l’amour fou, magnétique, incandescent. Peut-on construire un avenir, dans un pays fracturé, qu’on tente de quitter mais qui vous retient de façon irrésistible ?</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Animation, Comédie, Famille</t>
+          <t>Drame, Romance</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>110</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Lebanon, United States of America, Germany, Greece</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Owen Wilson, Dawson Littman, Tabitha St. Germain, Sebastian Billingsley-Rodriguez, Rhona Rees, Anthony Bolognese, Caitlynne Medrek, Emily Delahunty</t>
+          <t>Mounia Akl, Hassan Akil, Camille Salameh, Julia Kassar, Tino Karam, Nadyn Chalhoub, Alex Choueiry, Valentina Hachem</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VmxXMWGaDzQ</t>
+          <t>https://www.youtube.com/watch?v=tfhS2aXatiA</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017117.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000028071.html</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/cc/bb/ccbb0018fbe560c8535c07949d408025.jpg", "https://fr.web.img3.acsta.net/img/e7/ac/e7acc11655324629f86345607eafcf23.jpg", "https://fr.web.img2.acsta.net/img/f9/7b/f97bfe76e783f57e01a872b7c763cf47.jpg", "https://fr.web.img5.acsta.net/img/7f/c6/7fc688f605e3c9f8bb6fe9058bc80942.jpg", "https://fr.web.img5.acsta.net/img/67/0e/670e08bbd5558a2b53def24b58a59715.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/06/8a/068ae35ea83f35673f3e3e3e7833c203.jpg"]</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hamnet</t>
+          <t>Jumpers</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chloé Zhao</t>
+          <t>Daniel Chong</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026</t>
+          <t>TU 4,50 €</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Ciné Jeunes du samedi 18h</t>
+          <t>Jeune Public</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
+          <t>Ciné goûter</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/9a/f5/9af5f87b39938fec50f86c32c3d31b69.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/fc/0ffc959e65d43de4e4e3a40b80123e9e.jpg</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Angleterre, 1580. Un professeur de latin fauché, fait la connaissance d’Agnes, jeune femme à l’esprit libre. Fascinés l’un par l’autre, ils entament une liaison fougueuse avant de se marier et d’avoir trois enfants. Tandis que Will tente sa chance comme dramaturge à Londres, Agnes assume seule les tâches domestiques. Lorsqu’un drame se produit, le couple, autrefois profondément uni, vacille. Mais c’est de leur épreuve commune que naîtra l’inspiration d’un chef d’œuvre universel.</t>
+          <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Animation, Aventure, Comédie</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>United Kingdom, United States of America</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jessie Buckley, Paul Mescal, Emily Watson, Joe Alwyn, Jacobi Jupe, Noah Jupe, Bodhi Rae Breathnach, Olivia Lynes</t>
+          <t>Piper Curda, Bobby Moynihan, Jon Hamm, Kathy Najimy, Dave Franco, Eduardo Franco, Aparna Nancherla, Sam Richardson</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Meilleure film dramatique et meilleure actrice Golden Globes 2026, Golden Globes 2026: Meilleur film dramatique, Meilleure actrice dans un drame</t>
+          <t>TU 4, 50 €</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYcgQMxQwmk</t>
+          <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=315003.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/db/27/db27c1195bfb8835aef4671ac165e436.jpg", "https://fr.web.img3.acsta.net/img/ea/c4/eac4203c2df8347475f77ec8ce61d7ca.jpg", "https://fr.web.img6.acsta.net/img/7e/b8/7eb8bf6fa577347479dfd6347f103afb.jpg", "https://fr.web.img4.acsta.net/img/b0/3d/b03d7554c97c3f7ba8c880de57c35b31.jpg", "https://fr.web.img2.acsta.net/img/e0/f2/e0f2b4497faaf505ab30ecd733f2a531.jpg", "https://fr.web.img6.acsta.net/img/9a/fd/9afde980a6402b830c5007cc66e72aff.jpg", "https://fr.web.img5.acsta.net/img/ce/fe/cefe5da862eb8228d3bf79a068a9844a.jpg", "https://fr.web.img4.acsta.net/img/c0/41/c041a05c78908f57f777fb269f515979.jpg", "https://fr.web.img3.acsta.net/img/fd/f9/fdf917bfcee844d0fbd3ac41bba90997.jpg", "https://fr.web.img5.acsta.net/img/dc/88/dc886647f0301e242fd931547cd4d10e.jpg", "https://fr.web.img2.acsta.net/img/fc/d8/fcd8803be480fc3fd79f80b56597c9ba.jpg", "https://fr.web.img2.acsta.net/img/f1/de/f1deaf59daf5e4773c85bcf1702633d7.jpg", "https://fr.web.img2.acsta.net/img/5f/dc/5fdc64d7259e00568cfd5ab9344356b1.jpg", "https://fr.web.img3.acsta.net/img/19/5f/195f3ffc57720410317e2fb3d51ae61f.jpg", "https://fr.web.img2.acsta.net/img/b8/76/b876bf840dab929460f48ff0dac4d321.jpg"]</t>
+          <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A pied d'œuvre</t>
+          <t>Christy</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valérie Donzelli</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>David Michôd</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ADH 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ciné Jeunes du samedi 18h</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/45/92/4592d30b6f185a47c81625b1f94820bc.jpg</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Achever un texte ne veut pas dire être publié, être publié ne veut pas dire être lu, être lu ne veut pas dire être aimé, être aimé ne veut pas dire avoir du succès, avoir du succès n'augure aucune fortune.
- À Pied d’œuvre raconte l'histoire vraie d'un photographe à succès qui abandonne tout pour se consacrer à l'écriture, et découvre la pauvreté.</t>
+          <t>Inspiré d'une histoire vraie, Christy retrace l'ascension tumultueuse de la boxeuse Christy Martin, qui est passée de l'anonymat à la célébrité. La légendaire ténacité de Christy sur le ring cache en réalité des combats plus intimes avec sa famille, son identité et une relation toxique qui pourrait bien se transformer en une question de vie ou de mort.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Biopic, Drame</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>135</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bastien Bouillon, Marie Rivière, Virginie Ledoyen, André Marcon, Pauline Clément, Arthur Dupont, Émilie Caen, Quentin Dolmaire</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+          <t>Sydney Sweeney, Ben Foster, Merritt Wever, Katy O'Brian, Ethan Embry, Jess Gabor, Chad L. Coleman, Tony Cavalero</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>ADH 4 € - Autres 5 €</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Gifr5NrMeBk</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+          <t>https://www.youtube.com/watch?v=hSHwFDPfeV8</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=264144.html</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img6.acsta.net/img/10/aa/10aaea641b92c8254029081fc6fef889.jpg", "https://fr.web.img5.acsta.net/img/75/29/75293252277b9d1c570bcddc2612e423.jpg", "https://fr.web.img4.acsta.net/img/a6/c4/a6c4f6e7ce0a3a867c174d8b535371ff.jpg"]</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Les légendaires</t>
+          <t>La maison des femmes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3261,88 +3392,84 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guillaume Ivernel</t>
+          <t>Melisa Godet</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/2f/d5/2fd599857351d16d6bfdc4f2fefeb6c3.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/d0/9f/d09ff1ec5ee43c6f7f17d6622d7422d0.jpg</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Les Légendaires, intrépides aventuriers, étaient les plus grands héros de leur temps. Mais suite à une terrible malédiction, les voilà redevenus... des enfants de 10 ans ! Danaël, Jadina, Gryf, Shimy et Razzia vont unir leurs pouvoirs pour vaincre le sorcier Darkhell et libérer leur planète de l’enfance éternelle…</t>
+          <t>À la Maison des femmes, entre soin, écoute et solidarité, une équipe se bat chaque jour pour accompagner les femmes victimes de violences dans leur reconstruction. Dans ce lieu unique, Diane, Manon, Inès, Awa et leurs collègues accueillent, soutiennent, redonnent confiance. Ensemble, avec leurs forces, leurs fragilités, leurs convictions et une énergie inépuisable.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Animation, Aventure, Fantastique</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>110</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Belgium, France</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Roman Doduik, Esthèle Dumand, Elise Tilloloy, Thomas Sagols, Antoine Schoumsky, Damien Witecka, Arthur Raynal, Lila Lacombe</t>
+          <t>Karin Viard, Lætitia Dosch, Oulaya Amamra, Eye Haïdara, Pierre Deladonchamps, Juliette Armanet, Laurent Stocker, Jean-Charles Clichet</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pV1SWn1Ywh8</t>
+          <t>https://www.youtube.com/watch?v=yAwvKg9T47Q</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=281028.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012019.html</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/10/ff/10fffdefacafe24db47b052863ddda62.jpg", "https://fr.web.img2.acsta.net/img/6f/07/6f0749c6a78b06af7232687f6896c672.jpg", "https://fr.web.img3.acsta.net/img/fe/59/fe59795cff026603ec6509286e65cae2.jpg", "https://fr.web.img6.acsta.net/img/f0/16/f016b8c3dc3203dc1f6b36353293eee8.jpg", "https://fr.web.img5.acsta.net/img/63/32/63320b85a89d275f1a5d0d9c780b500f.jpg", "https://fr.web.img5.acsta.net/img/1a/99/1a997d97ddaa1d8dab61bdccc071b3c5.jpg", "https://fr.web.img5.acsta.net/img/98/fa/98faf076534288ceb543108e73e3207d.jpg", "https://fr.web.img3.acsta.net/img/95/d0/95d0df4ac2e7cb287b1d136b1889e820.jpg", "https://fr.web.img6.acsta.net/img/83/8b/838bbdf0b368f01174af41af63eaffe4.jpg", "https://fr.web.img5.acsta.net/img/09/62/0962ef494b4d4977bafb691688c32bae.jpg", "https://fr.web.img2.acsta.net/img/ce/35/ce351996d5af1ff6e50d2998a7c7bd5d.jpg", "https://fr.web.img6.acsta.net/img/ed/7f/ed7ff9fd0290f42f9a31398fd5ab6aa7.jpg", "https://fr.web.img6.acsta.net/img/83/4a/834ac89d75abf72496de462950e27138.jpg", "https://fr.web.img5.acsta.net/img/3b/03/3b03d942d59f7242d36becaf8ef6eccf.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/8a/88/8a88c2c86ed3698d1270a8e6f9fe393f.jpg", "https://fr.web.img5.acsta.net/img/0c/56/0c562bc4f318b3f6e87106caebada448.jpg", "https://fr.web.img6.acsta.net/img/4c/a6/4ca6651f4ffa090ac1ed0eb106059907.jpg", "https://fr.web.img5.acsta.net/img/d7/30/d7301415402762258a105d82a9c85c36.jpg", "https://fr.web.img6.acsta.net/img/82/1f/821fe7e03b70d805fd2a3ed6134b21c8.jpg", "https://fr.web.img2.acsta.net/img/c0/90/c090b4bec0837ebba7db0715d4cb11d6.jpg", "https://fr.web.img6.acsta.net/img/4c/69/4c69440f7cc977c3d0bd540e78d94da5.jpg", "https://fr.web.img4.acsta.net/img/80/d4/80d413965459d750fb2aa12f9fac9fd8.jpg", "https://fr.web.img5.acsta.net/img/f0/ae/f0aeafe6cde0b7d886d5ee466d139e39.jpg", "https://fr.web.img2.acsta.net/img/d8/be/d8becce5aeae185ef4b960ad7e8e2122.jpg", "https://fr.web.img6.acsta.net/img/80/17/801724aa27a843655c6382d36f6460c0.jpg", "https://fr.web.img4.acsta.net/img/66/ec/66ecb665598ef7bcafb61a2c356d22ab.jpg", "https://fr.web.img3.acsta.net/img/d9/99/d9995326016481320d40ce58a9362975.jpg", "https://fr.web.img3.acsta.net/img/2c/5f/2c5f82fc07e4a26f372da2d9abeb0776.jpg", "https://fr.web.img5.acsta.net/img/06/5e/065e2f738f2a2e12ea3d34c2ed30bb7c.jpg", "https://fr.web.img2.acsta.net/img/1b/9b/1b9b663d4879a9a924b1844ebee9185a.jpg", "https://fr.web.img4.acsta.net/img/ab/9b/ab9b7b6ed610c4f1345909ca45a3f7a5.jpg"]</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Promis le ciel</t>
+          <t>Allah n'est pas obligé</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3353,88 +3480,96 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erige Sehiri</t>
+          <t>Zaven Najjar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Famille  à partir de 9/10 ans</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>a partir de 12 ans</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/72/ba/72baef9032ae95ac8cf9be07f0cde8fe.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/41/c8/41c82c9f0ee7745eaa2220a0185ed6f2.jpg</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Marie, pasteure ivoirienne et ancienne journaliste, vit à Tunis. Elle héberge Naney, une jeune mère en quête d'un avenir meilleur, et Jolie, une étudiante déterminée qui porte les espoirs de sa famille restée au pays. Quand les trois femmes recueillent Kenza, 4 ans, rescapée d'un naufrage, leur refuge se transforme en famille recomposée tendre mais intranquille dans un climat social de plus en plus préoccupant.</t>
+          <t>Birahima, orphelin guinéen d’une dizaine d’années, doit quitter son village pour tenter de passer la frontière et retrouver une tante qui se serait installée au Libéria. Le jeune garçon se met dans les pas de Yacouba, bonimenteur de grands chemins jouant les guides de substitution. Mais sur la route, la rencontre avec des enfants soldats fait basculer le destin de Birahima. Engagé involontaire, que lui réserve le sentier de la guerre ?</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Animation, Drame</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>France, Tunisia, Egypt</t>
+          <t>France, Luxembourg, Canada, Belgium</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Aïssa Maïga, Laëtitia Ky, Déborah Naney, Mohamed Grayaâ, Foued Zaazaa, Estelle Dogbo, Touré Blamassi, Sophie Tankou</t>
+          <t>Chris Aboubacar Hanta Traoré / SK 07, Thomas Ngijol, Marc Zinga, Annabelle Lengronne</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9F-U2tndiUo</t>
+          <t>https://www.youtube.com/watch?v=K6gJ-fYqSlg</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006454.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=290253.html</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/14/9f/149f6fcc8a302c7ea298d331efa5620d.jpg", "https://fr.web.img3.acsta.net/img/78/f1/78f16e1dbafb42446322d41ce4a2fca6.jpg", "https://fr.web.img2.acsta.net/img/29/eb/29eba2f15c17c7b55739027b37be608d.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/2a/b0/2ab0dab69af2a3c63249e73dcd262867.jpg", "https://fr.web.img6.acsta.net/img/37/9a/379af02758660dd03f2426336e9ffdd9.jpg", "https://fr.web.img6.acsta.net/img/4a/44/4a44551c5d1f14c7c57339e469f6ccef.jpg", "https://fr.web.img4.acsta.net/img/31/ae/31ae353cea358ff3226ae772c97f95d5.jpg", "https://fr.web.img6.acsta.net/img/0a/36/0a367f14f4ffd873a5574667b9916736.jpg", "https://fr.web.img2.acsta.net/img/3b/0a/3b0a0e1de296b4b8dcaecbb146b3175d.jpg", "https://fr.web.img5.acsta.net/img/2d/35/2d35cb1eea9e4ef6f1322712b609a408.jpg", "https://fr.web.img6.acsta.net/img/96/76/967684c550c39eaae2241e3bed3201ff.jpg", "https://fr.web.img4.acsta.net/img/e3/54/e35484ccc63b23d91a9c0b3a07428ea8.jpg"]</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gourou</t>
+          <t>La guerre des prix</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3445,7 +3580,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yann Gozlan</t>
+          <t>Anthony Dechaux</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3454,22 +3589,22 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/70/e9/70e9dfd918886ca3ea4e1088f06f659c.jpg</t>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/82/9e/829ecf49faaf8f4534f045054c096d9d.jpg</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Matt est le coach en développement personnel le plus suivi de France. Dans une société en quête de sens où la réussite individuelle est devenue sacrée, il propose à ses adeptes une catharsis qui électrise les foules autant qu'elle inquiète les autorités. Sous le feu des critiques, Matt va s'engager dans une fuite en avant qui le mènera aux frontières de la folie et peut-être de la gloire...</t>
+          <t>Audrey, fille d’agriculteurs et cheffe de rayon dans un hypermarché en province, se voit propulsée à la centrale d’achat de son enseigne afin d'y défendre la filière bio et locale. Alors qu’elle fait équipe avec un négociateur aux méthodes redoutables, Audrey va devoir se battre pour faire exister ses convictions au sein d'un système impitoyable.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Thriller, Drame</t>
+          <t>Thriller</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3479,40 +3614,40 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pierre Niney, Marion Barbeau, Anthony Bajon, Christophe Montenez, Jonathan Turnbull, Raphaëlle Simon, Tracy Gotoas, Holt McCallany</t>
+          <t>Olivier Gourmet, Ana Girardot, Julien Frison, Jonas Bloquet, Camille Moutawakil, Catherine Vinatier, Camille Sansterre, Grégoire Monsaingeon</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fJPl2vIVyQo</t>
+          <t>https://www.youtube.com/watch?v=rR9WFbLhwzU</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=328179.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016305.html</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>["https://fr.web.img3.acsta.net/img/9f/1d/9f1dbd266488613c10a426a974261b8c.jpg", "https://fr.web.img4.acsta.net/img/17/c6/17c6e2af9d1f11967aaaa2f1306b540b.jpg", "https://fr.web.img6.acsta.net/img/9a/7a/9a7a22f18891b552a20f418c87e1e687.jpg", "https://fr.web.img4.acsta.net/img/8c/19/8c1949acd4d427f4b9d91909697caca2.jpg", "https://fr.web.img6.acsta.net/img/f1/57/f157ec82c7710e95087f7e892512471f.jpg", "https://fr.web.img2.acsta.net/img/3b/8c/3b8cc41306419098a3af1f0ac5e363f7.jpg", "https://fr.web.img4.acsta.net/img/cd/49/cd49a9acf07e9a8c2402d874604c8ff7.jpeg", "https://fr.web.img6.acsta.net/img/ac/6a/ac6a7407004bee6c41d905d61ec8a19c.jpg", "https://fr.web.img2.acsta.net/img/93/00/9300f8b3ff1dba6e2e53a0708e08ce5f.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/dd/4f/dd4fb9a2ec6c8efa39013f9d3eb8ec2c.jpg", "https://fr.web.img4.acsta.net/img/39/3a/393aae3289b4d53573b12a823953eaac.jpg", "https://fr.web.img4.acsta.net/img/75/eb/75eb5c8bef9955420f1ebf3eedc82df2.jpg", "https://fr.web.img4.acsta.net/img/8e/87/8e87b307c382d490c74c3c79f610faa2.jpg", "https://fr.web.img5.acsta.net/img/f0/6c/f06cf1035e85143198560d0dcad38928.jpg", "https://fr.web.img5.acsta.net/img/db/55/db5584a05d9b2d2aab28aa57a964c325.jpg", "https://fr.web.img5.acsta.net/img/54/f4/54f43ff75322bf10ba5436836a31a14d.jpg", "https://fr.web.img4.acsta.net/img/a4/9f/a49f5f02a8156d22c91c28d14c9a2d3f.jpg"]</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3522,199 +3657,183 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Les voyages de Tereza</t>
+          <t>Alter ego</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gabriel Mascaro</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Cinélatino</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Coup de cœur</t>
-        </is>
-      </c>
+          <t>Nicolas Charlet, Bruno Lavaine</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/a8/b9/a8b9fa641e4b57390f85e1efe2a0d0b0.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/a3/21/a3212f7a3bc901b69704c09de6e30093.jpg</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Tereza a vécu toute sa vie dans une petite ville industrielle d’Amazonie. Le jour venu, elle reçoit l'ordre officiel du gouvernement de s’installer dans une colonie isolée pour personnes âgées, où elles sont amenées à « profiter » de leurs dernières années. Tereza refuse ce destin imposé et décide de partir seule à l'aventure, découvrir son pays et accomplir son rêve secret…</t>
+          <t>Alex a un problème : son nouveau voisin est son sosie parfait. Avec des cheveux. Un double en mieux, qui va totalement bouleverser son existence.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Science Fiction, Drame</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Brazil, Mexico, Chile, Netherlands</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Denise Weinberg, Rodrigo Santoro, Miriam Socarrás, Adanilo, Rosa Malagueta, Clarissa Pinheiro, Dimas Mendonça, Daniel Ferrat</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Cinélatino, Berlinale 2025: Grand Prix du jury (Ours d'Argent)</t>
-        </is>
-      </c>
+          <t>Laurent Lafitte, Olga Kurylenko, Blanche Gardin, Valérie Donzelli, Monsieur Fraize, Zabou Breitman, Bertrand Goncalves</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nFQEUuodCQ0</t>
+          <t>https://www.youtube.com/watch?v=ObYzfs8ITaE</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000018687.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=288260.html</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/07/04/070497f251d896cda1f60520a6d0fc54.jpg", "https://fr.web.img4.acsta.net/img/57/d3/57d3438239174ee61a0deb88160b00ea.jpg", "https://fr.web.img3.acsta.net/img/42/5d/425de28d088602fdd78202c4aab16839.jpg", "https://fr.web.img3.acsta.net/img/9d/ff/9dfffe21a51747bac25c9d1e50ee820a.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/img/80/5b/805b22393a7bfefa87e3451df4cf7dec.jpg", "https://fr.web.img5.acsta.net/img/07/ab/07abed9ca6cb0edbc30f2b81cbb9b834.jpg", "https://fr.web.img6.acsta.net/img/4b/3f/4b3fbfd620d39125a6f27fb7892d55bb.jpg", "https://fr.web.img3.acsta.net/img/23/af/23af1eaeb399756c22b6bf621a1d2975.jpg", "https://fr.web.img6.acsta.net/img/33/47/334744d4e4ada016646ca09124efe5f1.jpg", "https://fr.web.img2.acsta.net/img/9a/5f/9a5fb0790ce6ddcc6a39202ec8828fe5.jpg", "https://fr.web.img6.acsta.net/img/6b/da/6bdaeb4a15e035b7aa58b4e87bd47ac7.jpg", "https://fr.web.img2.acsta.net/img/b9/62/b962e3314824b9b32d8cf4320496290c.jpg"]</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dreams</t>
+          <t>Le rêve américain</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Michel Franco</t>
+          <t>Anthony Marciano</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Découverte</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/01/fe/01fe8bc3ac70f32388a4c0f2f812e251.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Fernando, un jeune danseur de ballet originaire du Mexique, rêve de reconnaissance internationale et d’une vie meilleure aux États-Unis. Convaincu que sa maîtresse, Jennifer, une Américaine mondaine et philanthrope influente, l’aidera à réaliser ses ambitions, il quitte clandestinement son pays, échappant de justesse à la mort. Cependant, son arrivée vient bouleverser le monde soigneusement construit de Jennifer. Elle est prête à tout pour protéger leur avenir à tous deux, mais ne veut rien concéder de la vie qu'elle s'est construite.</t>
+          <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Drame, Romance, Thriller</t>
+          <t>Comédie</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>121</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Mexico, United States of America, United Kingdom</t>
+          <t>France, Canada</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Jessica Chastain, Isaac Hernández, Rupert Friend, Marshall Bell, Eligio Meléndez, Mercedes Hernández, Tatiana Ronderos, Bobby August Jr.</t>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Gregory Defleur, David Clark, Josh Casaubon, Etienne Guillou-Kervern, Gabriel Caballero, Momar Sakanoko</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=J6Al_zihrvw</t>
+          <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=320123.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>["https://fr.web.img4.acsta.net/img/0d/1c/0d1cd828167f24891af42a411720a8be.jpg", "https://fr.web.img6.acsta.net/img/88/fd/88fd163059381b8cae2549df3e5e9e30.jpg", "https://fr.web.img6.acsta.net/img/01/ce/01ce1339cf23ecbf5bdea6194ed07fc9.jpg", "https://fr.web.img5.acsta.net/img/41/d2/41d2907555a93459497eb7b075f16b32.jpg", "https://fr.web.img2.acsta.net/img/a8/26/a826b9510da8463466852c141af624af.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lol 2.0</t>
+          <t>Les figures de l'ombre</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3725,176 +3844,144 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lisa Azuelos</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>Theodore Melfi</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SCOL Pass culture</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://fr.web.img3.acsta.net/c_310_420/img/c4/54/c454690b912d2f827afd1c530d815186.jpg</t>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/17/01/10/15/08/573198.jpg</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Anne profite enfin de sa liberté après le départ de ses enfants. Mais tout bascule quand sa fille Louise, revient vivre chez elle après un échec professionnel et sentimental. Et comme une surprise n’arrive jamais seule, son fils Théo lui annonce qu’elle va devenir grand-mère ! Entre chocs générationnels, rêves en mutation et nouveaux élans amoureux… Anne comprend que la vie ne suit jamais tout à fait le plan prévu, et qu’à tout âge, on continue toujours d’apprendre à grandir.</t>
+          <t>Le destin extraordinaire des trois scientifiques afro-américaines qui ont permis aux États-Unis de prendre la tête de la conquête spatiale, grâce à la mise en orbite de l’astronaute John Glenn. Maintenues dans l’ombre de leurs collègues masculins et dans celle d’un pays en proie à de profondes inégalités, leur histoire longtemps restée méconnue est enfin portée à l’écran.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Comédie</t>
+          <t>Drame, Biopic</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sophie Marceau, Thaïs Alessandrin, Françoise Fabian, Félix Moati, Alexandre Astier, Lou Lesage, Sandrine Bonnaire, Pierre Deladonchamps</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+          <t>Taraji P. Henson, Octavia Spencer, Janelle Monaé, Kevin Costner, Kirsten Dunst, Jim Parsons, Mahershala Ali, Glen Powell</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>4, The Actor Awards 2017: Meilleur ensemble d'acteurs</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2017-03-08</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2tyGg2W5NfE</t>
+          <t>https://www.youtube.com/watch?v=_HbR5viCF3g</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000024120.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=219070.html</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/91/0c/910c9df46057596f7c75697ced84eefa.jpg", "https://fr.web.img3.acsta.net/img/b6/5a/b65abdfa3a24a32769eaa85105373ca4.jpg", "https://fr.web.img4.acsta.net/img/92/65/9265ce192a229f246430c135bae6be12.jpg", "https://fr.web.img4.acsta.net/img/cd/d5/cdd5ed3d51bafb6ec6b3ffafb4057b6d.jpg", "https://fr.web.img2.acsta.net/img/63/44/6344b9a3e80cf23b5b434333221468c6.jpg", "https://fr.web.img6.acsta.net/img/ab/b8/abb8eeba3fbcbe121af045fef1c39aca.jpg", "https://fr.web.img3.acsta.net/img/1d/48/1d48e8ac0dc355cf0a95757957ae76fb.jpg", "https://fr.web.img6.acsta.net/img/c7/34/c7342a1cffcbd824ea8b7db07a5c1ae2.jpg", "https://fr.web.img4.acsta.net/img/5e/c8/5ec8f9a5c2c2dda49e02c6190229cce6.jpg", "https://fr.web.img6.acsta.net/img/a1/31/a1314d5ea1ecefd608fcebf4bd68347f.jpg", "https://fr.web.img6.acsta.net/img/c0/c0/c0c07c78295184aecc47b9870b89627d.jpg", "https://fr.web.img4.acsta.net/img/49/be/49be1daf0d53e35466c50525a649edf9.jpg", "https://fr.web.img5.acsta.net/img/f3/8c/f38c33095b8afa91e7e63ff1b74b44a1.jpg", "https://fr.web.img4.acsta.net/img/cd/8d/cd8d6f6b9e616807904070250a3084fb.jpg", "https://fr.web.img2.acsta.net/img/0e/7c/0e7c4e425fc0b049d1ff4e68147fd6e8.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/pictures/17/01/30/11/25/216160.jpg", "https://fr.web.img6.acsta.net/pictures/16/12/09/11/08/113740.jpg", "https://fr.web.img4.acsta.net/pictures/16/12/09/11/07/479909.jpg", "https://fr.web.img6.acsta.net/pictures/16/12/09/11/07/479440.jpg", "https://fr.web.img2.acsta.net/pictures/16/12/09/11/07/478971.jpg", "https://fr.web.img4.acsta.net/pictures/16/12/09/11/07/478034.jpg", "https://fr.web.img5.acsta.net/pictures/16/10/18/10/13/486441.jpg", "https://fr.web.img6.acsta.net/pictures/16/10/18/10/13/485972.jpg", "https://fr.web.img4.acsta.net/pictures/16/10/06/09/44/210686.jpg", "https://fr.web.img6.acsta.net/pictures/16/10/06/09/44/075749.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/27/16/26/372625.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/27/16/26/372156.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/27/16/26/371687.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/27/16/26/371062.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/27/16/26/370437.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/13/17/58/418789.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/13/17/58/418321.jpg", "https://fr.web.img6.acsta.net/pictures/16/09/13/17/58/417696.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/13/17/58/417227.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/13/17/58/416445.jpg"]</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2017-03-08</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Super Charlie</t>
+          <t>Woman and child VO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jon Holmberg</t>
+          <t>Saeed Roustaee</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/f0/c9/f0c9c07f44b1e8dfd4f4793d81246491.jpg</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Will âgé de 10 ans, a toujours rêvé de devenir un super-héros et de lutter contre le crime aux côtés de son père, policier. Mais, son rêve est brutalement remis en cause à la naissance de son petit frère Charlie. Non seulement ce nourrisson attire toute l’attention de la famille et au-delà, mais Will découvre que Charlie a des super-pouvoirs … Lorsqu’un super-vilain et un scientifique dérangé mettent en œuvre un plan diabolique, Charlie, coaché par son grand frère, va alors endosser le costume de super-héros pour sauver le monde !... Y parviendront-ils ?</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Animation, Famille, Aventure, Comédie, Fantastique</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Denmark, Sweden</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Orlando Wahlsteen, Silas Strand, Tuva Novotny, Sven Björklund, Joakim Jennefors, Ulla Skoog, Johan Rödin, Lily Wahlsteen</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zHJaTRoqmEA</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=326812.html</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img5.acsta.net/img/c0/66/c0664919c43cb4c8fe8a3b076a057927.jpg", "https://fr.web.img2.acsta.net/img/51/0b/510b034f5f6bd1da71aae528408e3401.jpg", "https://fr.web.img6.acsta.net/img/51/5d/515daf26bc81cbec87c4d058c0699bf1.jpg", "https://fr.web.img2.acsta.net/img/74/09/7409b263cc69e9c55718c4d29d38ff34.jpg", "https://fr.web.img6.acsta.net/img/85/2b/852ba5cdd9c51100baf3c3ba5f6c61a4.jpg", "https://fr.web.img6.acsta.net/img/45/1a/451a8e335d22a14dc3315a6e6671f199.jpg", "https://fr.web.img6.acsta.net/img/89/13/8913b1cf9700240e35f53ef740f096be.jpg", "https://fr.web.img3.acsta.net/img/7a/22/7a22cea3f50ab26aa3dc5739d1c18a8f.jpg"]</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Abel</t>
+          <t>Pillion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3905,96 +3992,92 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Elzat Eskendir</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Grand Prix et Prix de la critique Vesoul 2025</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Ciné discussion - Coup ce cœur</t>
-        </is>
-      </c>
+          <t>Harry Lighton</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Adhérents 4 € - Autres 5 €</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://fr.web.img2.acsta.net/c_310_420/img/a5/9d/a59db0f04640682ed57e6e0d153fe78e.jpg</t>
+          <t>https://fr.web.img3.acsta.net/c_310_420/img/53/4b/534b15308fa026cff713af2a4ccae844.jpg</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Dans le tumulte post-soviétique du Kazakhstan en 1993, les fermes collectives sont démantelées et les propriétés sur le point d'être privatisées. Les dirigeants locaux ont depuis longtemps outrepassé leurs pouvoirs officiels, se partageant les ressources comme ils l’entendent. Abel, éleveur local, voudrait simplement sa part, mais la situation est plus complexe qu’il ne l’imaginait. Doit-il jouer le jeu de la corruption ou défendre ce qui lui paraît juste ?</t>
+          <t>Colin, un jeune homme introverti, rencontre Ray, le séduisant et charismatique leader d’un club de motards. Ray l’introduit dans sa communauté et fait de lui son soumis.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Famille, Drame</t>
+          <t>Drame, Erotique, Comédie, Romance</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>107</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>United Kingdom, Ireland, Netherlands</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Yerlan Toleutay, Nurzhan Beksultanova, Alikhan Lepesbaev, Ulan Nusipali</t>
+          <t>Harry Melling, Alexander Skarsgård, Lesley Sharp, Douglas Hodge, Jake Shears, Mat Hill, Nick Figgis, Zoe Engerer</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Grand Prix et Prix de la critique Vesoul 2025</t>
+          <t>Festival de Cannes 2025: Un Certain Regard - Prix du scénario</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Gl8n5I-IIHU</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012048.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000004467.html</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/0d/83/0d8360bdacfbb71b44bfdc8fb90ecf7f.jpg", "https://fr.web.img5.acsta.net/img/04/8e/048ebb38926740dfcfd073b3056a7b04.jpg", "https://fr.web.img4.acsta.net/img/8f/23/8f23909814dc0a2a580d89a815744c1c.jpg", "https://fr.web.img6.acsta.net/img/77/19/7719a44198a0cc7f2a1a2ed1d1e49913.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/40/d2/40d2e73cb6afdffbfe7eec89b048a071.jpg", "https://fr.web.img6.acsta.net/img/ab/be/abbe9e1f229cd506da96e78c680fceda.jpg", "https://fr.web.img6.acsta.net/img/dc/d2/dcd282952fe2ea9b5477ca04aa1be222.jpg", "https://fr.web.img6.acsta.net/img/59/5b/595bc464ed46845fb8ce804fe0eee894.jpg", "https://fr.web.img5.acsta.net/img/a3/07/a307f75887d4c360a599662e51bfa218.jpg", "https://fr.web.img5.acsta.net/img/e6/fb/e6fb4dd4df76c0acfec4d4beff1fcd3f.jpg", "https://fr.web.img4.acsta.net/img/b6/f8/b6f8d5502aa573671ed58cf052213e65.jpg", "https://fr.web.img6.acsta.net/img/7e/e1/7ee1912a1a102d73c581f70f5216fa5e.jpg", "https://fr.web.img6.acsta.net/img/1f/af/1faf21d86fb40f1ddf1f7743f1084f1e.jpg", "https://fr.web.img6.acsta.net/img/bb/c6/bbc687323048a5e0b72f7903f4689979.jpg", "https://fr.web.img4.acsta.net/img/93/14/9314fb2e77d009b6152e195eec5869ac.jpg", "https://fr.web.img5.acsta.net/img/e0/cf/e0cf8cd126fd311965af634189a1a084.jpg"]</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maigret et le mort amoureux</t>
+          <t>Le chant de la mer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4005,355 +4088,1031 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pascal Bonitzer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Tomm Moore</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SCOL liste</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://fr.web.img4.acsta.net/c_310_420/img/59/d8/59d850a90c94bb8ebbbb22fbff9d4970.jpg</t>
+          <t>https://fr.web.img4.acsta.net/c_310_420/pictures/14/12/01/12/08/107961.jpg</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Le commissaire Maigret est appelé en urgence au Quai d’Orsay. Monsieur Berthier-Lagès, ancien ambassadeur renommé, a été assassiné. Maigret découvre qu’il entretenait depuis cinquante ans une correspondance amoureuse avec la princesse de Vuynes, dont le mari, étrange coïncidence, vient de décéder. En se confrontant aux membres des deux familles et au mutisme suspect de la domestique du diplomate, Maigret va aller de surprise en surprise...</t>
+          <t>Ben et Maïna vivent avec leur père tout en haut d'un phare sur une petite île. Pour les protéger des dangers de la mer, leur grand-mère les emmène vivre à la ville. Ben découvre alors que sa petite soeur est une selkie, une fée de la mer dont le chant peut délivrer les êtres magiques du sort que leur a jeté la Sorcière aux hiboux. Au cours d'un fantastique voyage, Ben et Maïna vont devoir affronter peurs et dangers, et combattre la sorcière pour aider les êtres magiques à retrouver leur pouvoir.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Policier</t>
+          <t>Animation, Famille, Fantastique</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>93</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>Ireland, Luxembourg, Belgium, Denmark</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Denis Podalydès, Olivier Rabourdin, Micha Lescot, Laurent Poitrenaux, Irène Jacob, Manuel Guillot, Anne Alvaro, Julia Faure</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+          <t>David Rawle, Brendan Gleeson, Lisa Hannigan, Fionnula Flanagan, Lucy O'Connell, Jon Kenny, Pat Shortt, Colm Ó'Snodaigh</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4, European Film Awards - Prix du cinéma européen 2015: European Film Award du Meilleur film d'animation</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2014-12-10</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=G-_jyFNqjiY</t>
+          <t>https://www.youtube.com/watch?v=EjbEgXaEG8U</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325655.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=226004.html</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>["https://fr.web.img6.acsta.net/img/4c/4d/4c4dc3d77c2856f1326750e92055846b.jpg", "https://fr.web.img6.acsta.net/img/60/8a/608a37aacde1ea9c31e956ac83572fe0.jpg", "https://fr.web.img4.acsta.net/img/3e/0a/3e0aae1da4936eac025c4c097c0b2422.jpg", "https://fr.web.img6.acsta.net/img/e1/6e/e16e92bc9774d5ec304ae243afece809.jpg", "https://fr.web.img6.acsta.net/img/de/68/de688f3fa92fda9440f9423a8688cbe3.jpg", "https://fr.web.img2.acsta.net/img/33/5b/335b2eef6f1ae0101537081120fedf33.jpg", "https://fr.web.img2.acsta.net/img/68/56/6856f89d96ed0a1a1f56a8fc639032c1.jpg"]</t>
+          <t>["https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/066024.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/278027.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/274882.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/089885.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/084747.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/080255.jpg", "https://fr.web.img4.acsta.net/pictures/14/10/07/14/25/059597.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/052409.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/019143.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/011729.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/008262.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/000204.jpg", "https://fr.web.img2.acsta.net/pictures/14/09/26/15/58/003194.jpg", "https://fr.web.img5.acsta.net/pictures/14/08/27/16/36/103988.jpg", "https://fr.web.img6.acsta.net/pictures/14/06/02/16/12/536711.png"]</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2014-12-10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tafiti</t>
+          <t>Love on trial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nina Wels</t>
+          <t>Kôji Fukada</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tarif Unique 4,50 €</t>
+          <t>Découverte</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://fr.web.img5.acsta.net/c_310_420/img/e7/ff/e7ffdee0f33865e434c017c192af11ac.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/cb/0f/cb0f73df615316b86cb8478c341cb599.jpg</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Lorsque Tafiti, un jeune suricate, rencontre Mèchefol, un potamochère aussi sympathique qu’exubérant, il sait qu’ils ne pourront jamais devenir amis. En effet, la vie dans le désert est pleine de dangers et Tafiti a toujours respecté la règle essentielle de survie chez les suricates : il ne faut jamais se lier aux étrangers. Mais lorsque son grand-père est mordu par un serpent venimeux, Tafiti n’a pas le choix. Il doit partir à la recherche d’une fleur légendaire qui guérit de tous les maux, mais qui pousse au-delà des vastes étendues brûlantes du désert. Une quête périlleuse que Tafiti décide d’affronter seul. Mais c’est sans compter sur Mèchefol, bien décidé à accompagner son nouveau meilleur ami dans cette aventure, qu’il le veuille ou non…</t>
+          <t>Jeune idole de la pop en pleine ascension, Mai commet l’irréparable : tomber amoureuse, malgré l’interdiction formelle inscrite dans son contrat. Lorsque sa relation éclate au grand jour, Mai est traînée par sa propre agence devant la justice. Confrontés à une machine implacable, les deux amants décident de se battre pour défendre leur droit le plus universel : celui d’aimer.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Animation, Famille, Aventure</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan, France</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Cosima Henman, Steve Hudson, Bürger Lars Dietrich, Thomas Schmuckert, Dela Dabulamanzi, Simon Werner, Dustin Semmelrogge, Simone Cohn-Vossen</t>
+          <t>Kyoko Saito, Yuki Kura, Kenjirō Tsuda, Erika Karata, Yuna Nakamura, Miyu Ogawa</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0AG59XQEhbA</t>
+          <t>https://www.youtube.com/watch?v=opqrvdhNBGk</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=327254.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019853.html</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>["https://fr.web.img5.acsta.net/img/19/77/1977bdc7a0058cac90b8d00732caf0ca.jpg", "https://fr.web.img4.acsta.net/img/52/e6/52e62dd9215f23f1e25d326ba6b7a5fa.jpg", "https://fr.web.img2.acsta.net/img/e5/7e/e57edcf31ace74fb0a0f6f4de3be14cd.jpg", "https://fr.web.img6.acsta.net/img/aa/9f/aa9ff537ce0c29024615907c2622e4eb.jpg", "https://fr.web.img2.acsta.net/img/e5/8e/e58e207ab8bc2ac27ba7fec7da0c3696.jpg", "https://fr.web.img6.acsta.net/img/0a/ff/0aff7a5c96e70c97623d4098cfe9e51b.jpg", "https://fr.web.img4.acsta.net/img/83/73/837380da5f0906bbc4ddd94b380822c0.jpg", "https://fr.web.img3.acsta.net/img/65/3e/653e66af639a0e783b18aecde51ff7f3.jpg"]</t>
+          <t>["https://fr.web.img6.acsta.net/img/2a/ee/2aeeb5bac4f7e7738e57b64b3254f7ac.jpg", "https://fr.web.img2.acsta.net/img/57/58/5758b2b5d69e2a393dbc8c3e56f917f2.jpg", "https://fr.web.img2.acsta.net/img/a5/96/a59630b494a13bf5be9f32b88ff7a2e7.jpg", "https://fr.web.img6.acsta.net/img/af/6c/af6c769b3e356c39c2d4789eff46a044.jpg", "https://fr.web.img6.acsta.net/img/51/f1/51f1e538db936a7eb7769065a136c899.jpg", "https://fr.web.img3.acsta.net/img/38/cc/38cc70ca80d9bdd61ba77e39daf89326.jpg", "https://fr.web.img6.acsta.net/img/15/57/1557ea7681e4ff9c8d57f4e3f15ae069.jpg", "https://fr.web.img3.acsta.net/img/ce/b4/ceb47338452bd8d5073bd7805e5c916b.jpg", "https://fr.web.img6.acsta.net/img/7a/1b/7a1bd16d30f0f260f8ac109d51c109d8.jpg", "https://fr.web.img2.acsta.net/img/b3/4a/b34aa44facfe89723f48803f6e4c007d.jpg"]</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Les enfants de la Résistance</t>
+          <t>Il maestro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>VO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Christophe Barratier</t>
+          <t>Andrea di Stefano</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Famille, Jeune Public</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/19/f2/19f23e775fb0d088989e111f7a65d696.jpg</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
+          <t>Années 1980, un ancien joueur de tennis devient l’entraîneur d’un jeune talent timide, écrasé par les attentes de son père.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Drame, Historique, Aventure, Famille</t>
+          <t>Drame</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>125</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Artus, Gérard Jugnot, Pierre Deladonchamps, Julien Arruti, Oscar Boissière, Leslie Medina, Julien Pestel, Vanessa Guide</t>
+          <t>Pierfrancesco Favino, Tiziano Menichelli, Giovanni Ludeno, Dora Romano, Valentina Bellè, Astrid Meloni, Chiara Bassermann, Paolo Briguglia</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
+          <t>https://www.youtube.com/watch?v=aDZSR9JOUbw</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=283955.html</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
+          <t>["https://fr.web.img4.acsta.net/img/fa/42/fa42bd0b39395a94243253725e7d2140.jpg", "https://fr.web.img5.acsta.net/img/cc/d0/ccd0fd313423605647b83ef61de61a48.jpg", "https://fr.web.img6.acsta.net/img/33/ae/33ae80c7885681564d1357935cc63b6f.jpg", "https://fr.web.img4.acsta.net/img/9a/2b/9a2bc1a14727fcc9fee01a52697677b7.jpg", "https://fr.web.img2.acsta.net/img/01/73/017392cd8d6c596339cf1af8b45d5026.jpg", "https://fr.web.img6.acsta.net/img/08/c1/08c18c754ce9fd395965cc0e16509658.jpg", "https://fr.web.img5.acsta.net/img/9a/af/9aaf9af68b13c051ebc09568452697b6.jpg", "https://fr.web.img5.acsta.net/img/ba/58/ba58513acb3e3cbb3edcc8010a92c753.jpg", "https://fr.web.img3.acsta.net/img/19/8c/198cbbbe157e16d0ad6b5283f43efb41.jpg", "https://fr.web.img4.acsta.net/img/5b/40/5b40c90cb22733ea4e47125e7fd3b8fb.jpg", "https://fr.web.img3.acsta.net/img/39/00/390055c941655abb5b8b7b3399942430.jpg", "https://fr.web.img6.acsta.net/img/6c/69/6c69fb3ab9646bf2e9906d679b4d8661.jpg", "https://fr.web.img3.acsta.net/img/d6/4e/d64ee73f94fc2b9aca2b0db71a73d29a.jpg", "https://fr.web.img6.acsta.net/img/c5/9d/c59d6fc53d8b17e91055035ff758117e.jpg"]</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Le mystérieux regard du flamant rose</t>
+          <t>Scarlet et l'éternité</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VO</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Diego Cespedes</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Cinélatino</t>
-        </is>
-      </c>
+          <t>Mamoru Hosoda</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ados à partir de 9/10 ans Sony</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>a partir de 12 ans</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/87/5d/875d587601850e739b6222cabf1aff30.jpg</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Animation, Drame</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mana Ashida, Masaki Okada, Yutaka Matsushige, Kotaro Yoshida, Kôji Yakusho, Masachika Ichimura, Yuki Saito, Shōta Sometani</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>La grazia</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Paolo Sorrentino</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ADH 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Ciné Discussion du samedi 18h</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://fr.web.img2.acsta.net/c_310_420/img/cc/09/cc093056d1d3096effc536a9905e6d3d.jpg</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Mariano De Santis, Président de la République italienne, est un homme marqué par le deuil de sa femme et la solitude du pouvoir. Alors que son mandat touche à sa fin, il doit faire face à des décisions cruciales qui l’obligent à affronter ses propres dilemmes moraux : deux grâces présidentielles et un projet de loi hautement controversé.Aucune référence à des présidents existants, il est le fruit de l'imagination de l'auteur.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Drame, Romance</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Toni Servillo, Anna Ferzetti, Massimo Venturiello, Milvia Marigliano, Orlando Cinque, Giuseppe Gaiani, Giovanna Guida, Alessia Giuliani</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>ADH 4 € - Autres 5 €, Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mJH3p0hr7zA</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016512.html</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/img/4c/bb/4cbbbafb5f4ef80a8fd96826473953c6.jpg", "https://fr.web.img5.acsta.net/img/1c/30/1c301e495dc5675cc85d06ca20374a22.jpg", "https://fr.web.img6.acsta.net/img/d7/b7/d7b7a96adb9eb7ab085bb96f8b7f14ee.jpg", "https://fr.web.img3.acsta.net/img/67/cc/67ccd69691e93ba0fe65beee28d1f180.jpg", "https://fr.web.img3.acsta.net/img/2e/a8/2ea80882c03f9d0498b761b60089b2b1.jpg", "https://fr.web.img5.acsta.net/img/ba/cf/bacf16f5254a8c59045edd040f1e492b.jpg", "https://fr.web.img4.acsta.net/img/25/2c/252c2c8c4bdc2b5ee6453ca1e433aac0.jpg", "https://fr.web.img2.acsta.net/img/cb/16/cb161d0537f67fc117da4fa5eb0e0968.jpg", "https://fr.web.img6.acsta.net/img/bb/4c/bb4cfdb4e6e8395cb6f827a8bbab3267.jpg", "https://fr.web.img6.acsta.net/img/f2/28/f2287d7ccf2b6eb62a19598bff1b72de.jpg", "https://fr.web.img5.acsta.net/img/a9/b2/a9b22d04fa03e9bd50f9026148690ceb.jpg"]</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Le son des souvenirs</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Oliver Hermanus</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>Coup de cœur</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://fr.web.img6.acsta.net/c_310_420/img/a8/e5/a8e526e77f84a98e7a6d5dac7ba8e7f6.jpg</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Début des années 1980, dans le désert chilien. Lidia, 11 ans, grandit au sein d’une famille flamboyante qui a trouvé refuge dans un cabaret, aux abords d’une ville minière. Quand une mystérieuse maladie mortelle commence à se propager, une rumeur affirme qu’elle se transmettrait par un simple regard. La communauté devient rapidement la cible des peurs et fantasmes collectifs. Dans ce western moderne, Lidia défend les siens.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/c6/a0/c6a084a69f3a7a701da8a3308e8d5c5f.jpg</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Lionel, jeune chanteur talentueux originaire du Kentucky, grandit au son des chansons que son père chantait sur le perron de leur maison.En 1917, il quitte la ferme familiale pour intégrer le Conservatoire de Boston, où il fait la rencontre de David, un étudiant en composition aussi brillant que séduisant, mais leur lien naissant est brutalement interrompu lorsque David est mobilisé à la fin de la guerre.En 1920, réunis le temps d’un hiver, Lionel et David sillonnent les forêts et les îles du Maine pour collecter et préserver les chants folkloriques menacés d’oubli. Cette parenthèse marquera à jamais Lionel.Au cours des décennies suivantes, Lionel connaît la reconnaissance, la réussite, et d’autres histoires d’amour au fil de ses voyages à travers l’Europe. Mais ses souvenirs avec David le hantent encore, jusqu’au jour où une trace de leur œuvre commune ressurgit et lui révèle combien cette relation a résonné plus fort que toutes les autres..</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Romance, Historique, Drame</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>United Kingdom, United States of America, Sweden</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Paul Mescal, Josh O'Connor, Molly Price, Alison Bartlett, Michael Schantz, Chris Cooper, Raphael Sbarge, Hadley Robinson</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E2PSkw8BI7k</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=297924.html</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/img/1d/f8/1df8fb92d96b9df18fd392f746a4cbff.jpg", "https://fr.web.img6.acsta.net/img/28/9a/289a1bb9e08370588d27f4a930a761d0.jpg", "https://fr.web.img4.acsta.net/img/71/af/71af24f5f60f17af921c4decb16c86d4.jpg", "https://fr.web.img6.acsta.net/img/d7/a9/d7a9a5d1d14ea085059a66ee6204c67b.jpg"]</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Planètes</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Momoko Seto</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>TU 4,50 €</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Jeune Public</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/ea/8f/ea8fb95276ef64374d453772434084b5.jpg</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Quatre graines de pissenlit rescapées d’explosions nucléaires qui détruisent la Terre, se trouvent projetées dans le cosmos. Après s’être échouées sur une planète inconnue, elles partent à la quête d’un sol propice à la survie de leur espèce.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Animation, Science Fiction</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Belgium, France</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>TU 4, 50 €, Festival du Film d'Animation d'Annecy 2025: Prix Paul Grimault, Fondation Gan pour le cinéma 2022: Fondation Gan - Prix spécial</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Y4ucI60lK_M</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=279261.html</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img6.acsta.net/img/fc/d8/fcd82cd23dbd78358d01dd70a3669665.jpg", "https://fr.web.img3.acsta.net/img/ba/31/ba31db380503e009acfb33888f1ae891.jpg", "https://fr.web.img6.acsta.net/img/52/f0/52f07f622e0637f90deb44d709c33b7e.jpg", "https://fr.web.img3.acsta.net/img/6b/d7/6bd780e94b8b1a5a8e9e58b402daf4c6.jpg"]</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Le crime du 3e étage</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rémi Bezançon</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/b2/0f/b20fa135f8ed4c7d0a5e0949c56e095e.jpg</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Colette, professeure de cinéma spécialisée dans l’œuvre de Hitchcock, soupçonne son nouveau voisin d’en face d’avoir tué sa femme. Réalité ou déformation professionnelle ? Son mari, François, écrivain de romans historico-policiers un peu désuets, est d’abord sceptique face à l’obsession de Colette pour ce prétendu crime. Il se laisse cependant embarquer dans cette enquête rocambolesque, et, à mesure que les indices s’accumulent et que le mystère s’épaissit, ce couple ordinaire se transforme en duo de détectives hors pair. Alors, y a-t-il vraiment eu un crime au 3 e étage ?</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Comédie dramatique, Policier</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gilles Lellouche, Laetitia Casta, Guillaume Gallienne, Isabel Aimé González Sola, Jenna Knafo, Katayoon Latif, Matthias Jacquin, Bénédicte Choisnet</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nrjXeYFRkpE</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020100.html</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img2.acsta.net/img/af/56/af56a06bd606dccaa8b967c0030d4bd0.jpg", "https://fr.web.img2.acsta.net/img/b4/a1/b4a14af8622a802a494943a23a3986b6.jpg", "https://fr.web.img6.acsta.net/img/3b/72/3b72b4ad9ccf960ae3d393bf8e0317ff.jpg", "https://fr.web.img6.acsta.net/img/5c/7c/5c7c311be7cf8525412d5021ec277a20.jpg", "https://fr.web.img3.acsta.net/img/37/26/3726e04b5239c340e38b25a4bab52d0d.jpg", "https://fr.web.img6.acsta.net/img/6c/f0/6cf0a8524076e49e5f942240c0c7643d.jpg", "https://fr.web.img3.acsta.net/img/92/40/9240f2956590fe69a38a203a4c2ea2d0.jpg", "https://fr.web.img6.acsta.net/img/ee/55/ee55409d927fa8dc0fa5c6c6d9fbf318.jpg", "https://fr.web.img6.acsta.net/img/6e/b0/6eb04c2040068da9b797f85fd0efce76.jpg", "https://fr.web.img3.acsta.net/img/4d/b2/4db21f15cd675c352695b2d876ce72ba.jpg", "https://fr.web.img2.acsta.net/img/73/d6/73d66e3ed9719cd4cff3c0d97cd9e33e.jpg"]</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jim Capobianco</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SCOL EauC</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Bienvenue dans la Renaissance ! Une époque où artistes, savants, rois et reines inventent un monde nouveau. Parmi eux, un curieux personnage passe ses journées à dessiner d’étranges machines et à explorer les idées les plus folles. Observer la lune, voler comme un oiseau, découvrir les secrets de la médecine… il rêve de changer le monde. Embarquez pour un voyage avec le plus grand des génies, Léonard de Vinci !</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Animation, Famille, Aventure</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>France, Ireland, United States of America, United Kingdom</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stephen Fry, Daisy Ridley, Marion Cotillard, Matt Berry, Natalie Palamides, Jim Capobianco, Ben Stranahan, Jane Osborn</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z5My1jT2f1M</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=284744.html</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/pictures/23/07/05/15/50/5311709.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5297670.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5283631.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5269591.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5255552.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5239953.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5222793.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5208754.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5193155.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5177556.jpg"]</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Jim Capobianco</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SCOL EauC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Bienvenue dans la Renaissance ! Une époque où artistes, savants, rois et reines inventent un monde nouveau. Parmi eux, un curieux personnage passe ses journées à dessiner d’étranges machines et à explorer les idées les plus folles. Observer la lune, voler comme un oiseau, découvrir les secrets de la médecine… il rêve de changer le monde. Embarquez pour un voyage avec le plus grand des génies, Léonard de Vinci !</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Animation, Famille, Aventure</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>France, Ireland, United States of America, United Kingdom</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stephen Fry, Daisy Ridley, Marion Cotillard, Matt Berry, Natalie Palamides, Jim Capobianco, Ben Stranahan, Jane Osborn</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z5My1jT2f1M</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=284744.html</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img4.acsta.net/pictures/23/07/05/15/50/5311709.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5297670.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5283631.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5269591.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5255552.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5239953.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5222793.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5208754.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5193155.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5177556.jpg"]</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Les filles du ciel</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bérangère Mc Neese</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Découverte</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://fr.web.img5.acsta.net/c_310_420/img/4e/b7/4eb7083418c36bfd338cd34374143071.jpg</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Héloïse n’a nulle part où aller. Elle fait la rencontre de Mallorie qui lui propose de l’héberger dans l’appartement qu’elle partage avec deux autres jeunes femmes. Héloïse va trouver là un nouveau foyer et une nouvelle famille. Mais leurs blessures passées menacent l’équilibre fragile entre ces femmes en apparence si solides.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Chile, France, Spain, Belgium, Germany</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Tamara Cortés, Matías Catalán, Paula Dinamarca, Claudia Cabezas, Luis Dubó, Andrés Almeida, Felipe Ríos, Vicente Caballero</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Cinélatino, Festival de Cannes 2025: Prix Un Certain Regard</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=69S7bBUiBN8</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=298832.html</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>["https://fr.web.img2.acsta.net/img/82/90/82907cef76c8a8ed8ab5d99aab91f455.jpg", "https://fr.web.img2.acsta.net/img/44/85/44856197be75652c1527a3fcfc6a3d8b.jpg", "https://fr.web.img4.acsta.net/img/51/ab/51abdf1a07284b46031cdcda424d365e.jpg", "https://fr.web.img3.acsta.net/img/d3/3f/d33f7ebf1c5fefeb979bbd0439b138d0.png"]</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Belgium, France</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Héloïse Volle, Shirel Nataf, Yowa-Angélys Tshikaya, Mona Berard, Jonas Bloquet, Anne Coesens, Hugo Dillon, Kamel Laadaili</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iax6XaKnPdI</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=323410.html</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img3.acsta.net/img/28/97/2897e10fcc1bc33a8961751865a0bd97.jpg", "https://fr.web.img5.acsta.net/img/df/e8/dfe8357ec15075844e103524cbe7b7cf.jpg"]</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>

--- a/Lab/outils/work/enriched.xlsx
+++ b/Lab/outils/work/enriched.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>United Kingdom, United States of America</t>
+          <t>Grande-Bretagne</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Morocco, France, Spain, Germany, Belgium</t>
+          <t>France, Espagne, Maroc, Allemagne, Belgique</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -875,10 +875,14 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://fr.web.img3.acsta.net/c_310_420/medias/nmedia/18/70/18/27/19090499.jpg</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Voyage sur terre à l’échelle du centimètre. Ses habitants: insectes et autres animaux de l'herbe et de l'eau. Grand prix de la commission supérieure technique, Festival de Cannes 1996.</t>
+          <t>Voyage sur terre à l'echelle du centimètre. Ses habitants: insectes et autres animaux de l'herbe et de l'eau. Grand prix de la commission supérieure technique, Festival de Cannes 1996.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -893,7 +897,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>France, Switzerland, Italy</t>
+          <t>France, Suisse, Italie</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -901,10 +905,14 @@
           <t>Jacques Perrin</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2.8, César 1997: César de la Meilleure musique écrite pour un film, César du Producteur de l'année, César du Meilleur montage, César de la Meilleure photographie, César du Meilleur son, Festival de Cannes 1996: Prix Vulcain de l'Artiste-Technicien, Fondation Gan pour le cinéma 1992: Prix Fondation Gan</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1996-05-20</t>
+          <t>1996-11-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -912,11 +920,19 @@
           <t>https://www.youtube.com/watch?v=5fA3h9dy1NQ</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=42006.html</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img2.acsta.net/medias/nmedia/18/70/18/27/19090502.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/70/18/27/19090501.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/70/18/27/19090503.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/70/18/27/19090504.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/70/18/27/19090505.jpg"]</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1996-05-20</t>
+          <t>1996-11-20</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1071,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cinélatino Avant-première</t>
+          <t>Cinélatino Avant - première</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1081,7 +1097,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Colombia, Brazil, France</t>
+          <t>France, Colombie, Brésil</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1099,7 +1115,11 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/video/player_gen_cmedia=20633447&amp;cfilm=325278.html</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325278.html</t>
@@ -1165,7 +1185,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>France, Russie</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1179,7 +1199,11 @@
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/video/player_gen_cmedia=20630887&amp;cfilm=1000031821.html</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000031821.html</t>
@@ -1235,7 +1259,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ciné Documentaire du samedi 18h</t>
+          <t>Ciné Documentaire du samedi 18 €h</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1361,7 +1385,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1461,7 +1485,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1549,7 +1573,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1645,7 +1669,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Germany, United Kingdom</t>
+          <t>Grande-Bretagne</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1737,7 +1761,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>France, United States of America</t>
+          <t>France, U.S.A.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1849,7 +1873,11 @@
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023077.html</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>["https://image.tmdb.org/t/p/original/jwFj1fIxffU6CziBoufDiqNrkKA.jpg"]</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
@@ -1913,7 +1941,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Croatia, Slovenia, Serbia, Italy</t>
+          <t>Slovénie, Italie, Croatie, Serbie</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2009,7 +2037,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2087,25 +2115,29 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://fr.web.img4.acsta.net/c_310_420/img/cb/92/cb92cf130cfc390336b1400c7130de6f.jpg</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ex-membre des marines, Louanne Johnson accepte d'enseigner à la East Palo Alto Highschool, un établissement à la réputation sulfureuse. Réalisant que ses élèves possèdent de grandes capacités intellectuelles, elle décide de se battre pour les aider à apprendre.</t>
+          <t>Un tournesol hors norme, un gnome déterminé, une petite fille intrépide, défiant les lois de la nature, une fourmi rêveuse, des créatures gloutonnes… nul doute, la rébellion est en marche ! Programme de 6 courts métrages.Programme de 6 courts métrages : - Tournesol de Natalia Chernysheva (France, 2023, 4') : Un tournesol pas comme les autres choisit deporter un regard nouveau sur son environnement, il va découvrir un univers totalement différent…- Le Renard minuscule de Sylwia Szkiladz et Aline Quertain (Belgique, France, Suisse, 2015, 8') : Au milieu d'un jardin foisonnant, un tout petit renard rencontre une enfant intrépide qui fait pousser des plantes géantes ! Par un joyeux hasard, ils découvrent qu’ils peuvent faire pousser des objets, cela va donner des idées aux petits malins…- La Marche des fourmis de Fedor Yudin (Russie, 2022, 5') : Une fourmi part à la découverte du monde qui l'entoure et explore ses richesses sonores et musicales. Inspiré de l'art graphique chinois, ce film musical propose une contemplation de la nature et attire l'attention sur la beauté des choses petites et simples.- Le Gnome et le Nuage de Zuzana Čupová et Filip Diviak (République Tchèque, 2019, 5') : Petite île, ciel radieux. Monsieur Gnome souhaite passer cette splendide journée à bronzer sur un transat. Un petit nuage se met juste devant le soleil, ne lui laissant pas le temps d’en profiter. Mais Monsieur Gnome sait exactement quoi faire !- Le Dragon et la musique de Camille Muller (Suisse, 2015, 8') : L'amitié d'une petite joueuse de flûte et d'un dragon mélomane au sein d'un royaume n'autorisant que les marches militaires.- Mojappi - C'est à moi de Nijitaro (Japon, 2025, 3') : Dans la forêt, trois petites créatures fort coquines convoitent le gros pancake que se préparent leurs camarades. Tous les stratagèmes sont bons pour le récupérer !</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Drame</t>
+          <t>Animation, Famille</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>34</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>France, Belgique, Suisse, Russie, République tchèque, Japon</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2113,10 +2145,14 @@
           <t>Michelle Pfeiffer, George Dzundza, Courtney B. Vance, Robin Bartlett, Beatrice Winde, John Neville, Lorraine Toussaint, Renoly Santiago</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>TU 3 €</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1996-02-07</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2124,11 +2160,19 @@
           <t>https://www.youtube.com/watch?v=gA-5nLQCmW8</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000036350.html</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img5.acsta.net/img/4d/3c/4d3c7c4e51dcbb9c80ffa5db14a73afc.jpg", "https://fr.web.img4.acsta.net/img/aa/e1/aae1206b0311fb98aa0b613fd0cae29c.jpg", "https://fr.web.img3.acsta.net/img/85/77/8577949b432f39a0ab74c42315116e98.jpg", "https://fr.web.img6.acsta.net/img/7e/68/7e68d676372286e18b74e70be35e2ed4.jpg", "https://fr.web.img6.acsta.net/img/bf/48/bf482ae0bc64f3b584ef51abfc49aa15.jpg", "https://fr.web.img4.acsta.net/img/9e/ce/9ece6ddec5938f58bfa666c3b93958aa.jpg"]</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1996-02-07</t>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2211,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ciné Patrimoine du samedi 18h</t>
+          <t>Ciné Patrimoine du samedi 18 €h</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2193,7 +2237,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Hong-Kong</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2285,7 +2329,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>France, Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2477,7 +2521,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2565,7 +2609,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Belgium, France</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2661,7 +2705,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>France, Belgium</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2845,7 +2889,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Allemagne</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2937,7 +2981,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Germany, Cyprus, United States of America, Qatar, Saudi Arabia, Egypt, United Arab Emirates, Jordan, Kuwait</t>
+          <t>Allemagne, Chypre, Palestine, U.S.A., Jordanie, Emirats Arabes Unis</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3033,7 +3077,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>France, Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3129,7 +3173,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Lebanon, United States of America, Germany, Greece</t>
+          <t>Liban, U.S.A., Allemagne, Arabie Saoudite, Qatar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3229,7 +3273,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3303,7 +3347,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Ciné Jeunes du samedi 18h</t>
+          <t>Ciné Jeunes du samedi 18 €h</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3329,7 +3373,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3491,7 +3535,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Famille  à partir de 9/10 ans</t>
+          <t>Famille à partir de 9 € / 10 ans</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3521,7 +3565,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>France, Luxembourg, Canada, Belgium</t>
+          <t>France, Luxembourg, Canada, Belgique</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3785,7 +3829,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>France, Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3881,7 +3925,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3955,18 +3999,58 @@
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://fr.web.img6.acsta.net/c_310_420/img/48/5a/485af2a4575500546e6af0c462d9f150.jpg</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Mahnaz, une infirmière de 45 ans, élève seule ses enfants. Alors qu’elle s’apprête à épouser son petit ami Hamid, son fils Aliyar est renvoyé de l’école. Lorsqu’un un accident tragique vient tout bouleverser, Mahnaz se lance dans une quête de justice pour obtenir réparation...</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Drame</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/video/player_gen_cmedia=20632702&amp;cfilm=1000019745.html</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019745.html</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>["https://fr.web.img5.acsta.net/img/42/20/4220d60b7edb1ed8c0b8a85ea8ad9582.jpg", "https://fr.web.img4.acsta.net/img/77/a1/77a1bde1cabfd2b837735ac3a1c9ff72.jpg", "https://fr.web.img5.acsta.net/img/a4/b2/a4b2a9aa5fcbb8581be337ff35ce644b.jpg", "https://fr.web.img6.acsta.net/img/30/f6/30f6c8d983f12011d6edfbca88b118e1.jpg", "https://fr.web.img2.acsta.net/img/b6/8f/b68ff068e5eefbfad3c6393a1d1cd6f5.jpg", "https://fr.web.img4.acsta.net/img/b1/54/b1545b5f632dfd513dcf79312f5deda3.jpg", "https://fr.web.img5.acsta.net/img/50/69/5069460ce8637aff4292a0f24b5744d1.jpg"]</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4025,7 +4109,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>United Kingdom, Ireland, Netherlands</t>
+          <t>Grande-Bretagne, Irlande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4125,7 +4209,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Ireland, Luxembourg, Belgium, Denmark</t>
+          <t>Irlande, Danemark, Belgique, Luxembourg, France</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4221,7 +4305,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Japan, France</t>
+          <t>Japon, France</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4309,7 +4393,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Italie</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4379,7 +4463,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ados à partir de 9/10 ans Sony</t>
+          <t>ados à partir de 9 € / 10 ans Sony</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4409,7 +4493,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Japon, U.S.A.</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4479,7 +4563,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Ciné Discussion du samedi 18h</t>
+          <t>Ciné Discussion du samedi 18 €h</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -4505,7 +4589,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Italie</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4601,7 +4685,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>United Kingdom, United States of America, Sweden</t>
+          <t>U.S.A.</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4701,7 +4785,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Belgium, France</t>
+          <t>France, Belgique</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -4885,7 +4969,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>France, Ireland, United States of America, United Kingdom</t>
+          <t>Irlande, U.S.A.</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4985,7 +5069,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>France, Ireland, United States of America, United Kingdom</t>
+          <t>Irlande, U.S.A.</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5081,7 +5165,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Belgium, France</t>
+          <t>Belgique, France</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">

--- a/Lab/outils/work/enriched.xlsx
+++ b/Lab/outils/work/enriched.xlsx
@@ -567,17 +567,17 @@
           <t>Harris Dickinson</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
           <t>Coup de cœur</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Festival de Cannes 2025: Un Certain Regard - Prix du meilleur acteur</t>
+          <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes, Festival de Cannes 2025: Un Certain Regard - Prix du meilleur acteur</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -663,22 +663,22 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Patrick Imbert</t>
+          <t>Scolaire</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SCOL CauC</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>2,80 €</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Patrick Imbert / Collège Noé</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/pictures/21/07/29/17/38/3976490.jpg</t>
@@ -711,7 +711,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.8, César 2022: César du Meilleur film d'animation, Lumières de la presse étrangère 2022: Meilleur film d'animation, Fondation Gan pour le cinéma 2018: Prix Fondation Gan, Festival du Cinéma et Musique de Film de la Baule 2022: Ibis d'or de la meilleure musique de film de l'année</t>
+          <t>César 2022: César du Meilleur film d'animation, Lumières de la presse étrangère 2022: Meilleur film d'animation, Fondation Gan pour le cinéma 2018: Prix Fondation Gan, Festival du Cinéma et Musique de Film de la Baule 2022: Ibis d'or de la meilleure musique de film de l'année</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -767,17 +767,17 @@
           <t>Maryam Touzani</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prix du public Venise</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Prix du public Venise</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
           <t>Coup de cœur</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
@@ -809,7 +809,11 @@
           <t>Carmen Maura, Marta Etura, Ahmed Boulane, Miguel Garcés, María Alfonsa Rosso, La Imèn, Tarik Rmili, Mohamed Naimane</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Prix du public Venise</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>2026-02-25</t>
@@ -863,18 +867,22 @@
           <t>Claude Nuridsany, Marie Pérennou</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SCOL EauC</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2,80 €</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ec Labsstide Clermont</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>https://fr.web.img3.acsta.net/c_310_420/medias/nmedia/18/70/18/27/19090499.jpg</t>
@@ -907,7 +915,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.8, César 1997: César de la Meilleure musique écrite pour un film, César du Producteur de l'année, César du Meilleur montage, César de la Meilleure photographie, César du Meilleur son, Festival de Cannes 1996: Prix Vulcain de l'Artiste-Technicien, Fondation Gan pour le cinéma 1992: Prix Fondation Gan</t>
+          <t>César 1997: César de la Meilleure musique écrite pour un film, César du Producteur de l'année, César du Meilleur montage, César de la Meilleure photographie, César du Meilleur son, Festival de Cannes 1996: Prix Vulcain de l'Artiste-Technicien, Fondation Gan pour le cinéma 1992: Prix Fondation Gan</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -963,15 +971,15 @@
           <t>Nicolas Charlet, Bruno Lavaine</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TU 5 €</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI</t>
+          <t>Tarif Unique 5 €</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1005,11 +1013,7 @@
           <t>Laurent Lafitte, Olga Kurylenko, Blanche Gardin, Valérie Donzelli, Monsieur Fraize, Zabou Breitman, Bertrand Goncalves</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>TU 5 €</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>2026-03-04</t>
@@ -1063,17 +1067,17 @@
           <t>Aurélien Vernhes-Lermusiaux</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prix Fondation Gan</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Prix Fondation Gan</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Cinélatino Avant - première</t>
-        </is>
-      </c>
+          <t>Cinélatino Avant-première</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
@@ -1107,7 +1111,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Fondation Gan pour le cinéma 2023: Fondation Gan - Prix à la création</t>
+          <t>Prix Fondation Gan, Fondation Gan pour le cinéma 2023: Fondation Gan - Prix à la création</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1163,17 +1167,17 @@
           <t>Marie Caudry, Aurore Peuffier, Nina Bisyarina</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>TU 3 €</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
@@ -1189,11 +1193,7 @@
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>TU 3 €</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>2026-02-18</t>
@@ -1247,22 +1247,22 @@
           <t>Edouard Bergeon</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ADH 4 € - Autres 5 €</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Ciné Documentaire du samedi 18h</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>invité Jérôme Bayle attente de réponse</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Ciné Documentaire du samedi 18 €h</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/img/76/32/76325273dba162d20a31fbc235173f69.jpg</t>
@@ -1293,11 +1293,7 @@
           <t>Jérôme Bayle</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>ADH 4 € - Autres 5 €</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
@@ -1351,17 +1347,17 @@
           <t>Josh Safdie</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Golden Globe meilleur acteur</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Golden Globe meilleur acteur</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
           <t>Coup de cœur</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
@@ -1395,7 +1391,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
+          <t>Golden Globe meilleur acteur, Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,14 +1450,10 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Famille</t>
-        </is>
-      </c>
+          <t>Famille, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -1635,18 +1627,22 @@
           <t>Samantha Cutler, Daniel Snaddon</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SCOL Liste</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Ec mat Hellé</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/pictures/23/06/27/16/09/1673570.jpg</t>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4, International Emmy Awards 2023: Prix du Meilleur programme d'animation</t>
+          <t>International Emmy Awards 2023: Prix du Meilleur programme d'animation</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1824,12 +1820,12 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>DOC Découverte</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Documentaire Découverte</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
@@ -1912,12 +1908,12 @@
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
@@ -2003,17 +1999,17 @@
           <t>Josh Safdie</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Golden Globe meilleur acteur</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Golden Globe meilleur acteur</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
           <t>Coup de cœur</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
@@ -2047,7 +2043,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
+          <t>Golden Globe meilleur acteur, Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2103,17 +2099,17 @@
           <t>Natalia Chernysheva</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>TU 3 €</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Jeune Public</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Tarif Unique 3 €</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
@@ -2145,11 +2141,7 @@
           <t>Michelle Pfeiffer, George Dzundza, Courtney B. Vance, Robin Bartlett, Beatrice Winde, John Neville, Lorraine Toussaint, Renoly Santiago</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>TU 3 €</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>2026-02-18</t>
@@ -2203,18 +2195,22 @@
           <t>John Woo</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ADH 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ciné Patrimoine du samedi 18h</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ciné Patrimoine du samedi 18 €h</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>Adhérent 4 € - Autres 5 €</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Partenariat Empreinte Carbonne</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>https://fr.web.img6.acsta.net/c_310_420/img/8b/f4/8bf4588571b3ca5edd40c475993bc21b.jpg</t>
@@ -2245,11 +2241,7 @@
           <t>Tony Leung Chiu-Wai, 張學友, Waise Lee Chi-Hung, Simon Yam, 袁潔瑩, 甄楚倩, 林聰, 鮑起靜</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>ADH 4 € - Autres 5 €</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>1993-08-04</t>
@@ -2392,13 +2384,17 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>DOC Coup de coeur</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Documentaire Coup de coeur</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Séance sup suite séance annulée</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>https://fr.web.img2.acsta.net/c_310_420/img/f5/52/f5523e15c97af96169bdc93479553602.jpg</t>
@@ -2490,14 +2486,10 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Famille</t>
-        </is>
-      </c>
+          <t>Famille, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
@@ -2671,15 +2663,15 @@
           <t>Christophe Barratier</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SCOL Actu</t>
+          <t>3,50 €</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -2713,11 +2705,7 @@
           <t>Artus, Gérard Jugnot, Pierre Deladonchamps, Julien Arruti, Oscar Boissière, Leslie Medina, Julien Pestel, Vanessa Guide</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>2026-02-11</t>
@@ -2860,12 +2848,12 @@
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -2952,12 +2940,12 @@
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
@@ -3043,15 +3031,15 @@
           <t>Anthony Marciano</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>TU 5 €</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Séance EPHAD HANDI</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Séance EPHAD HANDI</t>
+          <t>Tarif Unique 5 €</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3085,11 +3073,7 @@
           <t>Jean-Pascal Zadi, Raphaël Quenard, Gregory Defleur, David Clark, Josh Casaubon, Etienne Guillou-Kervern, Gabriel Caballero, Momar Sakanoko</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>TU 5 €</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>2026-02-18</t>
@@ -3144,12 +3128,12 @@
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
@@ -3235,19 +3219,15 @@
           <t>Daniel Chong</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>TU 4,50 €</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Ciné goûter, Jeune Public</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Ciné goûter</t>
+          <t>Tarif Unique 4,50 €</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -3281,11 +3261,7 @@
           <t>Piper Curda, Bobby Moynihan, Jon Hamm, Kathy Najimy, Dave Franco, Eduardo Franco, Aparna Nancherla, Sam Richardson</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>TU 4, 50 €</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>2026-03-04</t>
@@ -3339,15 +3315,15 @@
           <t>David Michôd</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ADH 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ciné Jeunes du samedi 18h</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Ciné Jeunes du samedi 18 €h</t>
+          <t>Adhérent 4 € - Autres 5 €</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -3381,11 +3357,7 @@
           <t>Sydney Sweeney, Ben Foster, Merritt Wever, Katy O'Brian, Ethan Embry, Jess Gabor, Chad L. Coleman, Tony Cavalero</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>ADH 4 € - Autres 5 €</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>2026-03-04</t>
@@ -3530,14 +3502,10 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Famille à partir de 9 € / 10 ans</t>
-        </is>
-      </c>
+          <t>Famille à partir de 9/10 ans, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>a partir de 12 ans</t>
@@ -3891,18 +3859,22 @@
           <t>Theodore Melfi</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SCOL Pass culture</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Collège Abbal</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>https://fr.web.img5.acsta.net/c_310_420/pictures/17/01/10/15/08/573198.jpg</t>
@@ -3935,7 +3907,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4, The Actor Awards 2017: Meilleur ensemble d'acteurs</t>
+          <t>The Actor Awards 2017: Meilleur ensemble d'acteurs</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3992,12 +3964,12 @@
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
@@ -4080,12 +4052,12 @@
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
@@ -4175,18 +4147,22 @@
           <t>Tomm Moore</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SCOL liste</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>4 €</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Hellé élem</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>https://fr.web.img4.acsta.net/c_310_420/pictures/14/12/01/12/08/107961.jpg</t>
@@ -4219,7 +4195,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4, European Film Awards - Prix du cinéma européen 2015: European Film Award du Meilleur film d'animation</t>
+          <t>European Film Awards - Prix du cinéma européen 2015: European Film Award du Meilleur film d'animation</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4276,12 +4252,12 @@
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
@@ -4458,17 +4434,13 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>ados à partir de 9 € / 10 ans Sony</t>
-        </is>
-      </c>
+          <t>ados à partir de 9/10 ans Sony, Jeune Public</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>a partir de 12 ans</t>
+          <t>Sony, a partir de 12 ans</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4555,15 +4527,15 @@
           <t>Paolo Sorrentino</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ADH 4 € - Autres 5 €</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Ciné Discussion du samedi 18h</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Ciné Discussion du samedi 18 €h</t>
+          <t>Adhérent 4 € - Autres 5 €</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -4599,7 +4571,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>ADH 4 € - Autres 5 €, Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
+          <t>Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4656,12 +4628,12 @@
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Coup de cœur</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
@@ -4747,19 +4719,15 @@
           <t>Momoko Seto</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>TU 4,50 €</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Jeune Public</t>
+          <t>Famille, Jeune Public</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Famille</t>
+          <t>Tarif Unique 4,50 €</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -4791,7 +4759,7 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>TU 4, 50 €, Festival du Film d'Animation d'Annecy 2025: Prix Paul Grimault, Fondation Gan pour le cinéma 2022: Fondation Gan - Prix spécial</t>
+          <t>Festival du Film d'Animation d'Annecy 2025: Prix Paul Grimault, Fondation Gan pour le cinéma 2022: Fondation Gan - Prix spécial</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4935,18 +4903,22 @@
           <t>Jim Capobianco</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SCOL EauC</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>3,80 €</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Ec Lautignac</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
@@ -4977,11 +4949,7 @@
           <t>Stephen Fry, Daisy Ridley, Marion Cotillard, Matt Berry, Natalie Palamides, Jim Capobianco, Ben Stranahan, Jane Osborn</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>2024-01-31</t>
@@ -5035,18 +5003,22 @@
           <t>Jim Capobianco</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Scolaire</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SCOL EauC</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>3,80 €</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Ec Rieux</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
@@ -5077,11 +5049,7 @@
           <t>Stephen Fry, Daisy Ridley, Marion Cotillard, Matt Berry, Natalie Palamides, Jim Capobianco, Ben Stranahan, Jane Osborn</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>2024-01-31</t>
@@ -5136,12 +5104,12 @@
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Découverte</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>

--- a/Lab/outils/work/enriched.xlsx
+++ b/Lab/outils/work/enriched.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:W50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,55 +486,60 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>age_min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>synopsis</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>genres</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>duree_min</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>pays</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>acteurs_principaux</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>recompenses</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>date_sortie</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>trailer_url</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>allocine_url</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>backdrops</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>annee</t>
         </is>
@@ -584,57 +589,58 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/e7/82/e782432beca8a04cea3b2dc66459c4a5.jpg</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>À Londres, Mike vit dans la rue, il va de petits boulots en larcins, jusqu'au jour où il se fait incarcérer. À sa sortie de prison, aidé par les services sociaux, il tente de reprendre sa vie en main en combattant ses vieux démons.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Grande-Bretagne</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Frank Dillane, Megan Northam, Карина Химчук, Shonagh Marie, Amr Waked, Claudia Jones, Shahzad Ali, Michael Quartey</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>Frank Dillane, Megan Northam, Karyna Khymchuk</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes, Festival de Cannes 2025: Un Certain Regard - Prix du meilleur acteur</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=4cJL6vmYOeo</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019912.html</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/bb/78/bb784f39d4843f599afba87529b2c028.jpg", "https://fr.web.img2.acsta.net/img/df/3d/df3dc86c2a96673a0d49796581ea5929.jpg", "https://fr.web.img4.acsta.net/img/1e/44/1e4451e35e6059ee33003bb1ddbe8b9c.jpg", "https://fr.web.img2.acsta.net/img/2d/a2/2da21da8e6c084f763290e30f0e31548.jpg", "https://fr.web.img6.acsta.net/img/da/30/da301edeec034ee0839592ee70672741.jpg", "https://fr.web.img4.acsta.net/img/fc/1e/fc1e3b1ba4bbd2e5fb722ed5f0b294e3.jpg"]</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
@@ -684,57 +690,58 @@
           <t>https://fr.web.img2.acsta.net/c_310_420/pictures/21/07/29/17/38/3976490.jpg</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>A Katmandou, le reporter japonais Fukamachi croit reconnaître Habu Jôji, cet alpiniste que l'on pensait disparu depuis des années. Il semble tenir entre ses mains un appareil photo qui pourrait changer l’histoire de l’alpinisme. Et si George Mallory et Andrew Irvine étaient les premiers hommes à avoir atteint le sommet de l’Everest, le 8 juin 1924 ? Seul le petit Kodak Vest Pocket avec lequel ils devaient se photographier sur le toit du monde pourrait livrer la vérité. 70 ans plus tard, pour tenter de résoudre ce mystère, Fukamachi se lance sur les traces de Habu. Il découvre un monde de passionnés assoiffés de conquêtes impossibles et décide de l’accompagner jusqu’au voyage ultime vers le sommet des dieux.</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aventure, Animation, Drame</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>France, Luxembourg</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Éric Herson-Macarel, Damien Boisseau, Elisabeth Ventura, Lazare Herson-Macarel, Kylian Rehlinger, François Dunoyer, Philippe Vincent, Luc Bernard</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>Lazare Herson-Macarel, Eric Herson-Macarel, Damien Boisseau</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>César 2022: César du Meilleur film d'animation, Lumières de la presse étrangère 2022: Meilleur film d'animation, Fondation Gan pour le cinéma 2018: Prix Fondation Gan, Festival du Cinéma et Musique de Film de la Baule 2022: Ibis d'or de la meilleure musique de film de l'année</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2021-09-22</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=sM_KmxpEaJU</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=269946.html</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/pictures/21/07/09/13/07/5600107.jpg", "https://fr.web.img4.acsta.net/pictures/21/07/09/13/07/5586066.jpg", "https://fr.web.img6.acsta.net/pictures/21/07/09/13/07/5572026.jpg", "https://fr.web.img6.acsta.net/pictures/21/07/09/13/07/5557985.jpg", "https://fr.web.img3.acsta.net/pictures/21/07/09/13/07/5543945.jpg"]</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>2021-09-22</t>
         </is>
@@ -784,57 +791,58 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/4f/46/4f46a55374da1919875e846787fd1289.jpg</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Maria Angeles, une Espagnole de 79 ans, vit seule à Tanger, dans le nord du Maroc, où elle profite de sa ville et de son quotidien. Sa vie bascule lorsque sa fille Clara arrive de Madrid pour vendre l’appartement dans lequel elle a toujours vécu. Déterminée à rester dans cette ville qui l'a vue grandir, elle met tout en œuvre pour garder sa maison et récupérer les objets d'une vie. Contre toute attente, elle redécouvre en chemin l’amour et le désir.</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Comédie dramatique</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>France, Espagne, Maroc, Allemagne, Belgique</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Carmen Maura, Marta Etura, Ahmed Boulane, Miguel Garcés, María Alfonsa Rosso, La Imèn, Tarik Rmili, Mohamed Naimane</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>Carmen Maura, Marta Etura, Ahmed Boulane</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>Prix du public Venise</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FwtLBQpAnk0</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020088.html</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/84/df/84dfc5e9a03da904c491ef5bcab2ec53.jpg", "https://fr.web.img5.acsta.net/img/0e/d4/0ed4d030496886c31283dad276baec29.jpg", "https://fr.web.img5.acsta.net/img/4a/cb/4acb7d81653a7b5ca65bdc5257fefef6.jpg", "https://fr.web.img6.acsta.net/img/55/0b/550b3a5a46eefd999b31e246819e1b4d.jpg", "https://fr.web.img6.acsta.net/img/17/22/1722bdb5f07a5101d5df9ec34a463491.jpg"]</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
@@ -888,57 +896,58 @@
           <t>https://fr.web.img3.acsta.net/c_310_420/medias/nmedia/18/70/18/27/19090499.jpg</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Voyage sur terre à l'echelle du centimètre. Ses habitants: insectes et autres animaux de l'herbe et de l'eau. Grand prix de la commission supérieure technique, Festival de Cannes 1996.</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>France, Suisse, Italie</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Jacques Perrin</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>Jacques Perrin, Kristin Scott Thomas</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>César 1997: César de la Meilleure musique écrite pour un film, César du Producteur de l'année, César du Meilleur montage, César de la Meilleure photographie, César du Meilleur son, Festival de Cannes 1996: Prix Vulcain de l'Artiste-Technicien, Fondation Gan pour le cinéma 1992: Prix Fondation Gan</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1996-11-20</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=5fA3h9dy1NQ</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=42006.html</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/medias/nmedia/18/70/18/27/19090502.jpg", "https://fr.web.img6.acsta.net/medias/nmedia/18/70/18/27/19090501.jpg", "https://fr.web.img3.acsta.net/medias/nmedia/18/70/18/27/19090503.jpg", "https://fr.web.img4.acsta.net/medias/nmedia/18/70/18/27/19090504.jpg", "https://fr.web.img5.acsta.net/medias/nmedia/18/70/18/27/19090505.jpg"]</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>1996-11-20</t>
         </is>
@@ -988,53 +997,54 @@
           <t>https://fr.web.img4.acsta.net/c_310_420/img/a3/21/a3212f7a3bc901b69704c09de6e30093.jpg</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Alex a un problème : son nouveau voisin est son sosie parfait. Avec des cheveux. Un double en mieux, qui va totalement bouleverser son existence.</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Laurent Lafitte, Olga Kurylenko, Blanche Gardin, Valérie Donzelli, Monsieur Fraize, Zabou Breitman, Bertrand Goncalves</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Laurent Lafitte, Blanche Gardin, Olga Kurylenko</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ObYzfs8ITaE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=288260.html</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/80/5b/805b22393a7bfefa87e3451df4cf7dec.jpg", "https://fr.web.img5.acsta.net/img/07/ab/07abed9ca6cb0edbc30f2b81cbb9b834.jpg", "https://fr.web.img6.acsta.net/img/4b/3f/4b3fbfd620d39125a6f27fb7892d55bb.jpg", "https://fr.web.img3.acsta.net/img/23/af/23af1eaeb399756c22b6bf621a1d2975.jpg", "https://fr.web.img6.acsta.net/img/33/47/334744d4e4ada016646ca09124efe5f1.jpg", "https://fr.web.img2.acsta.net/img/9a/5f/9a5fb0790ce6ddcc6a39202ec8828fe5.jpg", "https://fr.web.img6.acsta.net/img/6b/da/6bdaeb4a15e035b7aa58b4e87bd47ac7.jpg", "https://fr.web.img2.acsta.net/img/b9/62/b962e3314824b9b32d8cf4320496290c.jpg"]</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -1084,57 +1094,58 @@
           <t>https://fr.web.img4.acsta.net/c_310_420/img/41/e6/41e68878abbf465c362d6dcf53bdf30d.jpg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Après des années d’absence, Ciro revient chez lui, au chevet de sa mère. Dans ce désert colombien de la Tatacoa, il retrouve ceux qu’il avait fuis et affronte les derniers gardiens d’un territoire aussi fragile qu’envoûtant.</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>France, Colombie, Brésil</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Alexis Tafur, Miguel Ángel Viera, Ángela Rodríguez, Laura Valentina Quintero, Virgelina Gil Saénz, Santiago Porras, Laura Rodríguez, Jonathan Mortenson</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>Alexis Lozano Tafur, Miguel Ángel Viera, Ángela Rodríguez (II)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>Prix Fondation Gan, Fondation Gan pour le cinéma 2023: Fondation Gan - Prix à la création</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/video/player_gen_cmedia=20633447&amp;cfilm=325278.html</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325278.html</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/bb/97/bb97bee3e88688957ba27a8753fbeb36.jpg", "https://fr.web.img6.acsta.net/img/e2/67/e267201f2a234b9227f0caf0c2fbe8f5.jpg", "https://fr.web.img6.acsta.net/img/e4/3f/e43f8f9bb6b21486ed7aaaf11ef813b4.jpg", "https://fr.web.img2.acsta.net/img/9c/23/9c236b8bfd0d130eb548acf4198ebacf.jpg", "https://fr.web.img4.acsta.net/img/d3/6b/d36b2b2c604b0fb61f8dc457d579f722.jpg", "https://fr.web.img3.acsta.net/img/df/f4/dff426c01fc11d33ec6f763b4a0ac0b4.jpg", "https://fr.web.img6.acsta.net/img/49/70/49705864b270d9141fd2f87877bfbb9b.jpg", "https://fr.web.img6.acsta.net/img/f6/fb/f6fbab37a4045cb645f3b2c585eeb018.jpg", "https://fr.web.img4.acsta.net/img/17/98/17984d2d9dc437fb8ab12cfbf25ae155.jpg"]</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
@@ -1184,37 +1195,50 @@
           <t>https://fr.web.img4.acsta.net/c_310_420/img/af/46/af46510d2d819c30b064e68efa6e5233.jpg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Quatre ours, quatre contes, quatre saisons : qu’ils soient immenses, ensommeillés ou gourmands, les ours savent aussi être tendres. À leurs côtés, un oisillon malicieux, un petit lapin friand de noisettes ou encore un oiseau sentimental vivent des aventures extraordinaires. Tout doucement, ils découvrent le bonheur d’être ensemble. Programme : Animal rit d'Aurore Peuffier (France, 3') : Fasciné par le spectacle d’un ours acrobate, un oisillon se met en tête de participer : ni une, ni deux, il saute sur scène et commence à amuser la galerie avec ses pitreries. Mais c’est tout un art de faire le clown… Chuuut ! de Nina Bisyarina (Russie, 7’) : Un ours s’approche d’un parc d’attractions quand il est surpris par la neige. Ses yeux commencent doucement à se fermer : il est temps pour lui d’hiberner, et cet endroit semble si douillet… Mais est-ce vraiment une bonne idée ? Émerveillement de Martin Clerget (France, 3′) : D’habitude, les ours n’aiment pas trop partager leurs réserves de noisettes, et surtout pas avec des petits chapardeurs. Mais cette nuit-là, pour le petit lapin et l’énorme ours, tout est différent… L'Ourse et l'oiseau de Marie Caudry (France, 26’) : Au cours de l’été, une ourse et un oiseau sont devenu·es inséparables. Quand l’automne arrive, il faut se rendre à l’évidence : bientôt l’ourse devra hiberner et l’oiseau devra migrer – l’une rêvera tandis que l’autre voyagera. L’heure des adieux approche… Mais on souffle alors à l’ourse une idée extraordinaire qui va changer son hiver.</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>France, Russie</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Noémie Lvovsky, Bertrand Belin, Estéban</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/video/player_gen_cmedia=20630887&amp;cfilm=1000031821.html</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000031821.html</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/84/71/8471bb1a8bd4e80543025ce50f15748f.jpg", "https://fr.web.img4.acsta.net/img/92/65/9265c8b5dc48406633f3fb1fbd6ddfca.jpg", "https://fr.web.img6.acsta.net/img/a4/17/a4178fea144bc542aeb1d67517b484e3.jpg", "https://fr.web.img6.acsta.net/img/21/b7/21b7fff1eb2b6d33c60f28bc8262df70.jpg", "https://fr.web.img6.acsta.net/img/36/d5/36d51017ba6721475005c65af158b8c3.jpg", "https://fr.web.img5.acsta.net/img/58/25/582576c31308e4460671911d2de3f3ee.jpg", "https://fr.web.img4.acsta.net/img/b9/71/b9712420bfd364b02b83bf3b22470764.jpg", "https://fr.web.img3.acsta.net/img/31/40/31403126892acb5287317c41fdd2b6ec.jpg", "https://fr.web.img2.acsta.net/img/fe/f2/fef22b1db43302c25cb11b8e256c850c.jpg", "https://fr.web.img4.acsta.net/img/bd/64/bd64033f6fc3148e1e917b1544f529b8.jpg", "https://fr.web.img5.acsta.net/img/21/9c/219c65998d57faaf9fe7e4c5bfba0480.jpg", "https://fr.web.img4.acsta.net/img/8f/e9/8fe98fbd0f4fcbc60df34c487b5dde28.jpg", "https://fr.web.img6.acsta.net/img/7f/89/7f89bdc9dbd33efc5169b6876d68a8bb.jpg", "https://fr.web.img3.acsta.net/img/79/d7/79d75776630a8743a034982631efb86e.jpg", "https://fr.web.img5.acsta.net/img/a2/c3/a2c34b595a816cf34d64067cabdbc71c.jpg", "https://fr.web.img4.acsta.net/img/17/4b/174bacf6107acbae117ee7f9ec5a4394.jpg", "https://fr.web.img6.acsta.net/img/b9/63/b963d7a5754630388677ab0567d52e58.jpg", "https://fr.web.img2.acsta.net/img/43/c4/43c4950db5cba3e0b60ed65b2a0a7c71.jpg", "https://fr.web.img4.acsta.net/img/51/a8/51a8e13eb81ae507eab521b88c67cff7.jpg", "https://fr.web.img2.acsta.net/img/15/37/1537d27e10786df4b6d3e23bfef289e7.jpg", "https://fr.web.img6.acsta.net/img/f8/f3/f8f30699660b4646ebdc89302c53fb43.jpg"]</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -1268,53 +1292,54 @@
           <t>https://fr.web.img2.acsta.net/c_310_420/img/76/32/76325273dba162d20a31fbc235173f69.jpg</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Edouard Bergeon (« Au Nom de la Terre ») nous plonge dans la vie de Jérôme Bayle, éleveur charismatique du Sud-Ouest et figure nationale de la ruralité. Avec humour et tendresse, il dresse un portrait sensible de l’agriculture familiale française d’aujourd’hui et de ceux qui se battent pour la faire perdurer.</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Jérôme Bayle</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=RdkB6UGDQmM</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000032102.html</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/a3/a0/a3a0456f8fa4f8c2dc2ffc3215e53740.jpg", "https://fr.web.img6.acsta.net/img/a6/7e/a67e4d10463b7272be66cb1bb3b44535.jpg", "https://fr.web.img4.acsta.net/img/1f/f7/1ff7c0cae0beb97de65034488de20640.jpg", "https://fr.web.img6.acsta.net/img/92/4e/924e7c5bcbe978bf140e4dca1c1a29e5.jpg", "https://fr.web.img4.acsta.net/img/d4/10/d41017db78436edfcd562b4192b02e56.jpg", "https://fr.web.img4.acsta.net/img/0c/41/0c410c9f2d25735e7cc3f72a79c16686.jpg", "https://fr.web.img4.acsta.net/img/19/d8/19d86ca951be7193dfbfc73330e0e761.jpg", "https://fr.web.img2.acsta.net/img/d2/e5/d2e56406a296cf0e5a5921fa34ed7415.jpg"]</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -1364,57 +1389,58 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/7d/cb/7dcb8416ab4e8fd4ff6eeaed758c6004.jpg</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Marty Mauser, un jeune homme à l’ambition démesurée, est prêt à tout pour réaliser son rêve et prouver au monde entier que rien ne lui est impossible.</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Drame, Biopic</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A'zion, Kevin O'Leary, Tyler, The Creator, Fran Drescher, Abel Ferrara, Emory Cohen</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A’zion</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>Golden Globe meilleur acteur, Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=s9gSuKaKcqM</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007317.html</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/c3/09/c309b5855c7b236945b1013c62676a5c.jpg", "https://fr.web.img5.acsta.net/img/29/b5/29b53a920df12d99a5314b789f1faf9c.jpg", "https://fr.web.img4.acsta.net/img/0d/7d/0d7dfee552b2aa4423aaf0e26885eb9d.jpg", "https://fr.web.img4.acsta.net/img/91/b0/91b02b31e4cf6df8f526d920ed5d1bbb.jpg", "https://fr.web.img5.acsta.net/img/09/80/09801189159bd682629326396f00f1b1.jpg", "https://fr.web.img6.acsta.net/img/cd/df/cddf292cfd1032909df0ccf6057bb151.jpg", "https://fr.web.img6.acsta.net/img/04/e1/04e1efb1f485ab6aa99c0c9ddf05ae28.jpg", "https://fr.web.img6.acsta.net/img/f2/86/f28623015549bbd278d0c162203d0e9d.jpg", "https://fr.web.img5.acsta.net/img/fa/ff/faffe9d8707cbb03040bae34d8bed952.jpg", "https://fr.web.img3.acsta.net/img/a3/04/a30488d5862e30c8597eddcee3f3c426.jpg", "https://fr.web.img6.acsta.net/img/b2/ae/b2ae37eae4f102a5427889137ea062be.jpg", "https://fr.web.img6.acsta.net/img/a1/88/a188dbf927027d760a1034d3cafb2dde.jpg", "https://fr.web.img4.acsta.net/img/f8/05/f8059864a9d229cab3d664173280ca83.jpg", "https://fr.web.img3.acsta.net/img/29/80/298098488caa5271b37f7b8207cc6f83.jpg", "https://fr.web.img6.acsta.net/img/63/88/63888a193780eeb0574c836513e5c75c.jpg"]</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -1462,51 +1488,56 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>Pour sauver son emploi, David accepte un plan foireux : ramener un mystérieux colis d’Amérique du Sud. Il se retrouve à bord d’une croisière avec son ex Tess, son fils Léo, et son collègue Stéphane, aussi benêt que maladroit, dont David se sert pour transporter le colis à sa place. Tout dérape lorsque ce dernier l’ouvre accidentellement : un adorable bébé Marsupilami apparait et le voyage vire au chaos ! La bande à Fifi est de retour et elle s’est fait un nouveau copain…</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Comédie, Aventure, Famille</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Philippe Lacheau, Jamel Debbouze, Tarek Boudali, Élodie Fontan, Julien Arruti, Jean Reno, Corentin Guillot, Gérard Jugnot</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Philippe Lacheau, Jamel Debbouze, Élodie Fontan</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jd1p07MSUHA</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317669.html</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/3f/ed/3feda78092e00ae808ac3b1459d7ce6d.jpg", "https://fr.web.img6.acsta.net/img/73/6c/736ca7cbb7149dc50fab40d89a4ede0b.jpg", "https://fr.web.img3.acsta.net/img/ba/b3/bab3e1215a3162567806058a4eca3366.jpg", "https://fr.web.img4.acsta.net/img/5c/f2/5cf297231feedcba95dbd750f3ff4a1b.jpg", "https://fr.web.img2.acsta.net/img/03/93/039383dd4d79a0cf1b6421d72fc5dcac.jpg", "https://fr.web.img6.acsta.net/img/6e/26/6e26cc82c87547ef1fe525c274e8207e.jpg", "https://fr.web.img5.acsta.net/img/dd/f6/ddf6b584fe3892e8614a3269a11fc5fd.jpg", "https://fr.web.img2.acsta.net/img/15/58/155880bca2d2f451afe6ebd37a5d0d5c.jpg", "https://fr.web.img3.acsta.net/img/12/7b/127bb7b1851154fe0647d7938a458454.jpg", "https://fr.web.img4.acsta.net/img/99/5f/995f1c3e1f3def1dbcedf39fc1b8ed1a.jpg", "https://fr.web.img4.acsta.net/img/fe/24/fe24cc8065bca7c905b4f6cd3df92823.jpg", "https://fr.web.img6.acsta.net/img/52/9c/529c6800b388fd6a3ee7921fa5c21abd.jpg", "https://fr.web.img4.acsta.net/img/88/a2/88a2c61b5b5e54483f284b6afeb02ccd.jpg", "https://fr.web.img6.acsta.net/img/66/c7/66c7424d9f2d1f307daf13f3a70de290.jpg"]</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
@@ -1548,53 +1579,54 @@
           <t>https://fr.web.img4.acsta.net/c_310_420/img/59/d8/59d850a90c94bb8ebbbb22fbff9d4970.jpg</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Le commissaire Maigret est appelé en urgence au Quai d’Orsay. Monsieur Berthier-Lagès, ancien ambassadeur renommé, a été assassiné. Maigret découvre qu’il entretenait depuis cinquante ans une correspondance amoureuse avec la princesse de Vuynes, dont le mari, étrange coïncidence, vient de décéder. En se confrontant aux membres des deux familles et au mutisme suspect de la domestique du diplomate, Maigret va aller de surprise en surprise...</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Policier</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>France, Belgique</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Denis Podalydès, Olivier Rabourdin, Micha Lescot, Laurent Poitrenaux, Irène Jacob, Manuel Guillot, Anne Alvaro, Julia Faure</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Denis Podalydès, Anne Alvaro, Manuel Guillot</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=G-_jyFNqjiY</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=325655.html</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/4c/4d/4c4dc3d77c2856f1326750e92055846b.jpg", "https://fr.web.img6.acsta.net/img/60/8a/608a37aacde1ea9c31e956ac83572fe0.jpg", "https://fr.web.img4.acsta.net/img/3e/0a/3e0aae1da4936eac025c4c097c0b2422.jpg", "https://fr.web.img6.acsta.net/img/e1/6e/e16e92bc9774d5ec304ae243afece809.jpg", "https://fr.web.img6.acsta.net/img/de/68/de688f3fa92fda9440f9423a8688cbe3.jpg", "https://fr.web.img2.acsta.net/img/33/5b/335b2eef6f1ae0101537081120fedf33.jpg", "https://fr.web.img2.acsta.net/img/68/56/6856f89d96ed0a1a1f56a8fc639032c1.jpg"]</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -1648,57 +1680,58 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/pictures/23/06/27/16/09/1673570.jpg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Un programme de quatre courts métrages haut en couleur pour triompher des différences !Les Tourouges et les Toubleus de Samantha Cutler et Daniel Snaddon • 2022 • 26mn • Grande Bretagne • Animation 3DSur une lointaine planète vivaient Édouard et Jeannette, un Toubleu et une Tourouge. Par un beau matin, ces deux-là tombèrent amoureux. Malheureusement pour eux, les Tourouges et les Toubleus ne se mélangent pas, et bien plus encore : ils se détestent depuis des générations...Sous les nuages de Vasilisa Tikunova • 2021 • 4 min • Russie Walter l’agneau souhaite plus que tout ressembler à un nuage. Mais le chemin qui mène à son rêve l’éloigne de son troupeau.Somni de Sonja Rohleder • 2023 • 3mn • Allemagne Le soleil se couche et les paupières se ferment. Se balançant d’une feuille à l’autre, le petit singe s’endort, basculant dans le monde des rêves, des plantes sauvages et des créatures mystérieuses et colorées.La Fiesta de Alfredo Soderguit et Alejo Schettini • 2021 • 3mn • Argentine, Colombie, Uruguay Deux petits oiseaux, l’un blanc, l’autre noir, vivent en harmonie dans le même arbre. Un jour, un groupe d’oiseaux rouges élit domicile au sommet de leur arbre... Les deux oiseaux vont tenter de se faire accepter.Par les créateurs du Gruffalo et de Superasticot, d’après le livre illustré de Julia Donaldson et Axel Scheffler.</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Animation, Famille</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Grande-Bretagne</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Sally Hawkins, Bill Bailey, Ashna Rabheru, Adjoa Andoh, Daniel Ezra, Meera Syal, Rob Brydon, Raphaella Crow</t>
-        </is>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>Maia Baran, Sally Hawkins, Marie Braam</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>International Emmy Awards 2023: Prix du Meilleur programme d'animation</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>2023-10-18</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=BT6b4zO-VSM</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>https://www.allocine.fr/video/player_gen_cmedia=19602323&amp;cfilm=317561.html</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317561.html</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/pictures/23/06/27/16/10/3295534.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/10/3281495.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/10/3265895.jpg", "https://fr.web.img2.acsta.net/pictures/23/06/27/16/10/3251856.jpg", "https://fr.web.img5.acsta.net/pictures/23/06/27/16/10/3236256.jpg", "https://fr.web.img4.acsta.net/pictures/23/06/27/16/09/5479872.jpg"]</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>2023-10-18</t>
         </is>
@@ -1740,53 +1773,54 @@
           <t>https://fr.web.img4.acsta.net/c_310_420/img/66/c3/66c3fe35122f2e0e86e01859a80153b7.jpg</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>A Paris, dans le tumulte de la Fashion Week, Maxine, une réalisatrice américaine apprend une nouvelle qui va bouleverser sa vie. Elle croise alors le chemin d’Ada, une jeune mannequin sud‐soudanaise ayant quitté son pays, et Angèle, une maquilleuse française aspirant à une autre vie. Entre ces trois femmes aux horizons pourtant si différents se tisse une solidarité insoupçonnée. Sous le vernis glamour se révèle une forme de révolte silencieuse : celle de femmes qui recousent, chacune à leur manière, les fils de leur propre histoire.</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>France, U.S.A.</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Angelina Jolie, Ella Rumpf, Anyier Anei, Louis Garrel, Garance Marillier, Vincent Lindon, Finnegan Oldfield, Sean Gullette</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Angelina Jolie, Ella Rumpf, Anyier Anei</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=UsUDEFfZiys</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000015619.html</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/38/0c/380ce7989a2c199ce7cee4765a58e93f.jpg", "https://fr.web.img4.acsta.net/img/6d/c7/6dc704d0821db6a38029b12f5cbf3801.jpg", "https://fr.web.img4.acsta.net/img/e2/05/e205108590799a901dd70d85f084b3a0.jpg", "https://fr.web.img3.acsta.net/img/67/90/6790c53e743597cc1816ffd26ab7d2f5.jpg", "https://fr.web.img2.acsta.net/img/bb/cc/bbcc4f05a05fd27bc0077fe6ed46b545.jpg", "https://fr.web.img4.acsta.net/img/10/c0/10c0566d711c8cfc5718381bfc384e3e.jpg", "https://fr.web.img6.acsta.net/img/82/50/825020e892f8ffd453c1375dc83187fb.jpg", "https://fr.web.img2.acsta.net/img/46/d4/46d4fb614854a9ba8365ebaa1ecf5fcd.jpg", "https://fr.web.img6.acsta.net/img/6a/6a/6a6a0371af4c1430a61630bd86961ccc.jpg"]</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -1832,49 +1866,50 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/82/5e/825eb2b7151adae83555d489e46dd35b.jpg</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>Benoît vit en Dordogne, à quelques kilomètres du village où il a grandi. Il a construit son paradis à l'abri des regards, s’est émancipé à sa manière, seul, dans la nature, avec ses couleurs. Il a trouvé ses manières de résister, de s’affranchir des stigmates du passé pour continuer à habiter le territoire de son enfance. Sur le chemin qu’il est parvenu à ouvrir, il reste des ronces qui continuent à le blesser. Alors ensemble on avance, on défriche parce que nos histoires résonnent, parce qu’on s’est trouvé. Et puis, avec les autres queers du coin on décide d’organiser une Pride, parce qu’il est temps de sortir du bois, de prendre l’espace qu’on n’a jamais eu, pour se célébrer, se réparer et enfin ouvrir une voie.</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>https://vimeo.com/1012828750</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000023077.html</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>["https://image.tmdb.org/t/p/original/jwFj1fIxffU6CziBoufDiqNrkKA.jpg"]</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -1920,53 +1955,54 @@
           <t>https://fr.web.img3.acsta.net/c_310_420/img/96/f6/96f64541b789c2a43df6ede012b98c59.jpg</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Lucia, une jeune fille introvertie, rejoint la chorale de son école et se lie d’amitié avec Ana-Maria, populaire et séduisante. Confrontée à un environnement inconnu et à l’éveil de sa sexualité, Lucia commence à remettre en question ses croyances, perturbant l’harmonie du chœur.</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Comédie dramatique</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Slovénie, Italie, Croatie, Serbie</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Jara Sofija Ostan, Mina Švajger, Saša Tabaković, Nataša Burger, Staša Popovič, Mateja Strle, Saša Pavček, Matia Casson</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Jara Sofija Ostan, Mina Švajger, Saša Tabaković</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Rm9m7u-NsN4</t>
-        </is>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>https://www.allocine.fr/video/player_gen_cmedia=20627331&amp;cfilm=317577.html</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=317577.html</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/da/f4/daf4bd80fababe2574f48d7370ece43e.jpg", "https://fr.web.img3.acsta.net/img/91/89/91893ef8d9c7d9e2f7227d74c7216b43.jpg", "https://fr.web.img3.acsta.net/img/26/8b/268b7f9aed09a21bb960d0d7150ddeb2.jpg", "https://fr.web.img4.acsta.net/img/42/a6/42a689bc3a96edb020c7da2b3b2d97e2.jpg", "https://fr.web.img2.acsta.net/img/0f/4b/0f4b473b8012df29d0a2c22c5b6c48ec.jpg"]</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -2016,57 +2052,58 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/7d/cb/7dcb8416ab4e8fd4ff6eeaed758c6004.jpg</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Marty Mauser, un jeune homme à l’ambition démesurée, est prêt à tout pour réaliser son rêve et prouver au monde entier que rien ne lui est impossible.</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Drame, Biopic</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A'zion, Kevin O'Leary, Tyler, The Creator, Fran Drescher, Abel Ferrara, Emory Cohen</t>
-        </is>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>Timothée Chalamet, Gwyneth Paltrow, Odessa A’zion</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>Golden Globe meilleur acteur, Golden Globes 2026: Meilleur acteur dans une comédie ou une comédie musicale</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=s9gSuKaKcqM</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000007317.html</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/c3/09/c309b5855c7b236945b1013c62676a5c.jpg", "https://fr.web.img5.acsta.net/img/29/b5/29b53a920df12d99a5314b789f1faf9c.jpg", "https://fr.web.img4.acsta.net/img/0d/7d/0d7dfee552b2aa4423aaf0e26885eb9d.jpg", "https://fr.web.img4.acsta.net/img/91/b0/91b02b31e4cf6df8f526d920ed5d1bbb.jpg", "https://fr.web.img5.acsta.net/img/09/80/09801189159bd682629326396f00f1b1.jpg", "https://fr.web.img6.acsta.net/img/cd/df/cddf292cfd1032909df0ccf6057bb151.jpg", "https://fr.web.img6.acsta.net/img/04/e1/04e1efb1f485ab6aa99c0c9ddf05ae28.jpg", "https://fr.web.img6.acsta.net/img/f2/86/f28623015549bbd278d0c162203d0e9d.jpg", "https://fr.web.img5.acsta.net/img/fa/ff/faffe9d8707cbb03040bae34d8bed952.jpg", "https://fr.web.img3.acsta.net/img/a3/04/a30488d5862e30c8597eddcee3f3c426.jpg", "https://fr.web.img6.acsta.net/img/b2/ae/b2ae37eae4f102a5427889137ea062be.jpg", "https://fr.web.img6.acsta.net/img/a1/88/a188dbf927027d760a1034d3cafb2dde.jpg", "https://fr.web.img4.acsta.net/img/f8/05/f8059864a9d229cab3d664173280ca83.jpg", "https://fr.web.img3.acsta.net/img/29/80/298098488caa5271b37f7b8207cc6f83.jpg", "https://fr.web.img6.acsta.net/img/63/88/63888a193780eeb0574c836513e5c75c.jpg"]</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -2118,51 +2155,52 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>Un tournesol hors norme, un gnome déterminé, une petite fille intrépide, défiant les lois de la nature, une fourmi rêveuse, des créatures gloutonnes… nul doute, la rébellion est en marche ! Programme de 6 courts métrages.Programme de 6 courts métrages : - Tournesol de Natalia Chernysheva (France, 2023, 4') : Un tournesol pas comme les autres choisit deporter un regard nouveau sur son environnement, il va découvrir un univers totalement différent…- Le Renard minuscule de Sylwia Szkiladz et Aline Quertain (Belgique, France, Suisse, 2015, 8') : Au milieu d'un jardin foisonnant, un tout petit renard rencontre une enfant intrépide qui fait pousser des plantes géantes ! Par un joyeux hasard, ils découvrent qu’ils peuvent faire pousser des objets, cela va donner des idées aux petits malins…- La Marche des fourmis de Fedor Yudin (Russie, 2022, 5') : Une fourmi part à la découverte du monde qui l'entoure et explore ses richesses sonores et musicales. Inspiré de l'art graphique chinois, ce film musical propose une contemplation de la nature et attire l'attention sur la beauté des choses petites et simples.- Le Gnome et le Nuage de Zuzana Čupová et Filip Diviak (République Tchèque, 2019, 5') : Petite île, ciel radieux. Monsieur Gnome souhaite passer cette splendide journée à bronzer sur un transat. Un petit nuage se met juste devant le soleil, ne lui laissant pas le temps d’en profiter. Mais Monsieur Gnome sait exactement quoi faire !- Le Dragon et la musique de Camille Muller (Suisse, 2015, 8') : L'amitié d'une petite joueuse de flûte et d'un dragon mélomane au sein d'un royaume n'autorisant que les marches militaires.- Mojappi - C'est à moi de Nijitaro (Japon, 2025, 3') : Dans la forêt, trois petites créatures fort coquines convoitent le gros pancake que se préparent leurs camarades. Tous les stratagèmes sont bons pour le récupérer !</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Animation, Famille</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>France, Belgique, Suisse, Russie, République tchèque, Japon</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Michelle Pfeiffer, George Dzundza, Courtney B. Vance, Robin Bartlett, Beatrice Winde, John Neville, Lorraine Toussaint, Renoly Santiago</t>
-        </is>
-      </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=gA-5nLQCmW8</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>https://www.allocine.fr/video/player_gen_cmedia=20632118&amp;cfilm=1000036350.html</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000036350.html</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/4d/3c/4d3c7c4e51dcbb9c80ffa5db14a73afc.jpg", "https://fr.web.img4.acsta.net/img/aa/e1/aae1206b0311fb98aa0b613fd0cae29c.jpg", "https://fr.web.img3.acsta.net/img/85/77/8577949b432f39a0ab74c42315116e98.jpg", "https://fr.web.img6.acsta.net/img/7e/68/7e68d676372286e18b74e70be35e2ed4.jpg", "https://fr.web.img6.acsta.net/img/bf/48/bf482ae0bc64f3b584ef51abfc49aa15.jpg", "https://fr.web.img4.acsta.net/img/9e/ce/9ece6ddec5938f58bfa666c3b93958aa.jpg"]</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -2216,53 +2254,54 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/8b/f4/8bf4588571b3ca5edd40c475993bc21b.jpg</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>Hong Kong 1967. Tandis que les manifestations pro-communistes secouent la colonie britannique, trois amis, Ben, Frank et Paul tentent de subsister malgré leur condition sociale précaire. Devenu assassin malgré-lui le jour même de son mariage, Ben se voit contraint de fuir au Vietnam, accompagné de ses deux camarades. Projetés dans la guerre qui fait rage, les 3 jeunes hommes vont subir les pires revers et humiliations, jusqu’à ce que leur amitié explose...</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Drame, Action, Thriller</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Hong-Kong</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Tony Leung Chiu-Wai, 張學友, Waise Lee Chi-Hung, Simon Yam, 袁潔瑩, 甄楚倩, 林聰, 鮑起靜</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Tony Leung Chiu-Wai, Jacky Cheung, Waise Lee</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
         <is>
           <t>1993-08-04</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=NIACrhExQgM</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=8190.html</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/medias/nmedia/18/35/56/43/18407018.jpg"]</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>1993-08-04</t>
         </is>
@@ -2304,53 +2343,54 @@
           <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Jean-Pascal Zadi, Raphaël Quenard, Gregory Defleur, David Clark, Josh Casaubon, Etienne Guillou-Kervern, Gabriel Caballero, Momar Sakanoko</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -2400,57 +2440,58 @@
           <t>https://fr.web.img2.acsta.net/c_310_420/img/f5/52/f5523e15c97af96169bdc93479553602.jpg</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>Après La Panthère des neiges, Vincent Munier nous invite au coeur des forêts des Vosges. C’est ici qu’il a tout appris grâce à son père Michel, naturaliste, ayant passé sa vie à l’affut dans les bois. Il est l’heure pour eux de transmettre ce savoir à Simon, le fils de Vincent. Trois regards, trois générations, une même fascination pour la vie sauvage. Nous découvrirons avec eux cerfs, oiseaux rares, renards et lynx… et parfois, le battement d’ailes d’un animal légendaire : le Grand Tétras.</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Documentaire</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Vincent Munier, Michel Munier, Simon Munier</t>
-        </is>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>Vincent Munier</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>César 2026: César du Meilleur documentaire, César du Meilleur son</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2025-12-17</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=heoMyS_hjm8</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=321789.html</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/48/79/4879231bf7df434ccefa260bf84fb18e.jpg", "https://fr.web.img2.acsta.net/img/06/47/0647937046e9709ff0b5a12f5af66696.jpg", "https://fr.web.img3.acsta.net/img/65/07/6507a80e00b779bd573a117ffb50cb59.jpg", "https://fr.web.img5.acsta.net/img/6d/64/6d641e15f7e1462ca5892078bb90c316.jpg", "https://fr.web.img5.acsta.net/img/69/b5/69b5410351d939cf5c005d68177db47c.jpg", "https://fr.web.img6.acsta.net/img/59/c4/59c4faa4bcbdbf003d6d30ecf546b632.jpg", "https://fr.web.img2.acsta.net/img/3f/d9/3fd9448d45fd39f1e5528ce6fef5de9d.jpg", "https://fr.web.img6.acsta.net/img/3d/a8/3da8c497a50cc952bb2b6da89f2095bd.jpg", "https://fr.web.img6.acsta.net/img/a5/ec/a5ecb292afd35323c0ba493853527eb1.jpg", "https://fr.web.img6.acsta.net/img/80/32/803246533fc9555b203272de850bede6.jpg", "https://fr.web.img4.acsta.net/img/5d/66/5d664316ddf74a92e69ea1f8bfb8051e.jpg"]</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>2025-12-17</t>
         </is>
@@ -2498,51 +2539,56 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Drame, Historique, Aventure, Famille</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Artus, Gérard Jugnot, Pierre Deladonchamps, Julien Arruti, Oscar Boissière, Leslie Medina, Julien Pestel, Vanessa Guide</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
@@ -2584,53 +2630,54 @@
           <t>https://fr.web.img5.acsta.net/c_310_420/img/29/3f/293f877dfb7dcb5672591cba06329a20.jpg</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>Quand Alice et Vincent Gauthier convoquent en urgence leurs trois enfants, la fratrie débarque affolée craignant le pire … mais, bonne nouvelle, leurs parents ont en fait touché le Jackpot ! Le problème : ils ne comptent pas leur donner un centime.</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>France, Belgique</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>André Dussollier, Miou-Miou, Arnaud Ducret, Thomas Solivérès, Pauline Clément, Frédérique Tirmont, Bernard Alane</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>André Dussollier, Miou-Miou, Arnaud Ducret</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=hHBRGiURnQM</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012022.html</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/ca/f1/caf1ebc7acc4d5c28fec740b199c3ac5.jpg", "https://fr.web.img6.acsta.net/img/7d/4f/7d4f4464f105a1b8cddd1149eac963e1.jpg", "https://fr.web.img4.acsta.net/img/4d/88/4d88b430ffeeadd55f368e40fcb13ab9.jpg", "https://fr.web.img4.acsta.net/img/b9/31/b931cab8dbe5ad24c3d0628e07f9f6f3.jpg", "https://fr.web.img5.acsta.net/img/04/2d/042d382e1411fe7f363b4a11103eabb6.jpg", "https://fr.web.img2.acsta.net/img/6d/4e/6d4ef8abf0fc4f96c924143e2c838e7e.jpg", "https://fr.web.img3.acsta.net/img/6c/40/6c40df5dcbab1a70702d9f196a1a9cd1.jpg", "https://fr.web.img6.acsta.net/img/f9/67/f967f2b5b10d36297d2a6eb307032374.jpg", "https://fr.web.img5.acsta.net/img/ee/33/ee33247bf7021e9758af1add30d0903a.jpg"]</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
@@ -2680,53 +2727,54 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/0f/58/0f58892693cc868f4c0caf21614954cf.jpg</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>Pendant l’occupation allemande durant la Seconde Guerre mondiale, François, Eusèbe et Lisa, trois enfants courageux, se lancent dans une aventure secrète : résister aux nazis en plein cœur de la France. Sabotages, messages cachés et évasions périlleuses, ils mènent des actions clandestines sous le nez de l’ennemi. L’audace et l’amitié sont leurs seules armes pour lutter contre l’injustice.</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Drame, Historique, Aventure, Famille</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Artus, Gérard Jugnot, Pierre Deladonchamps, Julien Arruti, Oscar Boissière, Leslie Medina, Julien Pestel, Vanessa Guide</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Lucas Hector, Nina Filbrandt, Octave Gerbi</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-2v2vWrUwcA</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000006174.html</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/8a/42/8a4292a470667f8315381e42f336d546.jpg", "https://fr.web.img2.acsta.net/img/cc/c7/ccc7fb7e24f2235353ddf413eb3b8734.jpg", "https://fr.web.img4.acsta.net/img/f4/15/f4153f99f16722bd823824a193194ef2.jpg", "https://fr.web.img5.acsta.net/img/f4/8f/f48f09cfc47da3cd5ac0478fc59f009c.jpg", "https://fr.web.img2.acsta.net/img/e2/f9/e2f9eb754cbec5fa08ec375ab52c1309.jpg", "https://fr.web.img5.acsta.net/img/a8/5f/a85f6763e4eb13807ebf8c3a67dd508e.jpg", "https://fr.web.img4.acsta.net/img/31/ca/31cab79941ff24e2744c2e49315c7573.jpg", "https://fr.web.img5.acsta.net/img/1a/c1/1ac144fe2f6c4df6d2656c9998eab111.jpg"]</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
@@ -2768,53 +2816,54 @@
           <t>https://fr.web.img3.acsta.net/c_310_420/img/7b/ec/7bec0c5e6b6d2cf4f985353223ae133a.jpg</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
         <is>
           <t>Habité par Victor Hugo, le comédien Robert Zucchini traîne une douce mélancolie lorsqu'il n'est pas sur scène. Chaque soir, il remplit les salles en transmettant son amour des mots. Jusqu’au jour où réapparaît sa fille, qu’il n’a pas vue grandir… Et si aimer, pour une fois, valait mieux qu’admirer ?</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Comédie dramatique</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Fabrice Luchini, Chiara Mastroianni, Louise Orry-Diquéro, Suzanne De Baecque, Marie Narbonne, Lauretta Trefeu, Iris Bry, Naidra Ayadi</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Fabrice Luchini, Chiara Mastroianni, Marie Narbonne</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=t0RrVuOml0M</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000021956.html</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/ae/9c/ae9c941a95ecbbce7cec4a9a6b007863.jpg", "https://fr.web.img6.acsta.net/img/d7/63/d76336aeef620ee4276e61ca19c16ae9.jpg", "https://fr.web.img5.acsta.net/img/b2/65/b26508a01fde5b941dbedd03c31f92d8.jpg", "https://fr.web.img6.acsta.net/img/a1/11/a1112c0a20486aba18ff5c874a31ce07.jpg", "https://fr.web.img5.acsta.net/img/a2/45/a24509dcf0996c251a6521648eb25183.jpg", "https://fr.web.img6.acsta.net/img/d3/eb/d3eb19a79b8f3f2ddc49f16017f1094a.jpg", "https://fr.web.img4.acsta.net/img/e9/87/e987439316c89fa9fecbc48c10843d0a.jpg"]</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -2860,53 +2909,54 @@
           <t>https://fr.web.img2.acsta.net/c_310_420/img/8b/f3/8bf3d9725705d4ef36ebe09fcb93c92f.jpg</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Julia et Tobias semblent être le couple parfait. Mais derrière les apparences, un trouble gronde. L’équilibre fragile entre les deux est brisé lorsque leur fille Marielle développe soudainement des capacités télépathiques, lui accordant le pouvoir de voir et d’entendre tout ce que ses parents font, jour et nuit.</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Allemagne</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Laeni Geiseler, Julia Jentsch, Felix Kramer, Mehmet Ateşçi, Moritz von Treuenfels, Sissy Höfferer, Victoria Mayer, Nadja Sabersky</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Laeni Geiseler, Julia Jentsch, Felix Kramer</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=nbe3ITNfonQ</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017164.html</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/4d/e0/4de04abb0de6ae7a78ee6ea947452ab4.jpg", "https://fr.web.img5.acsta.net/img/5c/82/5c82daf8abe88d5ea23412e933b4ce33.jpg", "https://fr.web.img6.acsta.net/img/53/99/5399df917873462fcafb51c07268b43d.jpg"]</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
@@ -2952,53 +3002,54 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/ab/be/abbedce650d9fd1b3fe6c2defe9c3518.jpg</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>De 1948 à nos jours, trois générations d’une famille palestinienne portent les espoirs et les blessures d’un peuple. Une fresque où Histoire et intime se rencontrent.</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Allemagne, Chypre, Palestine, U.S.A., Jordanie, Emirats Arabes Unis</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Saleh Bakri, Cherien Dabis, Adam Bakri, Maria Zreik, Mohammad Bakri, Muhammad Abed Elrahman, Sanad Alkabareti, Salah Al Din</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Saleh Bakri, Cherien Dabis, Adam Bakri</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=od_EKv4n3p0</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016229.html</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/82/b7/82b77dbba1ff19a6af5101f7fca7e897.jpg", "https://fr.web.img3.acsta.net/img/88/40/8840f9da13b5c59b532851fd21c5ae09.jpg", "https://fr.web.img4.acsta.net/img/36/2d/362d347ccb59c8956dba8ebccd40706e.jpg", "https://fr.web.img2.acsta.net/img/3f/0e/3f0ebf1110ef9ed746188c3b1d427fab.jpg", "https://fr.web.img3.acsta.net/img/a5/6c/a56c1f84811272bfc647ba1b6637f2d6.jpg", "https://fr.web.img2.acsta.net/img/60/2d/602db1d598e3d59161f9688de9b5439b.jpg", "https://fr.web.img2.acsta.net/img/df/be/dfbe86dfd73724f319005c36aae16701.jpg", "https://fr.web.img6.acsta.net/img/a5/bd/a5bdc5b23848b8c4c0141a3442356f79.jpg"]</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -3048,53 +3099,54 @@
           <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Jean-Pascal Zadi, Raphaël Quenard, Gregory Defleur, David Clark, Josh Casaubon, Etienne Guillou-Kervern, Gabriel Caballero, Momar Sakanoko</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -3140,53 +3192,54 @@
           <t>https://fr.web.img4.acsta.net/c_310_420/img/9e/96/9e96bec2d1ac11dba0c4a6c65454a0ef.jpg</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
         <is>
           <t>Nino et Yasmina tombent amoureux dans la cour de leur école à Beyrouth, et rêvent à leur vie d’adulte, à un monde merveilleux. 20 ans plus tard, ils se retrouvent par accident et c’est à nouveau l’amour fou, magnétique, incandescent. Peut-on construire un avenir, dans un pays fracturé, qu’on tente de quitter mais qui vous retient de façon irrésistible ?</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Drame, Romance</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Liban, U.S.A., Allemagne, Arabie Saoudite, Qatar</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Mounia Akl, Hassan Akil, Camille Salameh, Julia Kassar, Tino Karam, Nadyn Chalhoub, Alex Choueiry, Valentina Hachem</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Mounia Akl, Hassan Akil, Julia Kassar</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=tfhS2aXatiA</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000028071.html</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/06/8a/068ae35ea83f35673f3e3e3e7833c203.jpg"]</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -3238,51 +3291,56 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>Mabel, une adolescente passionnée par les animaux, saute (littéralement !) sur l’occasion d’essayer une nouvelle technologie révolutionnaire permettant de communiquer avec eux d’une manière totalement inédite… en se glissant dans la peau d’une adorable femelle castor. Conçu par des scientifiques visionnaires, ce dispositif permet de transférer la conscience humaine dans le corps de robots-animaux plus vrais que nature. Mabel se lance alors dans une aventure unique et riche en découvertes au cœur du règne animal.</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Animation, Aventure, Comédie</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Piper Curda, Bobby Moynihan, Jon Hamm, Kathy Najimy, Dave Franco, Eduardo Franco, Aparna Nancherla, Sam Richardson</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Mallory Wanecque, Piper Curda, Artus</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=K2tl-7DCb8o</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000009065.html</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/88/05/8805e6066390aca96dbd7097cf95f4ee.jpg", "https://fr.web.img6.acsta.net/img/61/8c/618c5ab7cd904bd390930c512362f430.jpg", "https://fr.web.img4.acsta.net/img/8c/38/8c38d8211474adcd11137cca34850e58.jpg", "https://fr.web.img2.acsta.net/img/23/a8/23a82df42389f30bae3bec524a6f3578.jpg", "https://fr.web.img5.acsta.net/img/4f/9e/4f9e3ed6f7c1375756cf8917cef8a045.jpg", "https://fr.web.img2.acsta.net/img/56/2d/562d4b296cf88c30f1c65a2e5e2b687c.jpg", "https://fr.web.img3.acsta.net/img/e1/5e/e15eb116a489b8fb20ef41766e378b24.jpg", "https://fr.web.img5.acsta.net/img/4c/9c/4c9c7308b2263e54974566f40f86375c.jpg", "https://fr.web.img4.acsta.net/img/e3/4d/e34dc0c5f2b1cb75e2fbc4399c1a1bad.jpg", "https://fr.web.img2.acsta.net/img/56/52/56521974a832a18c8409390f77810111.jpg", "https://fr.web.img5.acsta.net/img/38/4a/384aa05b75485739d194d62dadd28191.jpg", "https://fr.web.img4.acsta.net/img/87/06/8706b673a255d30d9506e690b49cbe80.jpg", "https://fr.web.img4.acsta.net/img/a3/e4/a3e4bc7bcb51c89f350f81a3e7f650f6.jpg", "https://fr.web.img4.acsta.net/img/03/f0/03f05c19decc527a54138ce32eed93b5.jpg", "https://fr.web.img2.acsta.net/img/97/c5/97c5c63191f1901d79430d20d3065787.jpg", "https://fr.web.img4.acsta.net/img/07/e4/07e41e103425a278485d5aaaff68d0c6.jpg", "https://fr.web.img5.acsta.net/img/ab/4a/ab4ab1b0924cfc57f2073c406e519f14.jpg", "https://fr.web.img6.acsta.net/img/64/6e/646ede7db2362b0697e7b19d027c4a49.jpg", "https://fr.web.img6.acsta.net/img/31/85/31856503cab9ba555d66d41ca2689bad.jpg", "https://fr.web.img5.acsta.net/img/da/5f/da5f5c1914f50e29b804184eb7c06aa0.jpg", "https://fr.web.img5.acsta.net/img/1d/6f/1d6fc64b29393b832f1271a4677e1a7f.jpg", "https://fr.web.img2.acsta.net/img/1b/ec/1bec74255b059c49218ba26bf12722ee.jpg", "https://fr.web.img3.acsta.net/img/fa/b7/fab79f452c9f9f4ed49c3ce148afd3c7.jpg", "https://fr.web.img5.acsta.net/img/bd/3a/bd3a0822ef04419f508c8fb8e8af0fa0.jpg", "https://fr.web.img3.acsta.net/img/e6/e3/e6e3e6cf4d5c66835eee0f63f8c0fc64.jpg", "https://fr.web.img4.acsta.net/img/0b/0e/0b0e34f52e2c6f2e176fe981f559d64f.jpg", "https://fr.web.img2.acsta.net/img/c9/94/c9946bdc5ddab7d74b340b46e6030467.jpg", "https://fr.web.img2.acsta.net/img/0d/fd/0dfd011c9452529aaf0832ba691ef050.jpg"]</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -3332,53 +3390,54 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/45/92/4592d30b6f185a47c81625b1f94820bc.jpg</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
         <is>
           <t>Inspiré d'une histoire vraie, Christy retrace l'ascension tumultueuse de la boxeuse Christy Martin, qui est passée de l'anonymat à la célébrité. La légendaire ténacité de Christy sur le ring cache en réalité des combats plus intimes avec sa famille, son identité et une relation toxique qui pourrait bien se transformer en une question de vie ou de mort.</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Biopic, Drame</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sydney Sweeney, Ben Foster, Merritt Wever, Katy O'Brian, Ethan Embry, Jess Gabor, Chad L. Coleman, Tony Cavalero</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sydney Sweeney, Ben Foster, Merritt Wever</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=hSHwFDPfeV8</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=264144.html</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/10/aa/10aaea641b92c8254029081fc6fef889.jpg", "https://fr.web.img5.acsta.net/img/75/29/75293252277b9d1c570bcddc2612e423.jpg", "https://fr.web.img4.acsta.net/img/a6/c4/a6c4f6e7ce0a3a867c174d8b535371ff.jpg"]</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -3420,53 +3479,54 @@
           <t>https://fr.web.img5.acsta.net/c_310_420/img/d0/9f/d09ff1ec5ee43c6f7f17d6622d7422d0.jpg</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>À la Maison des femmes, entre soin, écoute et solidarité, une équipe se bat chaque jour pour accompagner les femmes victimes de violences dans leur reconstruction. Dans ce lieu unique, Diane, Manon, Inès, Awa et leurs collègues accueillent, soutiennent, redonnent confiance. Ensemble, avec leurs forces, leurs fragilités, leurs convictions et une énergie inépuisable.</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Karin Viard, Lætitia Dosch, Oulaya Amamra, Eye Haïdara, Pierre Deladonchamps, Juliette Armanet, Laurent Stocker, Jean-Charles Clichet</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Karin Viard, Laetitia Dosch, Eye Haïdara</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=yAwvKg9T47Q</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012019.html</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/8a/88/8a88c2c86ed3698d1270a8e6f9fe393f.jpg", "https://fr.web.img5.acsta.net/img/0c/56/0c562bc4f318b3f6e87106caebada448.jpg", "https://fr.web.img6.acsta.net/img/4c/a6/4ca6651f4ffa090ac1ed0eb106059907.jpg", "https://fr.web.img5.acsta.net/img/d7/30/d7301415402762258a105d82a9c85c36.jpg", "https://fr.web.img6.acsta.net/img/82/1f/821fe7e03b70d805fd2a3ed6134b21c8.jpg", "https://fr.web.img2.acsta.net/img/c0/90/c090b4bec0837ebba7db0715d4cb11d6.jpg", "https://fr.web.img6.acsta.net/img/4c/69/4c69440f7cc977c3d0bd540e78d94da5.jpg", "https://fr.web.img4.acsta.net/img/80/d4/80d413965459d750fb2aa12f9fac9fd8.jpg", "https://fr.web.img5.acsta.net/img/f0/ae/f0aeafe6cde0b7d886d5ee466d139e39.jpg", "https://fr.web.img2.acsta.net/img/d8/be/d8becce5aeae185ef4b960ad7e8e2122.jpg", "https://fr.web.img6.acsta.net/img/80/17/801724aa27a843655c6382d36f6460c0.jpg", "https://fr.web.img4.acsta.net/img/66/ec/66ecb665598ef7bcafb61a2c356d22ab.jpg", "https://fr.web.img3.acsta.net/img/d9/99/d9995326016481320d40ce58a9362975.jpg", "https://fr.web.img3.acsta.net/img/2c/5f/2c5f82fc07e4a26f372da2d9abeb0776.jpg", "https://fr.web.img5.acsta.net/img/06/5e/065e2f738f2a2e12ea3d34c2ed30bb7c.jpg", "https://fr.web.img2.acsta.net/img/1b/9b/1b9b663d4879a9a924b1844ebee9185a.jpg", "https://fr.web.img4.acsta.net/img/ab/9b/ab9b7b6ed610c4f1345909ca45a3f7a5.jpg"]</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -3506,11 +3566,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>a partir de 12 ans</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>https://fr.web.img5.acsta.net/c_310_420/img/41/c8/41c82c9f0ee7745eaa2220a0185ed6f2.jpg</t>
@@ -3518,51 +3574,56 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>Birahima, orphelin guinéen d’une dizaine d’années, doit quitter son village pour tenter de passer la frontière et retrouver une tante qui se serait installée au Libéria. Le jeune garçon se met dans les pas de Yacouba, bonimenteur de grands chemins jouant les guides de substitution. Mais sur la route, la rencontre avec des enfants soldats fait basculer le destin de Birahima. Engagé involontaire, que lui réserve le sentier de la guerre ?</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Animation, Drame</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>France, Luxembourg, Canada, Belgique</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Chris Aboubacar Hanta Traoré / SK 07, Thomas Ngijol, Marc Zinga, Annabelle Lengronne</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>SK07, Thomas Ngijol, Marc Zinga</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=K6gJ-fYqSlg</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=290253.html</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/2a/b0/2ab0dab69af2a3c63249e73dcd262867.jpg", "https://fr.web.img6.acsta.net/img/37/9a/379af02758660dd03f2426336e9ffdd9.jpg", "https://fr.web.img6.acsta.net/img/4a/44/4a44551c5d1f14c7c57339e469f6ccef.jpg", "https://fr.web.img4.acsta.net/img/31/ae/31ae353cea358ff3226ae772c97f95d5.jpg", "https://fr.web.img6.acsta.net/img/0a/36/0a367f14f4ffd873a5574667b9916736.jpg", "https://fr.web.img2.acsta.net/img/3b/0a/3b0a0e1de296b4b8dcaecbb146b3175d.jpg", "https://fr.web.img5.acsta.net/img/2d/35/2d35cb1eea9e4ef6f1322712b609a408.jpg", "https://fr.web.img6.acsta.net/img/96/76/967684c550c39eaae2241e3bed3201ff.jpg", "https://fr.web.img4.acsta.net/img/e3/54/e35484ccc63b23d91a9c0b3a07428ea8.jpg"]</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -3604,53 +3665,54 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/82/9e/829ecf49faaf8f4534f045054c096d9d.jpg</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
         <is>
           <t>Audrey, fille d’agriculteurs et cheffe de rayon dans un hypermarché en province, se voit propulsée à la centrale d’achat de son enseigne afin d'y défendre la filière bio et locale. Alors qu’elle fait équipe avec un négociateur aux méthodes redoutables, Audrey va devoir se battre pour faire exister ses convictions au sein d'un système impitoyable.</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Thriller</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Olivier Gourmet, Ana Girardot, Julien Frison, Jonas Bloquet, Camille Moutawakil, Catherine Vinatier, Camille Sansterre, Grégoire Monsaingeon</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Ana Girardot, Olivier Gourmet, Julien Frison</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=rR9WFbLhwzU</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016305.html</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/dd/4f/dd4fb9a2ec6c8efa39013f9d3eb8ec2c.jpg", "https://fr.web.img4.acsta.net/img/39/3a/393aae3289b4d53573b12a823953eaac.jpg", "https://fr.web.img4.acsta.net/img/75/eb/75eb5c8bef9955420f1ebf3eedc82df2.jpg", "https://fr.web.img4.acsta.net/img/8e/87/8e87b307c382d490c74c3c79f610faa2.jpg", "https://fr.web.img5.acsta.net/img/f0/6c/f06cf1035e85143198560d0dcad38928.jpg", "https://fr.web.img5.acsta.net/img/db/55/db5584a05d9b2d2aab28aa57a964c325.jpg", "https://fr.web.img5.acsta.net/img/54/f4/54f43ff75322bf10ba5436836a31a14d.jpg", "https://fr.web.img4.acsta.net/img/a4/9f/a49f5f02a8156d22c91c28d14c9a2d3f.jpg"]</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
@@ -3692,53 +3754,54 @@
           <t>https://fr.web.img4.acsta.net/c_310_420/img/a3/21/a3212f7a3bc901b69704c09de6e30093.jpg</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
         <is>
           <t>Alex a un problème : son nouveau voisin est son sosie parfait. Avec des cheveux. Un double en mieux, qui va totalement bouleverser son existence.</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Laurent Lafitte, Olga Kurylenko, Blanche Gardin, Valérie Donzelli, Monsieur Fraize, Zabou Breitman, Bertrand Goncalves</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Laurent Lafitte, Blanche Gardin, Olga Kurylenko</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ObYzfs8ITaE</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=288260.html</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/80/5b/805b22393a7bfefa87e3451df4cf7dec.jpg", "https://fr.web.img5.acsta.net/img/07/ab/07abed9ca6cb0edbc30f2b81cbb9b834.jpg", "https://fr.web.img6.acsta.net/img/4b/3f/4b3fbfd620d39125a6f27fb7892d55bb.jpg", "https://fr.web.img3.acsta.net/img/23/af/23af1eaeb399756c22b6bf621a1d2975.jpg", "https://fr.web.img6.acsta.net/img/33/47/334744d4e4ada016646ca09124efe5f1.jpg", "https://fr.web.img2.acsta.net/img/9a/5f/9a5fb0790ce6ddcc6a39202ec8828fe5.jpg", "https://fr.web.img6.acsta.net/img/6b/da/6bdaeb4a15e035b7aa58b4e87bd47ac7.jpg", "https://fr.web.img2.acsta.net/img/b9/62/b962e3314824b9b32d8cf4320496290c.jpg"]</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -3780,53 +3843,54 @@
           <t>https://fr.web.img3.acsta.net/c_310_420/img/d2/72/d272d8a1cec3d5bf9aa5e254588b10de.jpg</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
         <is>
           <t>Personne n'aurait parié sur Jérémy, coincé derrière le comptoir d’un vidéo club à Amiens, ou sur Bouna, lorsqu'il faisait des ménages à l’aéroport d’Orly. Sans contacts, sans argent et avec un niveau d'anglais plus qu’approximatif, rien ne les prédestinait à devenir des agents qui comptent en NBA.Inspiré d’une histoire vraie, ce film raconte le parcours de deux outsiders qui, grâce à leur passion absolue pour le basket et leur amitié indéfectible, ont bravé tous les obstacles pour réaliser leur Rêve Américain.</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Comédie</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Jean-Pascal Zadi, Raphaël Quenard, Gregory Defleur, David Clark, Josh Casaubon, Etienne Guillou-Kervern, Gabriel Caballero, Momar Sakanoko</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Jean-Pascal Zadi, Raphaël Quenard, Olga Mouak</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=X-wf0nW8E1Q</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000012480.html</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/b7/65/b765d01c1f83fab3afe71087abd35a06.jpg", "https://fr.web.img4.acsta.net/img/ea/31/ea31591200d967dcd2999ed02f382e8e.jpg", "https://fr.web.img4.acsta.net/img/ff/61/ff61f45f7bdcf7a7ca6862dfc48ba478.jpg", "https://fr.web.img6.acsta.net/img/32/bf/32bfb682f73bf2711f47407c031df038.jpg", "https://fr.web.img5.acsta.net/img/12/cd/12cd6ac013e7b4b199c369c0083224e7.jpg", "https://fr.web.img6.acsta.net/img/81/50/815024efa8eb8af4d95e58639086579c.jpg", "https://fr.web.img6.acsta.net/img/b1/b9/b1b9f4f289f95d92a85f8ac535a51e0e.jpg", "https://fr.web.img4.acsta.net/img/b1/22/b12203583896a9a8fd28e964c04cd303.jpg", "https://fr.web.img6.acsta.net/img/e8/43/e8434aa96819d25b68a2b94fce29b356.jpg", "https://fr.web.img2.acsta.net/img/77/c9/77c9d4f0698e9100645f9fd750d27772.jpg", "https://fr.web.img2.acsta.net/img/e7/0d/e70d84534a583d330f41bef5182f7421.jpg", "https://fr.web.img4.acsta.net/img/96/ee/96eec49247ebf80dcd7c4efd4d801cde.jpg", "https://fr.web.img6.acsta.net/img/c8/cb/c8cb5557dd1cbaa78829f18c5f5cc79f.jpg"]</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -3880,57 +3944,58 @@
           <t>https://fr.web.img5.acsta.net/c_310_420/pictures/17/01/10/15/08/573198.jpg</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
         <is>
           <t>Le destin extraordinaire des trois scientifiques afro-américaines qui ont permis aux États-Unis de prendre la tête de la conquête spatiale, grâce à la mise en orbite de l’astronaute John Glenn. Maintenues dans l’ombre de leurs collègues masculins et dans celle d’un pays en proie à de profondes inégalités, leur histoire longtemps restée méconnue est enfin portée à l’écran.</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Drame, Biopic</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Taraji P. Henson, Octavia Spencer, Janelle Monaé, Kevin Costner, Kirsten Dunst, Jim Parsons, Mahershala Ali, Glen Powell</t>
-        </is>
-      </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>Taraji P. Henson, Octavia Spencer, Janelle Monáe</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
           <t>The Actor Awards 2017: Meilleur ensemble d'acteurs</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>2017-03-08</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=_HbR5viCF3g</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=219070.html</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/pictures/17/01/30/11/25/216160.jpg", "https://fr.web.img6.acsta.net/pictures/16/12/09/11/08/113740.jpg", "https://fr.web.img4.acsta.net/pictures/16/12/09/11/07/479909.jpg", "https://fr.web.img6.acsta.net/pictures/16/12/09/11/07/479440.jpg", "https://fr.web.img2.acsta.net/pictures/16/12/09/11/07/478971.jpg", "https://fr.web.img4.acsta.net/pictures/16/12/09/11/07/478034.jpg", "https://fr.web.img5.acsta.net/pictures/16/10/18/10/13/486441.jpg", "https://fr.web.img6.acsta.net/pictures/16/10/18/10/13/485972.jpg", "https://fr.web.img4.acsta.net/pictures/16/10/06/09/44/210686.jpg", "https://fr.web.img6.acsta.net/pictures/16/10/06/09/44/075749.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/27/16/26/372625.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/27/16/26/372156.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/27/16/26/371687.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/27/16/26/371062.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/27/16/26/370437.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/13/17/58/418789.jpg", "https://fr.web.img4.acsta.net/pictures/16/09/13/17/58/418321.jpg", "https://fr.web.img6.acsta.net/pictures/16/09/13/17/58/417696.jpg", "https://fr.web.img2.acsta.net/pictures/16/09/13/17/58/417227.jpg", "https://fr.web.img3.acsta.net/pictures/16/09/13/17/58/416445.jpg"]</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>2017-03-08</t>
         </is>
@@ -3949,7 +4014,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woman and child VO</t>
+          <t>Woman and child</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3976,49 +4041,54 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/48/5a/485af2a4575500546e6af0c462d9f150.jpg</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
         <is>
           <t>Mahnaz, une infirmière de 45 ans, élève seule ses enfants. Alors qu’elle s’apprête à épouser son petit ami Hamid, son fils Aliyar est renvoyé de l’école. Lorsqu’un un accident tragique vient tout bouleverser, Mahnaz se lance dans une quête de justice pour obtenir réparation...</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>131</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Parinaz Izadyar, Sinan Mohebi, Payman Maadi</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>https://www.allocine.fr/video/player_gen_cmedia=20632702&amp;cfilm=1000019745.html</t>
-        </is>
-      </c>
       <c r="T38" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/watch?v=PXyb_-CAgNk</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019745.html</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/42/20/4220d60b7edb1ed8c0b8a85ea8ad9582.jpg", "https://fr.web.img4.acsta.net/img/77/a1/77a1bde1cabfd2b837735ac3a1c9ff72.jpg", "https://fr.web.img5.acsta.net/img/a4/b2/a4b2a9aa5fcbb8581be337ff35ce644b.jpg", "https://fr.web.img6.acsta.net/img/30/f6/30f6c8d983f12011d6edfbca88b118e1.jpg", "https://fr.web.img2.acsta.net/img/b6/8f/b68ff068e5eefbfad3c6393a1d1cd6f5.jpg", "https://fr.web.img4.acsta.net/img/b1/54/b1545b5f632dfd513dcf79312f5deda3.jpg", "https://fr.web.img5.acsta.net/img/50/69/5069460ce8637aff4292a0f24b5744d1.jpg"]</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
@@ -4064,57 +4134,58 @@
           <t>https://fr.web.img3.acsta.net/c_310_420/img/53/4b/534b15308fa026cff713af2a4ccae844.jpg</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
         <is>
           <t>Colin, un jeune homme introverti, rencontre Ray, le séduisant et charismatique leader d’un club de motards. Ray l’introduit dans sa communauté et fait de lui son soumis.</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Drame, Erotique, Comédie, Romance</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Grande-Bretagne, Irlande</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Harry Melling, Alexander Skarsgård, Lesley Sharp, Douglas Hodge, Jake Shears, Mat Hill, Nick Figgis, Zoe Engerer</t>
-        </is>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
+          <t>Harry Melling, Alexander Skarsgård, Douglas Hodge</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
           <t>Festival de Cannes 2025: Un Certain Regard - Prix du scénario</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Gl8n5I-IIHU</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000004467.html</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/40/d2/40d2e73cb6afdffbfe7eec89b048a071.jpg", "https://fr.web.img6.acsta.net/img/ab/be/abbe9e1f229cd506da96e78c680fceda.jpg", "https://fr.web.img6.acsta.net/img/dc/d2/dcd282952fe2ea9b5477ca04aa1be222.jpg", "https://fr.web.img6.acsta.net/img/59/5b/595bc464ed46845fb8ce804fe0eee894.jpg", "https://fr.web.img5.acsta.net/img/a3/07/a307f75887d4c360a599662e51bfa218.jpg", "https://fr.web.img5.acsta.net/img/e6/fb/e6fb4dd4df76c0acfec4d4beff1fcd3f.jpg", "https://fr.web.img4.acsta.net/img/b6/f8/b6f8d5502aa573671ed58cf052213e65.jpg", "https://fr.web.img6.acsta.net/img/7e/e1/7ee1912a1a102d73c581f70f5216fa5e.jpg", "https://fr.web.img6.acsta.net/img/1f/af/1faf21d86fb40f1ddf1f7743f1084f1e.jpg", "https://fr.web.img6.acsta.net/img/bb/c6/bbc687323048a5e0b72f7903f4689979.jpg", "https://fr.web.img4.acsta.net/img/93/14/9314fb2e77d009b6152e195eec5869ac.jpg", "https://fr.web.img5.acsta.net/img/e0/cf/e0cf8cd126fd311965af634189a1a084.jpg"]</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
@@ -4168,57 +4239,58 @@
           <t>https://fr.web.img4.acsta.net/c_310_420/pictures/14/12/01/12/08/107961.jpg</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
         <is>
           <t>Ben et Maïna vivent avec leur père tout en haut d'un phare sur une petite île. Pour les protéger des dangers de la mer, leur grand-mère les emmène vivre à la ville. Ben découvre alors que sa petite soeur est une selkie, une fée de la mer dont le chant peut délivrer les êtres magiques du sort que leur a jeté la Sorcière aux hiboux. Au cours d'un fantastique voyage, Ben et Maïna vont devoir affronter peurs et dangers, et combattre la sorcière pour aider les êtres magiques à retrouver leur pouvoir.</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Animation, Famille, Fantastique</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Irlande, Danemark, Belgique, Luxembourg, France</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>David Rawle, Brendan Gleeson, Lisa Hannigan, Fionnula Flanagan, Lucy O'Connell, Jon Kenny, Pat Shortt, Colm Ó'Snodaigh</t>
-        </is>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
+          <t>Jean-Stan Du Pac, David Rawle, Patrick Bethune</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
           <t>European Film Awards - Prix du cinéma européen 2015: European Film Award du Meilleur film d'animation</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>2014-12-10</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=EjbEgXaEG8U</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=226004.html</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/066024.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/278027.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/274882.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/089885.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/084747.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/080255.jpg", "https://fr.web.img4.acsta.net/pictures/14/10/07/14/25/059597.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/052409.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/019143.jpg", "https://fr.web.img6.acsta.net/pictures/14/10/07/14/25/011729.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/008262.jpg", "https://fr.web.img5.acsta.net/pictures/14/10/07/14/25/000204.jpg", "https://fr.web.img2.acsta.net/pictures/14/09/26/15/58/003194.jpg", "https://fr.web.img5.acsta.net/pictures/14/08/27/16/36/103988.jpg", "https://fr.web.img6.acsta.net/pictures/14/06/02/16/12/536711.png"]</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>2014-12-10</t>
         </is>
@@ -4264,53 +4336,54 @@
           <t>https://fr.web.img2.acsta.net/c_310_420/img/cb/0f/cb0f73df615316b86cb8478c341cb599.jpg</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
         <is>
           <t>Jeune idole de la pop en pleine ascension, Mai commet l’irréparable : tomber amoureuse, malgré l’interdiction formelle inscrite dans son contrat. Lorsque sa relation éclate au grand jour, Mai est traînée par sa propre agence devant la justice. Confrontés à une machine implacable, les deux amants décident de se battre pour défendre leur droit le plus universel : celui d’aimer.</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Japon, France</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Kyoko Saito, Yuki Kura, Kenjirō Tsuda, Erika Karata, Yuna Nakamura, Miyu Ogawa</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Kyoko Saito, Yuki Kura, Erika Karata</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=opqrvdhNBGk</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000019853.html</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/2a/ee/2aeeb5bac4f7e7738e57b64b3254f7ac.jpg", "https://fr.web.img2.acsta.net/img/57/58/5758b2b5d69e2a393dbc8c3e56f917f2.jpg", "https://fr.web.img2.acsta.net/img/a5/96/a59630b494a13bf5be9f32b88ff7a2e7.jpg", "https://fr.web.img6.acsta.net/img/af/6c/af6c769b3e356c39c2d4789eff46a044.jpg", "https://fr.web.img6.acsta.net/img/51/f1/51f1e538db936a7eb7769065a136c899.jpg", "https://fr.web.img3.acsta.net/img/38/cc/38cc70ca80d9bdd61ba77e39daf89326.jpg", "https://fr.web.img6.acsta.net/img/15/57/1557ea7681e4ff9c8d57f4e3f15ae069.jpg", "https://fr.web.img3.acsta.net/img/ce/b4/ceb47338452bd8d5073bd7805e5c916b.jpg", "https://fr.web.img6.acsta.net/img/7a/1b/7a1bd16d30f0f260f8ac109d51c109d8.jpg", "https://fr.web.img2.acsta.net/img/b3/4a/b34aa44facfe89723f48803f6e4c007d.jpg"]</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
@@ -4352,53 +4425,54 @@
           <t>https://fr.web.img2.acsta.net/c_310_420/img/19/f2/19f23e775fb0d088989e111f7a65d696.jpg</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
         <is>
           <t>Années 1980, un ancien joueur de tennis devient l’entraîneur d’un jeune talent timide, écrasé par les attentes de son père.</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Pierfrancesco Favino, Tiziano Menichelli, Giovanni Ludeno, Dora Romano, Valentina Bellè, Astrid Meloni, Chiara Bassermann, Paolo Briguglia</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Pierfrancesco Favino, Tiziano Menichelli, Giovanni Ludeno</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=aDZSR9JOUbw</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=283955.html</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/fa/42/fa42bd0b39395a94243253725e7d2140.jpg", "https://fr.web.img5.acsta.net/img/cc/d0/ccd0fd313423605647b83ef61de61a48.jpg", "https://fr.web.img6.acsta.net/img/33/ae/33ae80c7885681564d1357935cc63b6f.jpg", "https://fr.web.img4.acsta.net/img/9a/2b/9a2bc1a14727fcc9fee01a52697677b7.jpg", "https://fr.web.img2.acsta.net/img/01/73/017392cd8d6c596339cf1af8b45d5026.jpg", "https://fr.web.img6.acsta.net/img/08/c1/08c18c754ce9fd395965cc0e16509658.jpg", "https://fr.web.img5.acsta.net/img/9a/af/9aaf9af68b13c051ebc09568452697b6.jpg", "https://fr.web.img5.acsta.net/img/ba/58/ba58513acb3e3cbb3edcc8010a92c753.jpg", "https://fr.web.img3.acsta.net/img/19/8c/198cbbbe157e16d0ad6b5283f43efb41.jpg", "https://fr.web.img4.acsta.net/img/5b/40/5b40c90cb22733ea4e47125e7fd3b8fb.jpg", "https://fr.web.img3.acsta.net/img/39/00/390055c941655abb5b8b7b3399942430.jpg", "https://fr.web.img6.acsta.net/img/6c/69/6c69fb3ab9646bf2e9906d679b4d8661.jpg", "https://fr.web.img3.acsta.net/img/d6/4e/d64ee73f94fc2b9aca2b0db71a73d29a.jpg", "https://fr.web.img6.acsta.net/img/c5/9d/c59d6fc53d8b17e91055035ff758117e.jpg"]</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -4440,7 +4514,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sony, a partir de 12 ans</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4450,51 +4524,56 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
           <t>Scarlet, une princesse médiévale experte en combat à l'épée se lance dans une périlleuse quête pour venger la mort de son père. Son plan échoue et grièvement blessée elle se retrouve projetée dans un autre monde, le Pays des Morts. Elle va croiser la route d'un jeune homme idéaliste de notre époque, qui non seulement l'aide à guérir mais lui laisse également entrevoir qu'un monde sans rancœur ni colère est possible. Face au meurtrier de son père, Scarlet devra alors mener son plus grand combat : briser le cycle de la haine et donner un sens à sa vie en dépassant son désir de vengeance.</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Animation, Drame</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Japon, U.S.A.</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Mana Ashida, Masaki Okada, Yutaka Matsushige, Kotaro Yoshida, Kôji Yakusho, Masachika Ichimura, Yuki Saito, Shōta Sometani</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Mana Ashida, Masaki Okada, Masachika Ichimura</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=HBwFFjlfWmM</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000017448.html</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>["https://fr.web.img5.acsta.net/img/29/64/2964de26a516d8ed1135e52158c86303.jpg", "https://fr.web.img4.acsta.net/img/34/52/34520a32818fc0f068fdd6582303c6e4.jpg", "https://fr.web.img6.acsta.net/img/16/de/16deeb7b15a8f154209b1c0b20fbae6c.jpg", "https://fr.web.img6.acsta.net/img/12/46/1246b0c5254a63e1433b8b9b26b1303e.jpg", "https://fr.web.img2.acsta.net/img/80/f0/80f0078803925d21f0ffa8802a17a481.jpg", "https://fr.web.img5.acsta.net/img/1d/db/1ddb882ebf3742cea840abd4da5715bb.jpg", "https://fr.web.img4.acsta.net/img/be/fb/befb71925276774dd7af527aa8c330c6.jpg", "https://fr.web.img5.acsta.net/img/0f/52/0f5287e4b03b2804b6e596a3ba244f5b.jpg", "https://fr.web.img3.acsta.net/img/81/36/8136ab363e2760e8726eb3c90f72d81a.jpg", "https://fr.web.img6.acsta.net/img/b7/c7/b7c721051b64fb6a41ca7f2d4bd69965.jpg", "https://fr.web.img6.acsta.net/img/bc/68/bc685c8a111af3a25fae17e8da4d0b06.jpg", "https://fr.web.img4.acsta.net/img/32/0d/320da09f69e878439aacfca01629664c.jpg", "https://fr.web.img5.acsta.net/img/93/03/93035aaf9bd9e7f846b7e7ef18b0662d.jpg", "https://fr.web.img6.acsta.net/img/e6/c1/e6c1eaa360640935b9d8eb04f9c54a10.jpg", "https://fr.web.img4.acsta.net/img/16/fc/16fc1b312395f6b9d61845e496a05c36.JPG", "https://fr.web.img6.acsta.net/img/3b/48/3b48af3fd723313d43f9714a323818d0.JPG", "https://fr.web.img6.acsta.net/img/d1/37/d137627d9e97e0f29cfc36b443cfc798.JPG", "https://fr.web.img6.acsta.net/img/a8/ca/a8ca693084b88c847123f104a7cc0ae8.JPG", "https://fr.web.img3.acsta.net/img/74/35/74352d1cbe758062224039f65af2952e.JPG"]</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -4544,57 +4623,58 @@
           <t>https://fr.web.img2.acsta.net/c_310_420/img/cc/09/cc093056d1d3096effc536a9905e6d3d.jpg</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
         <is>
           <t>Mariano De Santis, Président de la République italienne, est un homme marqué par le deuil de sa femme et la solitude du pouvoir. Alors que son mandat touche à sa fin, il doit faire face à des décisions cruciales qui l’obligent à affronter ses propres dilemmes moraux : deux grâces présidentielles et un projet de loi hautement controversé.Aucune référence à des présidents existants, il est le fruit de l'imagination de l'auteur.</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Drame, Romance</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Toni Servillo, Anna Ferzetti, Massimo Venturiello, Milvia Marigliano, Orlando Cinque, Giuseppe Gaiani, Giovanna Guida, Alessia Giuliani</t>
-        </is>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
+          <t>Toni Servillo, Anna Ferzetti, Orlando Cinque</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>Mostra de Venise 2025: Coupe Volpi de la meilleure interprétation masculine</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=mJH3p0hr7zA</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000016512.html</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/4c/bb/4cbbbafb5f4ef80a8fd96826473953c6.jpg", "https://fr.web.img5.acsta.net/img/1c/30/1c301e495dc5675cc85d06ca20374a22.jpg", "https://fr.web.img6.acsta.net/img/d7/b7/d7b7a96adb9eb7ab085bb96f8b7f14ee.jpg", "https://fr.web.img3.acsta.net/img/67/cc/67ccd69691e93ba0fe65beee28d1f180.jpg", "https://fr.web.img3.acsta.net/img/2e/a8/2ea80882c03f9d0498b761b60089b2b1.jpg", "https://fr.web.img5.acsta.net/img/ba/cf/bacf16f5254a8c59045edd040f1e492b.jpg", "https://fr.web.img4.acsta.net/img/25/2c/252c2c8c4bdc2b5ee6453ca1e433aac0.jpg", "https://fr.web.img2.acsta.net/img/cb/16/cb161d0537f67fc117da4fa5eb0e0968.jpg", "https://fr.web.img6.acsta.net/img/bb/4c/bb4cfdb4e6e8395cb6f827a8bbab3267.jpg", "https://fr.web.img6.acsta.net/img/f2/28/f2287d7ccf2b6eb62a19598bff1b72de.jpg", "https://fr.web.img5.acsta.net/img/a9/b2/a9b22d04fa03e9bd50f9026148690ceb.jpg"]</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>2026-01-28</t>
         </is>
@@ -4640,53 +4720,54 @@
           <t>https://fr.web.img6.acsta.net/c_310_420/img/c6/a0/c6a084a69f3a7a701da8a3308e8d5c5f.jpg</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
         <is>
           <t>Lionel, jeune chanteur talentueux originaire du Kentucky, grandit au son des chansons que son père chantait sur le perron de leur maison.En 1917, il quitte la ferme familiale pour intégrer le Conservatoire de Boston, où il fait la rencontre de David, un étudiant en composition aussi brillant que séduisant, mais leur lien naissant est brutalement interrompu lorsque David est mobilisé à la fin de la guerre.En 1920, réunis le temps d’un hiver, Lionel et David sillonnent les forêts et les îles du Maine pour collecter et préserver les chants folkloriques menacés d’oubli. Cette parenthèse marquera à jamais Lionel.Au cours des décennies suivantes, Lionel connaît la reconnaissance, la réussite, et d’autres histoires d’amour au fil de ses voyages à travers l’Europe. Mais ses souvenirs avec David le hantent encore, jusqu’au jour où une trace de leur œuvre commune ressurgit et lui révèle combien cette relation a résonné plus fort que toutes les autres..</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Romance, Historique, Drame</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>U.S.A.</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Paul Mescal, Josh O'Connor, Molly Price, Alison Bartlett, Michael Schantz, Chris Cooper, Raphael Sbarge, Hadley Robinson</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Josh O'Connor, Paul Mescal, Chris Cooper</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=E2PSkw8BI7k</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=297924.html</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/img/1d/f8/1df8fb92d96b9df18fd392f746a4cbff.jpg", "https://fr.web.img6.acsta.net/img/28/9a/289a1bb9e08370588d27f4a930a761d0.jpg", "https://fr.web.img4.acsta.net/img/71/af/71af24f5f60f17af921c4decb16c86d4.jpg", "https://fr.web.img6.acsta.net/img/d7/a9/d7a9a5d1d14ea085059a66ee6204c67b.jpg"]</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
@@ -4738,51 +4819,56 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
           <t>Quatre graines de pissenlit rescapées d’explosions nucléaires qui détruisent la Terre, se trouvent projetées dans le cosmos. Après s’être échouées sur une planète inconnue, elles partent à la quête d’un sol propice à la survie de leur espèce.</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Animation, Science Fiction</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>France, Belgique</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>Festival du Film d'Animation d'Annecy 2025: Prix Paul Grimault, Fondation Gan pour le cinéma 2022: Fondation Gan - Prix spécial</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Y4ucI60lK_M</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=279261.html</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>["https://fr.web.img6.acsta.net/img/fc/d8/fcd82cd23dbd78358d01dd70a3669665.jpg", "https://fr.web.img3.acsta.net/img/ba/31/ba31db380503e009acfb33888f1ae891.jpg", "https://fr.web.img6.acsta.net/img/52/f0/52f07f622e0637f90deb44d709c33b7e.jpg", "https://fr.web.img3.acsta.net/img/6b/d7/6bd780e94b8b1a5a8e9e58b402daf4c6.jpg"]</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -4824,53 +4910,54 @@
           <t>https://fr.web.img5.acsta.net/c_310_420/img/b2/0f/b20fa135f8ed4c7d0a5e0949c56e095e.jpg</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
         <is>
           <t>Colette, professeure de cinéma spécialisée dans l’œuvre de Hitchcock, soupçonne son nouveau voisin d’en face d’avoir tué sa femme. Réalité ou déformation professionnelle ? Son mari, François, écrivain de romans historico-policiers un peu désuets, est d’abord sceptique face à l’obsession de Colette pour ce prétendu crime. Il se laisse cependant embarquer dans cette enquête rocambolesque, et, à mesure que les indices s’accumulent et que le mystère s’épaissit, ce couple ordinaire se transforme en duo de détectives hors pair. Alors, y a-t-il vraiment eu un crime au 3 e étage ?</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Comédie dramatique, Policier</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Gilles Lellouche, Laetitia Casta, Guillaume Gallienne, Isabel Aimé González Sola, Jenna Knafo, Katayoon Latif, Matthias Jacquin, Bénédicte Choisnet</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Gilles Lellouche, Laetitia Casta, Guillaume Gallienne</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=nrjXeYFRkpE</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=1000020100.html</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>["https://fr.web.img2.acsta.net/img/af/56/af56a06bd606dccaa8b967c0030d4bd0.jpg", "https://fr.web.img2.acsta.net/img/b4/a1/b4a14af8622a802a494943a23a3986b6.jpg", "https://fr.web.img6.acsta.net/img/3b/72/3b72b4ad9ccf960ae3d393bf8e0317ff.jpg", "https://fr.web.img6.acsta.net/img/5c/7c/5c7c311be7cf8525412d5021ec277a20.jpg", "https://fr.web.img3.acsta.net/img/37/26/3726e04b5239c340e38b25a4bab52d0d.jpg", "https://fr.web.img6.acsta.net/img/6c/f0/6cf0a8524076e49e5f942240c0c7643d.jpg", "https://fr.web.img3.acsta.net/img/92/40/9240f2956590fe69a38a203a4c2ea2d0.jpg", "https://fr.web.img6.acsta.net/img/ee/55/ee55409d927fa8dc0fa5c6c6d9fbf318.jpg", "https://fr.web.img6.acsta.net/img/6e/b0/6eb04c2040068da9b797f85fd0efce76.jpg", "https://fr.web.img3.acsta.net/img/4d/b2/4db21f15cd675c352695b2d876ce72ba.jpg", "https://fr.web.img2.acsta.net/img/73/d6/73d66e3ed9719cd4cff3c0d97cd9e33e.jpg"]</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
@@ -4924,53 +5011,54 @@
           <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
         <is>
           <t>Bienvenue dans la Renaissance ! Une époque où artistes, savants, rois et reines inventent un monde nouveau. Parmi eux, un curieux personnage passe ses journées à dessiner d’étranges machines et à explorer les idées les plus folles. Observer la lune, voler comme un oiseau, découvrir les secrets de la médecine… il rêve de changer le monde. Embarquez pour un voyage avec le plus grand des génies, Léonard de Vinci !</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Animation, Famille, Aventure</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Irlande, U.S.A.</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Stephen Fry, Daisy Ridley, Marion Cotillard, Matt Berry, Natalie Palamides, Jim Capobianco, Ben Stranahan, Jane Osborn</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>André Dussollier, Stephen Fry, Juliette Armanet</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=z5My1jT2f1M</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=284744.html</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/pictures/23/07/05/15/50/5311709.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5297670.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5283631.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5269591.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5255552.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5239953.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5222793.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5208754.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5193155.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5177556.jpg"]</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
@@ -5024,53 +5112,54 @@
           <t>https://fr.web.img5.acsta.net/c_310_420/pictures/23/11/07/16/21/1931517.jpg</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
         <is>
           <t>Bienvenue dans la Renaissance ! Une époque où artistes, savants, rois et reines inventent un monde nouveau. Parmi eux, un curieux personnage passe ses journées à dessiner d’étranges machines et à explorer les idées les plus folles. Observer la lune, voler comme un oiseau, découvrir les secrets de la médecine… il rêve de changer le monde. Embarquez pour un voyage avec le plus grand des génies, Léonard de Vinci !</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Animation, Famille, Aventure</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Irlande, U.S.A.</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Stephen Fry, Daisy Ridley, Marion Cotillard, Matt Berry, Natalie Palamides, Jim Capobianco, Ben Stranahan, Jane Osborn</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>André Dussollier, Stephen Fry, Juliette Armanet</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=z5My1jT2f1M</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=284744.html</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>["https://fr.web.img4.acsta.net/pictures/23/07/05/15/50/5311709.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5297670.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5283631.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5269591.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5255552.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5239953.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5222793.jpg", "https://fr.web.img3.acsta.net/pictures/23/07/05/15/50/5208754.jpg", "https://fr.web.img6.acsta.net/pictures/23/07/05/15/50/5193155.jpg", "https://fr.web.img2.acsta.net/pictures/23/07/05/15/50/5177556.jpg"]</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
@@ -5116,53 +5205,54 @@
           <t>https://fr.web.img5.acsta.net/c_310_420/img/4e/b7/4eb7083418c36bfd338cd34374143071.jpg</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
         <is>
           <t>Héloïse n’a nulle part où aller. Elle fait la rencontre de Mallorie qui lui propose de l’héberger dans l’appartement qu’elle partage avec deux autres jeunes femmes. Héloïse va trouver là un nouveau foyer et une nouvelle famille. Mais leurs blessures passées menacent l’équilibre fragile entre ces femmes en apparence si solides.</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Drame</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>Belgique, France</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Héloïse Volle, Shirel Nataf, Yowa-Angélys Tshikaya, Mona Berard, Jonas Bloquet, Anne Coesens, Hugo Dillon, Kamel Laadaili</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Héloïse Volle, Shirel Nataf, Yowa-Angélys Tshikaya</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Iax6XaKnPdI</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>https://www.allocine.fr/film/fichefilm_gen_cfilm=323410.html</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>["https://fr.web.img3.acsta.net/img/28/97/2897e10fcc1bc33a8961751865a0bd97.jpg", "https://fr.web.img5.acsta.net/img/df/e8/dfe8357ec15075844e103524cbe7b7cf.jpg"]</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>

--- a/Lab/outils/work/enriched.xlsx
+++ b/Lab/outils/work/enriched.xlsx
@@ -1132,7 +1132,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/video/player_gen_cmedia=20633447&amp;cfilm=325278.html</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/09/10/59/20633447_hd_013.mp4</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/video/player_gen_cmedia=20630887&amp;cfilm=1000031821.html</t>
+          <t>https://www.youtube.com/watch?v=T1DZPWrTBQI</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/video/player_gen_cmedia=19602323&amp;cfilm=317561.html</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/23/09/18/17/19602323_hd_013.mp4</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/video/player_gen_cmedia=20627331&amp;cfilm=317577.html</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/02/04/10/37/20627331_hd_013.mp4</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.allocine.fr/video/player_gen_cmedia=20632118&amp;cfilm=1000036350.html</t>
+          <t>https://fr.vid.web.acsta.net/nmedia/33/26/01/12/11/51/20632118_hd_013.mp4</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
